--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X161"/>
+  <dimension ref="A1:X156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="U3" t="n">
         <v>87</v>
@@ -1312,10 +1312,10 @@
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U9" t="n">
         <v>77</v>
@@ -1505,10 +1505,10 @@
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
         <v>75</v>
@@ -2465,10 +2465,10 @@
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
         <v>72</v>
@@ -2561,10 +2561,10 @@
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U22" t="n">
         <v>72</v>
@@ -3127,10 +3127,10 @@
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U28" t="n">
         <v>69</v>
@@ -4095,10 +4095,10 @@
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="U38" t="n">
         <v>67</v>
@@ -4383,10 +4383,10 @@
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U41" t="n">
         <v>67</v>
@@ -4575,10 +4575,10 @@
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U43" t="n">
         <v>67</v>
@@ -5323,10 +5323,10 @@
       </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T51" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="U51" t="n">
         <v>66</v>
@@ -5611,10 +5611,10 @@
       </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T54" t="n">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="U54" t="n">
         <v>65</v>
@@ -5637,30 +5637,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GOLDEN GATE</t>
+          <t xml:space="preserve">SILVER BEAR (L.1781)          </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>092L  005</t>
+          <t>082FNW100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Zeballos</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.4</v>
+        <v>13.1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead, Zinc, Silver</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5676,54 +5676,54 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>652 kt</t>
+          <t>459 t</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 56.1g/t, Ag 11.3g/t</t>
+          <t>Ag 398g/t, Pb 1.33%, Zn 3.81%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>In 1939, a sample from the Golden Gate vein, taken at 12.9 metres from the collar of the shaft, assayed 645.7 grams per tonne gold with 346.1 grams per tonne silver over 0.45 metre, whereas a sample from the bottom of the shaft assayed 91.7 grams per tonne gold over a width of 12.5 centimetres (Property File - W.A. In 1983, diamond drilling encountered a 9.8-metre intercept of 9.6 grams per tonne gold (diamond-drill hole #5) and a 1.5-metre section assaying 135.7 grams per tonne gold and 44.2 grams per tonne silver (George Cross Newsletter #191, #192, 1983; Also at this time, four grab samples from the central trench yielded an average of 20.5 grams per tonne gold and 11.3 grams per tonne silver, whereas a 0.45-metre chip sample (9270) taken 3.7 metres north of the trench assayed 55.8 gram</t>
+          <t>A 35-metre trench sample assayed 221.5 grams per tonne silver, 2.40 per cent zinc and 1.57 per cent lead (GCNL #230, 1997). Drilling intercepts included 102.6, 1877.1 and 574.5 grams per tonne silver, 0.79, 22.6 and 1.09 per cent lead with 1.21, 5.34 and 5.22 per cent zinc over 1.96, 0.51 and 0.54 metres, respectively, in holes 98SB-02, -05 and -06 (McBride, D.E.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$993k</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P55" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Sibola Mines, Billiken Resources Ltd., Can. Superior Ex.</t>
+          <t>Cream Minerals Ltd., Tay Resources Inc., Spey Resources Corp.</t>
         </is>
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U55" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="V55" t="n">
-        <v>50.0025</v>
+        <v>49.85917</v>
       </c>
       <c r="W55" t="n">
-        <v>-126.83194</v>
+        <v>-117.12694</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW100</t>
         </is>
       </c>
     </row>
@@ -5733,21 +5733,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BEAR (L.1781)          </t>
+          <t>SILVER CUP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>082FNW100</t>
+          <t>093M  040</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Glen Vowell</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>13.1</v>
+        <v>10.8</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Silver, Lead, Zinc, Gold, Antimony</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5772,54 +5772,54 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>459 t</t>
+          <t>5 kt</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Ag 398g/t, Pb 1.33%, Zn 3.81%</t>
+          <t>Ag 1484g/t, Pb 9.98%, Zn 9.67%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>A 35-metre trench sample assayed 221.5 grams per tonne silver, 2.40 per cent zinc and 1.57 per cent lead (GCNL #230, 1997). Drilling intercepts included 102.6, 1877.1 and 574.5 grams per tonne silver, 0.79, 22.6 and 1.09 per cent lead with 1.21, 5.34 and 5.22 per cent zinc over 1.96, 0.51 and 0.54 metres, respectively, in holes 98SB-02, -05 and -06 (McBride, D.E.</t>
+          <t>Woolverton in 1927, an average assay for the mine was calculated to be 1483.89 grams per tonne silver, 9.98 per cent lead and 9.67 per cent zinc (Ministry of Mines Annual Report, 1928, page 155).</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>$993k</t>
+          <t>$956k</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P56" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Cream Minerals Ltd., Tay Resources Inc., Spey Resources Corp.</t>
+          <t>Garibaldi Resources Corporation, Golden Sabre Resources Limited; Molnar, Andrew W.</t>
         </is>
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="U56" t="n">
         <v>62</v>
       </c>
       <c r="V56" t="n">
-        <v>49.85917</v>
+        <v>55.35111</v>
       </c>
       <c r="W56" t="n">
-        <v>-117.12694</v>
+        <v>-127.51611</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW100</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++040</t>
         </is>
       </c>
     </row>
@@ -5829,21 +5829,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SILVER CUP</t>
+          <t xml:space="preserve">INDEX                         </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>093M  040</t>
+          <t>082FNW101</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Glen Vowell</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>10.8</v>
+        <v>13.3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Antimony</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5864,40 +5864,44 @@
         <v>0</v>
       </c>
       <c r="J57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>5 kt</t>
+          <t>20 t</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Ag 1484g/t, Pb 9.98%, Zn 9.67%</t>
+          <t>Ag 158g/t, Pb 4.38%, Zn 10.53%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Woolverton in 1927, an average assay for the mine was calculated to be 1483.89 grams per tonne silver, 9.98 per cent lead and 9.67 per cent zinc (Ministry of Mines Annual Report, 1928, page 155).</t>
+          <t>a grab sample assayed 158.1 grams per tonne silver, 10.53 per cent zinc and 4.38 per cent lead (GCNL #174, 1997).</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>$956k</t>
+          <t>$950k</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P57" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Garibaldi Resources Corporation, Golden Sabre Resources Limited; Molnar, Andrew W.</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
+          <t>Cream Minerals Ltd., Tay Resources Inc., Spey Resources Corp.</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>abuts Kokanee Glacier Park boundary</t>
+        </is>
+      </c>
       <c r="S57" t="n">
         <v>1</v>
       </c>
@@ -5908,14 +5912,14 @@
         <v>62</v>
       </c>
       <c r="V57" t="n">
-        <v>55.35111</v>
+        <v>49.85556</v>
       </c>
       <c r="W57" t="n">
-        <v>-127.51611</v>
+        <v>-117.1325</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++040</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW101</t>
         </is>
       </c>
     </row>
@@ -5925,21 +5929,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">INDEX                         </t>
+          <t>AMERICAN BOY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>082FNW101</t>
+          <t>093M  047</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Two Mile</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>13.3</v>
+        <v>6.1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5948,7 +5952,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Silver, Lead, Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5960,44 +5964,40 @@
         <v>0</v>
       </c>
       <c r="J58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>20 t</t>
+          <t>348 t</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Ag 158g/t, Pb 4.38%, Zn 10.53%</t>
+          <t>Ag 366g/t</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>a grab sample assayed 158.1 grams per tonne silver, 10.53 per cent zinc and 4.38 per cent lead (GCNL #174, 1997).</t>
+          <t xml:space="preserve">3 vein is reported to have assayed 49.1 grams per tonne gold, 369.7 grams per tonne silver and 13.46 per cent lead (Thomson, G.R. 1 vein yielded intercepts of 121.8 grams per tone silver over 0.20 metre in hole AB-1 and 59.5 grams per tonne silver over 0.15 metre in hole AB-2 (Thomson, G.R. 6 vein assayed between 6.856 and 14 671.8 grams per tonne silver (George Cross Newsletter #41, 1984). In 2009, drillhole AB10-DDH-1 returned 0.61 metres of 1.2 grams per tonne gold, 151 grams per tonne silver, 1.07 per cent zinc and 2.35 per cent arsenic (Assessment Report 31655, page 28). 4 veins in 1976 and 1978, respectively, is reported to have yielded 4.0 grams per tonne gold with 10,243 grams per tonne silver and 5.9 grams per tonne gold with 57.1 grams per tonne silver over a length of 30 metres </t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>$950k</t>
+          <t>$927k</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P58" t="n">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Cream Minerals Ltd., Tay Resources Inc., Spey Resources Corp.</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>abuts Kokanee Glacier Park boundary</t>
-        </is>
-      </c>
+          <t>Golden Sabre Resources Limited; Molnar, Andrew W., TAD Capital Corp.</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
         <v>1</v>
       </c>
@@ -6008,14 +6008,14 @@
         <v>62</v>
       </c>
       <c r="V58" t="n">
-        <v>49.85556</v>
+        <v>55.31528</v>
       </c>
       <c r="W58" t="n">
-        <v>-117.1325</v>
+        <v>-127.57167</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW101</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++047</t>
         </is>
       </c>
     </row>
@@ -6387,10 +6387,10 @@
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T62" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="U62" t="n">
         <v>62</v>
@@ -7181,35 +7181,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SMITH COPPER (MAIN)</t>
+          <t>TRUE BLUE (L.4859)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>092L  208</t>
+          <t>082FNE002</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Mirror Lake</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Copper, Silver, Gold, Zinc, Lead, Cobalt</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -7220,54 +7220,54 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>84 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Ag 64.4g/t, Cu 1.69%, Pb 3.70%, Zn 12.50%</t>
+          <t>Au 0.9g/t, Ag 37.7g/t, Cu 6.75%, Pb 0.12%, Zn 2.76%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>In 1981, diamond drilling intersected mineralized sections yielding up to 0.67 per cent copper, 0.25 per cent lead, 10.87 per cent zinc and 17.1 grams per tonne silver over 4.5 metres in DDH J-3-81. Another drill hole (DDH J-9-81) intersected 0.17 per cent copper, 5.08 per cent lead, 8.88 per cent zinc and 106.3 grams per tonne silver over 0.8 metre. In 1988, drilling intersected 1.1 metres assaying 1.2 per cent copper and 17.0 per cent zinc in hole N88-03 on the western edge of the occurence (Assessment Report 18704). Drill indicated reserves are 83,906 tonnes grading 64.4 grams per tonne silver, 1.69 per cent copper, 3.7 per cent lead and 12.5 per cent zinc (George Cross News Letter December 7, 1988). Chip sampling (CI-62642), performed during same year, yielded up to 1.18 per cent coppe</t>
+          <t>In 1979, a chip sample from a mineralized lens assayed 0.9 gram per tonne gold, 37.7 grams per tonne silver, 0.12 per cent lead, 2.76 per cent zinc and 6.75 per cent copper (Property File - D.H.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>$455k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="P71" t="n">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Hercules Ventures Inc., Mar-Gold Res., Imperial Metals Corporation</t>
+          <t>QPX Minerals Inc., Sultan Minerals Inc., SMD Min.</t>
         </is>
       </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T71" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U71" t="n">
         <v>62</v>
       </c>
       <c r="V71" t="n">
-        <v>50.36444</v>
+        <v>49.88139</v>
       </c>
       <c r="W71" t="n">
-        <v>-126.91361</v>
+        <v>-116.96</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++208</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE002</t>
         </is>
       </c>
     </row>
@@ -7277,30 +7277,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TRUE BLUE (L.4859)</t>
+          <t xml:space="preserve">MOTHER LODE (L.1497)          </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>082FNE002</t>
+          <t>082KSW089</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mirror Lake</t>
+          <t>Poplar Creek</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Zinc, Lead, Cobalt</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7316,54 +7316,54 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Au 0.9g/t, Ag 37.7g/t, Cu 6.75%, Pb 0.12%, Zn 2.76%</t>
+          <t>Ag 1190g/t, Au 5.5g/t, Pb 15%, Zn 10%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>In 1979, a chip sample from a mineralized lens assayed 0.9 gram per tonne gold, 37.7 grams per tonne silver, 0.12 per cent lead, 2.76 per cent zinc and 6.75 per cent copper (Property File - D.H.</t>
+          <t>A grab sample of the replacement vein assayed 5.5 grams per tonne gold, 1190 grams per tonne silver, 15 per cent lead and 10 per cent zinc (Minister of Mines Annual Report 1919).</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$445k</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P72" t="n">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>QPX Minerals Inc., Sultan Minerals Inc., SMD Min.</t>
+          <t>Wealth Minerals Ltd., Cream Minerals Ltd., Denny</t>
         </is>
       </c>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T72" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U72" t="n">
         <v>62</v>
       </c>
       <c r="V72" t="n">
-        <v>49.88139</v>
+        <v>50.38917</v>
       </c>
       <c r="W72" t="n">
-        <v>-116.96</v>
+        <v>-117.165</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW089</t>
         </is>
       </c>
     </row>
@@ -7373,21 +7373,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOTHER LODE (L.1497)          </t>
+          <t xml:space="preserve">CURLEW (L.1220)               </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>082KSW089</t>
+          <t>082FSW154</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Poplar Creek</t>
+          <t>Rossland</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Silver, Gold, Lead, Zinc, Copper, Antimony</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7408,58 +7408,62 @@
         <v>0</v>
       </c>
       <c r="J73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>6 t (assay)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Ag 1190g/t, Au 5.5g/t, Pb 15%, Zn 10%</t>
+          <t>Ag 2740g/t, Au 17g/t</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>A grab sample of the replacement vein assayed 5.5 grams per tonne gold, 1190 grams per tonne silver, 15 per cent lead and 10 per cent zinc (Minister of Mines Annual Report 1919).</t>
+          <t>The ore is reported to have given assays from 10 to 17 grams per tonne gold and from 2400 to 2740 grams per tonne silver (Minister of Mines Annual Report 1896, page 31).</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>$445k</t>
+          <t>$436k</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="P73" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Wealth Minerals Ltd., Cream Minerals Ltd., Denny</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
+          <t>Antelope Resources Inc., Kerr Addison Mines, Rossland Mines</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Conditional Registration Reserve (Pipeline) — special process</t>
+        </is>
+      </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T73" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="U73" t="n">
         <v>62</v>
       </c>
       <c r="V73" t="n">
-        <v>50.38917</v>
+        <v>49.05639</v>
       </c>
       <c r="W73" t="n">
-        <v>-117.165</v>
+        <v>-117.80056</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW089</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW154</t>
         </is>
       </c>
     </row>
@@ -7469,30 +7473,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">CURLEW (L.1220)               </t>
+          <t xml:space="preserve">SOUTHEASTER                   </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>082FSW154</t>
+          <t>103G  004</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Rossland</t>
+          <t>Skidegate</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc, Copper, Antimony</t>
+          <t>Gold, Silver, Lead, Copper, Zinc</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7504,44 +7508,40 @@
         <v>0</v>
       </c>
       <c r="J74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>6 t (assay)</t>
+          <t>5 kt (assay)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Ag 2740g/t, Au 17g/t</t>
+          <t>Ag 33.3g/t, Au 76.5g/t, Cu 0.058%, Pb 7.09%, Zn 13.9%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>The ore is reported to have given assays from 10 to 17 grams per tonne gold and from 2400 to 2740 grams per tonne silver (Minister of Mines Annual Report 1896, page 31).</t>
+          <t>Five surface samples over widths of 0.7 metre to 2 metres gave assays ranging from 0.6 to 179.7 grams per tonne gold. An average sample of dump material assayed 76.5 grams per tonne gold, 33.3 grams per tonne silver, 0.058 per cent copper, 7.09 per cent lead, and 13.90 per cent zinc (Assessment Report 9769). A trench sample taken across 3.7 metres of quartz vein and stockwork assayed 4.502 grams per tonne gold (Assessment Report 19941, page 7, Trench 2). Drilling in 1990 encountered 2.7 metres assaying 16.39 grams per tonne gold and 6.27 grams per tonne silver (Assessment Report 20493, page 1, DDH 11).</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>$436k</t>
+          <t>$418k</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="P74" t="n">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Antelope Resources Inc., Kerr Addison Mines, Rossland Mines</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Conditional Registration Reserve (Pipeline) — special process</t>
-        </is>
-      </c>
+          <t>Rayner, G.H., Clear Creek Resources Ltd.</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
         <v>2</v>
       </c>
@@ -7552,14 +7552,14 @@
         <v>62</v>
       </c>
       <c r="V74" t="n">
-        <v>49.05639</v>
+        <v>53.2775</v>
       </c>
       <c r="W74" t="n">
-        <v>-117.80056</v>
+        <v>-131.99056</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW154</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103G++004</t>
         </is>
       </c>
     </row>
@@ -7569,21 +7569,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOUTHEASTER                   </t>
+          <t>BOBMAC 6</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>103G  004</t>
+          <t>092L  179</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Skidegate</t>
+          <t>Warner Bay</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.2</v>
+        <v>9.6</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper, Zinc</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7608,33 +7608,33 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>5 kt (assay)</t>
+          <t>610 t</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Ag 33.3g/t, Au 76.5g/t, Cu 0.058%, Pb 7.09%, Zn 13.9%</t>
+          <t>Au 15.7g/t, Ag 37.2g/t, Pb 1.37%, Zn 0.61%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Five surface samples over widths of 0.7 metre to 2 metres gave assays ranging from 0.6 to 179.7 grams per tonne gold. An average sample of dump material assayed 76.5 grams per tonne gold, 33.3 grams per tonne silver, 0.058 per cent copper, 7.09 per cent lead, and 13.90 per cent zinc (Assessment Report 9769). A trench sample taken across 3.7 metres of quartz vein and stockwork assayed 4.502 grams per tonne gold (Assessment Report 19941, page 7, Trench 2). Drilling in 1990 encountered 2.7 metres assaying 16.39 grams per tonne gold and 6.27 grams per tonne silver (Assessment Report 20493, page 1, DDH 11).</t>
+          <t xml:space="preserve">A sample across 0.9 metre, 1.2 metres from the creek, assayed 21.77 grams per tonne gold and 37.2 grams per tonne silver (1938 Report in Property File). Approximately 23 metres to the northwest, a sample across 0.3 metre measured from the footwall assayed 92.06 grams per tonne gold, 136.9 grams per tonne silver, and 2.5 per cent lead. The 0.6 metre adjacent to the hanging wall assayed 12.44 grams per tonne gold and 2.49 grams per tonne silver. A sample of quartz containing some fragments of wallrock but practically no sulphides assayed 1.87 grams per tonne gold and 49.8 grams per tonne silver (Property File). In 1998, sampling of the main showing (Vein 6) yielded up to 0.247 per cent lead, 0.612 per cent zinc, 13.9 grams per tonne silver and 15.7 grams per tonne gold (sample 28856), while </t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>$418k</t>
+          <t>$417k</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P75" t="n">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Rayner, G.H., Clear Creek Resources Ltd.</t>
+          <t>Solaia Ventures Inc., Pacific Topaz Resources Ltd., Frank Beban Logging Ltd.</t>
         </is>
       </c>
       <c r="R75" t="inlineStr"/>
@@ -7648,14 +7648,14 @@
         <v>62</v>
       </c>
       <c r="V75" t="n">
-        <v>53.2775</v>
+        <v>50.99722</v>
       </c>
       <c r="W75" t="n">
-        <v>-131.99056</v>
+        <v>-127.20944</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103G++004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++179</t>
         </is>
       </c>
     </row>
@@ -7665,30 +7665,30 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BOBMAC 6</t>
+          <t>COLORADO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>092L  179</t>
+          <t>093L  043</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Warner Bay</t>
+          <t>Tatlow</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7704,54 +7704,54 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>610 t</t>
+          <t>269 t</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 15.7g/t, Ag 37.2g/t, Pb 1.37%, Zn 0.61%</t>
+          <t>Ag 2523g/t, Cu 1.20%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">A sample across 0.9 metre, 1.2 metres from the creek, assayed 21.77 grams per tonne gold and 37.2 grams per tonne silver (1938 Report in Property File). Approximately 23 metres to the northwest, a sample across 0.3 metre measured from the footwall assayed 92.06 grams per tonne gold, 136.9 grams per tonne silver, and 2.5 per cent lead. The 0.6 metre adjacent to the hanging wall assayed 12.44 grams per tonne gold and 2.49 grams per tonne silver. A sample of quartz containing some fragments of wallrock but practically no sulphides assayed 1.87 grams per tonne gold and 49.8 grams per tonne silver (Property File). In 1998, sampling of the main showing (Vein 6) yielded up to 0.247 per cent lead, 0.612 per cent zinc, 13.9 grams per tonne silver and 15.7 grams per tonne gold (sample 28856), while </t>
+          <t>In 1914 a sample from the dump of unsorted ore assayed 0.69 gram per tonne gold, 2372.5 grams per tonne silver and 6.5 per cent copper (Minister of Mines Annual Report 1914, page 221). A sample taken in 1985, of malachite-stained dump material assayed 1051.3 grams per tonne silver and 2.32 per cent copper (Property File Rimfire Dujardin, 1985). Several open cuts and a 4.8 metre adit were cut on the Hunter in 1914 exposing high grade lenses, with 23 tonnes from the dump assaying 1.2 per cent copper, 2523 grams per tonne silver and 0.69 gram per tonne gram per tonne gold and a tunnel was driven on the Hannah, with no significant mineralization encountered.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>$417k</t>
+          <t>$410k</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P76" t="n">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Solaia Ventures Inc., Pacific Topaz Resources Ltd., Frank Beban Logging Ltd.</t>
+          <t>Lions Gate Energy Inc., Atna Resources Ltd., Standard Drilling and Engineering Ltd.</t>
         </is>
       </c>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U76" t="n">
         <v>62</v>
       </c>
       <c r="V76" t="n">
-        <v>50.99722</v>
+        <v>54.52944</v>
       </c>
       <c r="W76" t="n">
-        <v>-127.20944</v>
+        <v>-127.19361</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++179</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++043</t>
         </is>
       </c>
     </row>
@@ -7761,30 +7761,30 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>COLORADO</t>
+          <t xml:space="preserve">STAR OF EMORY 3               </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>093L  043</t>
+          <t>092HSW093</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tatlow</t>
+          <t>Trafalgar</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>19.6</v>
+        <v>8.6</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Nickel, Copper, Chromium, Gold, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7800,33 +7800,33 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>269 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Ag 2523g/t, Cu 1.20%</t>
+          <t>Cu 0.28%, Ni 4.69%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>In 1914 a sample from the dump of unsorted ore assayed 0.69 gram per tonne gold, 2372.5 grams per tonne silver and 6.5 per cent copper (Minister of Mines Annual Report 1914, page 221). A sample taken in 1985, of malachite-stained dump material assayed 1051.3 grams per tonne silver and 2.32 per cent copper (Property File Rimfire Dujardin, 1985). Several open cuts and a 4.8 metre adit were cut on the Hunter in 1914 exposing high grade lenses, with 23 tonnes from the dump assaying 1.2 per cent copper, 2523 grams per tonne silver and 0.69 gram per tonne gram per tonne gold and a tunnel was driven on the Hannah, with no significant mineralization encountered.</t>
+          <t>In one hole, mineralization over 2.75 metres yielded 2.2 per cent nickel and 0.58 per cent copper. Another intersection over 0.9 metre yielded 4.69 per cent nickel and 0.28 per cent copper (Assessment Report 5385).</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>$410k</t>
+          <t>$405k</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P77" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Lions Gate Energy Inc., Atna Resources Ltd., Standard Drilling and Engineering Ltd.</t>
+          <t>APAC RESOURCES INC., Pacific Coast Nickel Corp., International Millennium Mining Corp.</t>
         </is>
       </c>
       <c r="R77" t="inlineStr"/>
@@ -7840,14 +7840,14 @@
         <v>62</v>
       </c>
       <c r="V77" t="n">
-        <v>54.52944</v>
+        <v>49.46861</v>
       </c>
       <c r="W77" t="n">
-        <v>-127.19361</v>
+        <v>-121.53917</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++043</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW093</t>
         </is>
       </c>
     </row>
@@ -7857,30 +7857,30 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR OF EMORY 3               </t>
+          <t>STANDARD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>092HSW093</t>
+          <t>082ESW091</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Trafalgar</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>8.6</v>
+        <v>2.7</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Chromium, Gold, Platinum, Palladium</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7896,33 +7896,33 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>2 kt</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Cu 0.28%, Ni 4.69%</t>
+          <t>Au 8.7g/t, Ag 97.4g/t</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>In one hole, mineralization over 2.75 metres yielded 2.2 per cent nickel and 0.58 per cent copper. Another intersection over 0.9 metre yielded 4.69 per cent nickel and 0.28 per cent copper (Assessment Report 5385).</t>
+          <t>Samples taken by Continental Consolidated and Norex in 1961 and 1962 yielded 28.86 grams per tonne gold across 1.06 metres (Assessment Report 12971). The one-metre interval between 68.7 and 69.7 metres yielded 8.43 grams per tonne gold and 97.37 grams per tonne silver (Assessment Report 12971). The 0.80-metre interval between 63.7 and 64.5 metres yielded 10.4 grams per tonne gold (Assessment Report 12971). Sample 51296, taken 50.5 metres from the portal, yielded 8.67 grams per tonne gold and 102.17 grams per tonne silver (Assessment Report 12971). A 0.81-metre interval at 69 metres yielded 5.55 grams per tonne gold and 51.08 grams per tonne silver (Assessment Report 15833).</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>$405k</t>
+          <t>$403k</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P78" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>APAC RESOURCES INC., Pacific Coast Nickel Corp., International Millennium Mining Corp.</t>
+          <t>Cominco Ltd., Kronex Resources Ltd., Vermillion Resources Inc.</t>
         </is>
       </c>
       <c r="R78" t="inlineStr"/>
@@ -7936,14 +7936,14 @@
         <v>62</v>
       </c>
       <c r="V78" t="n">
-        <v>49.46861</v>
+        <v>49.19944</v>
       </c>
       <c r="W78" t="n">
-        <v>-121.53917</v>
+        <v>-119.57694</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW093</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ESW091</t>
         </is>
       </c>
     </row>
@@ -7953,21 +7953,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STANDARD</t>
+          <t>BEAVER CREEK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>082ESW091</t>
+          <t>082FSW266</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Ross Spur</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7992,54 +7992,54 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2 kt</t>
+          <t>55 t</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Au 8.7g/t, Ag 97.4g/t</t>
+          <t>Au 13.0g/t, Ag 130g/t, Cu 0.01%, Zn 0.03%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Samples taken by Continental Consolidated and Norex in 1961 and 1962 yielded 28.86 grams per tonne gold across 1.06 metres (Assessment Report 12971). The one-metre interval between 68.7 and 69.7 metres yielded 8.43 grams per tonne gold and 97.37 grams per tonne silver (Assessment Report 12971). The 0.80-metre interval between 63.7 and 64.5 metres yielded 10.4 grams per tonne gold (Assessment Report 12971). Sample 51296, taken 50.5 metres from the portal, yielded 8.67 grams per tonne gold and 102.17 grams per tonne silver (Assessment Report 12971). A 0.81-metre interval at 69 metres yielded 5.55 grams per tonne gold and 51.08 grams per tonne silver (Assessment Report 15833).</t>
+          <t>One sample that was reported as a 3-metre grab sample assayed 130 grams per tonne silver, 13 grams per tonne gold, 0.01 per cent copper, 0.27 lead and 0.03 per cent zinc (Assessment Report 12762).</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>$403k</t>
+          <t>$380k</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P79" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Cominco Ltd., Kronex Resources Ltd., Vermillion Resources Inc.</t>
+          <t>International Corona Corp., Rio Algom Exploration Inc., Lacana Ex.</t>
         </is>
       </c>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T79" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U79" t="n">
         <v>62</v>
       </c>
       <c r="V79" t="n">
-        <v>49.19944</v>
+        <v>49.20583</v>
       </c>
       <c r="W79" t="n">
-        <v>-119.57694</v>
+        <v>-117.45972</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ESW091</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW266</t>
         </is>
       </c>
     </row>
@@ -8049,21 +8049,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BEAVER CREEK</t>
+          <t xml:space="preserve">COLUMBIA-KOOTENAY             </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>082FSW266</t>
+          <t>082FSW151</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ross Spur</t>
+          <t>Rossland</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Copper, Nickel, Bismuth</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8088,54 +8088,54 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>55 t</t>
+          <t>9 kt</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 13.0g/t, Ag 130g/t, Cu 0.01%, Zn 0.03%</t>
+          <t>Au 13.0g/t</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>One sample that was reported as a 3-metre grab sample assayed 130 grams per tonne silver, 13 grams per tonne gold, 0.01 per cent copper, 0.27 lead and 0.03 per cent zinc (Assessment Report 12762).</t>
+          <t>In 1984, a dump sample (83172) of massive sulphides in a siliceous matrix assayed 6.1 grams per tonne gold, 4.1 grams per tonne silver and 0.44 per cent copper (Assessment Report 14236). In 1986, a chip sample (83138C) of massive pyrrhotite in augite porphyry assayed 60.9 grams per tonne gold over 0.25 metre, whereas a 2.0-metre chip sample (83141C) of massive pyrite-pyrrhotite with quartz in a granodiorite assayed 9.4 grams per tonne gold (Assessment Report 15432). Prior to 1898, approximately 4000 metres of underground development work had been completed with unverified reports indicating a total of approximately 11 617 tonnes averaging 13.0 grams per tonne gold being produced (Assessment Report 15432).</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>$380k</t>
+          <t>$374k</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="P80" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>International Corona Corp., Rio Algom Exploration Inc., Lacana Ex.</t>
+          <t>Gallant Gold Mines Limited, Currie Rose Resources Inc, Antelope Resources Inc.</t>
         </is>
       </c>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U80" t="n">
         <v>62</v>
       </c>
       <c r="V80" t="n">
-        <v>49.20583</v>
+        <v>49.08917</v>
       </c>
       <c r="W80" t="n">
-        <v>-117.45972</v>
+        <v>-117.78389</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW266</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW151</t>
         </is>
       </c>
     </row>
@@ -8145,30 +8145,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLUMBIA-KOOTENAY             </t>
+          <t>ARMSTRONG (L.5483)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>082FSW151</t>
+          <t>082FSW267</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Rossland</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gold, Copper, Nickel, Bismuth</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8184,54 +8184,54 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>9 kt</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Au 13.0g/t</t>
+          <t>Au 0.7g/t, Ag 459g/t, Pb 3.70%, Zn 0.50%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>In 1984, a dump sample (83172) of massive sulphides in a siliceous matrix assayed 6.1 grams per tonne gold, 4.1 grams per tonne silver and 0.44 per cent copper (Assessment Report 14236). In 1986, a chip sample (83138C) of massive pyrrhotite in augite porphyry assayed 60.9 grams per tonne gold over 0.25 metre, whereas a 2.0-metre chip sample (83141C) of massive pyrite-pyrrhotite with quartz in a granodiorite assayed 9.4 grams per tonne gold (Assessment Report 15432). Prior to 1898, approximately 4000 metres of underground development work had been completed with unverified reports indicating a total of approximately 11 617 tonnes averaging 13.0 grams per tonne gold being produced (Assessment Report 15432).</t>
+          <t>A 30-centimetre sample assayed 0.69 gram per tonne gold, 459.43 grams per tonne silver, 3.7 per cent lead and 0.5 per cent zinc (Minister of Mines Annual Report, 1928, page 338). In 1928, a 30-centimetre sample assayed 0.69 gram per tonne gold, 459.43 grams per tonne silver, 3.7 per cent lead and 0.5 per cent zinc (Minister of Mines Annual Report, 1928, page 338).</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>$374k</t>
+          <t>$336k</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P81" t="n">
         <v>2020</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Gallant Gold Mines Limited, Currie Rose Resources Inc, Antelope Resources Inc.</t>
+          <t>International Corona Corp., Kootenay Gold Corp, Kootenay Gold Inc.</t>
         </is>
       </c>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T81" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="U81" t="n">
         <v>62</v>
       </c>
       <c r="V81" t="n">
-        <v>49.08917</v>
+        <v>49.19389</v>
       </c>
       <c r="W81" t="n">
-        <v>-117.78389</v>
+        <v>-117.36778</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW151</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW267</t>
         </is>
       </c>
     </row>
@@ -8241,21 +8241,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ARMSTRONG (L.5483)</t>
+          <t>INGENIKA MINE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>082FSW267</t>
+          <t>094C  002</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Ingenika Mine</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -8280,54 +8280,54 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>23 kt</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Ag 459g/t, Pb 3.70%, Zn 0.50%</t>
+          <t>Ag 241g/t, Pb 15.00%, Zn 7.50%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>A 30-centimetre sample assayed 0.69 gram per tonne gold, 459.43 grams per tonne silver, 3.7 per cent lead and 0.5 per cent zinc (Minister of Mines Annual Report, 1928, page 338). In 1928, a 30-centimetre sample assayed 0.69 gram per tonne gold, 459.43 grams per tonne silver, 3.7 per cent lead and 0.5 per cent zinc (Minister of Mines Annual Report, 1928, page 338).</t>
+          <t>One intersection from the Cominco 1957 diamond drill program yielded 15 per cent lead, 7.5 per cent zinc and 240.8 grams per tonne silver over 2.4 metres (Property File - E.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>$336k</t>
+          <t>$325k</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="P82" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>International Corona Corp., Kootenay Gold Corp, Kootenay Gold Inc.</t>
+          <t>Selkirk Metals Holdings Corp., Cross Lake Minerals Ltd, International Impala Resources; Intl. Impala Res.</t>
         </is>
       </c>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T82" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="U82" t="n">
         <v>62</v>
       </c>
       <c r="V82" t="n">
-        <v>49.19389</v>
+        <v>56.69194</v>
       </c>
       <c r="W82" t="n">
-        <v>-117.36778</v>
+        <v>-125.175</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW267</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094C++002</t>
         </is>
       </c>
     </row>
@@ -8337,35 +8337,35 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INGENIKA MINE</t>
+          <t xml:space="preserve">SPITZEE (L.2520)              </t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>094C  002</t>
+          <t>082FSW121</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ingenika Mine</t>
+          <t>Rossland</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Silver, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -8376,54 +8376,54 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>23 kt</t>
+          <t>6 kt (assay)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Ag 241g/t, Pb 15.00%, Zn 7.50%</t>
+          <t>Ag 17.14g/t, Au 8.57g/t, Cu 0.7%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>One intersection from the Cominco 1957 diamond drill program yielded 15 per cent lead, 7.5 per cent zinc and 240.8 grams per tonne silver over 2.4 metres (Property File - E.</t>
+          <t>In 1906, the average analysis of the ore assayed 8.57 grams per tonne gold, 17.14 grams per tonne silver, and 0.7 per cent copper (Geological Survey of Canada Memoir 77, page 141).</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>$325k</t>
+          <t>$318k</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P83" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Selkirk Metals Holdings Corp., Cross Lake Minerals Ltd, International Impala Resources; Intl. Impala Res.</t>
+          <t>Currie Rose Resources Inc, Pacific Vangold Mines Ltd., Bragg</t>
         </is>
       </c>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T83" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U83" t="n">
         <v>62</v>
       </c>
       <c r="V83" t="n">
-        <v>56.69194</v>
+        <v>49.07417</v>
       </c>
       <c r="W83" t="n">
-        <v>-125.175</v>
+        <v>-117.80333</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW121</t>
         </is>
       </c>
     </row>
@@ -8433,30 +8433,30 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPITZEE (L.2520)              </t>
+          <t>DIBBLE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>082FSW121</t>
+          <t>082GNW003</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Rossland</t>
+          <t>Fenwick</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.7</v>
+        <v>13.8</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Tungsten</t>
+          <t>Silver, Copper, Gold</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8472,54 +8472,54 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>6 kt (assay)</t>
+          <t>4 t</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Ag 17.14g/t, Au 8.57g/t, Cu 0.7%</t>
+          <t>Au 127g/t, Ag 3822g/t, Cu 4.10%, Pb 0.01%, Zn 0.15%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>In 1906, the average analysis of the ore assayed 8.57 grams per tonne gold, 17.14 grams per tonne silver, and 0.7 per cent copper (Geological Survey of Canada Memoir 77, page 141).</t>
+          <t>Highest assays from these narrow veins were 4.1 per cent copper, 3822.2 grams per tonne silver, 0.01 per cent lead, 0.15 per cent zinc and 126.8 grams per tonne gold (Assessment Report 18309).</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>$318k</t>
+          <t>$316k</t>
         </is>
       </c>
       <c r="O84" t="n">
         <v>11</v>
       </c>
       <c r="P84" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Currie Rose Resources Inc, Pacific Vangold Mines Ltd., Bragg</t>
+          <t>Big B Resources, F &amp; B Silver, Babcock</t>
         </is>
       </c>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T84" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U84" t="n">
         <v>62</v>
       </c>
       <c r="V84" t="n">
-        <v>49.07417</v>
+        <v>49.59722</v>
       </c>
       <c r="W84" t="n">
-        <v>-117.80333</v>
+        <v>-115.43861</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW121</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082GNW003</t>
         </is>
       </c>
     </row>
@@ -8529,21 +8529,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DIBBLE</t>
+          <t>JENNY LONG (L.718)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>082GNW003</t>
+          <t>092ISE031</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fenwick</t>
+          <t>Stump Lake</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>13.8</v>
+        <v>8.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold</t>
+          <t>Silver, Lead, Zinc, Gold, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8568,54 +8568,54 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>4 t</t>
+          <t>635 t</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Au 127g/t, Ag 3822g/t, Cu 4.10%, Pb 0.01%, Zn 0.15%</t>
+          <t>Au 18.4g/t, Ag 294g/t, Cu 0.30%, Pb 1.00%, Sb 0.20%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Highest assays from these narrow veins were 4.1 per cent copper, 3822.2 grams per tonne silver, 0.01 per cent lead, 0.15 per cent zinc and 126.8 grams per tonne gold (Assessment Report 18309).</t>
+          <t>A sample of mineralized quartz vein from the Jenny Long system assayed 18.4 grams per tonne gold, 294.1 grams per tonne silver, 0.3 per cent copper, 1.0 per cent lead and 0.2 per cent antimony (Assessment Report 24923;</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>$316k</t>
+          <t>$315k</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P85" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Big B Resources, F &amp; B Silver, Babcock</t>
+          <t>Celebrity Energy Corporation, Juniper Mines, Graham</t>
         </is>
       </c>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U85" t="n">
         <v>62</v>
       </c>
       <c r="V85" t="n">
-        <v>49.59722</v>
+        <v>50.31639</v>
       </c>
       <c r="W85" t="n">
-        <v>-115.43861</v>
+        <v>-120.36472</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082GNW003</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092ISE031</t>
         </is>
       </c>
     </row>
@@ -8625,21 +8625,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JENNY LONG (L.718)</t>
+          <t xml:space="preserve">VICTORY                       </t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>092ISE031</t>
+          <t>093L  093</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Stump Lake</t>
+          <t>Lake Kathlyn</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper, Tungsten</t>
+          <t>Silver, Lead, Zinc, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8664,33 +8664,33 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>635 t</t>
+          <t>4 kt (assay)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Au 18.4g/t, Ag 294g/t, Cu 0.30%, Pb 1.00%, Sb 0.20%</t>
+          <t>Ag 358.3g/t, Au 15.1g/t, Pb 6.4%, Zn 1.1%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>A sample of mineralized quartz vein from the Jenny Long system assayed 18.4 grams per tonne gold, 294.1 grams per tonne silver, 0.3 per cent copper, 1.0 per cent lead and 0.2 per cent antimony (Assessment Report 24923;</t>
+          <t>A 13 centimetre channel sample across the main zone assayed 14.4 grams per tonne gold, 501.9 grams per tonne silver, 23.45 per cent lead and 13.36 per cent zinc (Geological Survey of Canada Bulletin 1). A 56 centi- metre channel sample assayed 1.5 grams per tonne gold, 83.7 grams per tonne silver, 2.78 per cent lead, and 2.11 per cent zinc. The sample assayed 15.1 grams per tonne gold, 358.3 grams per tonne silver, 6.4 per cent lead and 1.1 per cent zinc (Geological Survey of Canada Bulletin 1, page 53). In 1987, assays from the underground sampling ranged from 3.4 to 34.28 grams per tonne silver and 0.2 to 1.5 per cent lead and zinc.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>$315k</t>
+          <t>$310k</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="P86" t="n">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Celebrity Energy Corporation, Juniper Mines, Graham</t>
+          <t>Geostar Mining Corp., Bishop Resources Development Ltd.; Duthie Holdings, Blue Pearl Mining Inc.</t>
         </is>
       </c>
       <c r="R86" t="inlineStr"/>
@@ -8704,14 +8704,14 @@
         <v>62</v>
       </c>
       <c r="V86" t="n">
-        <v>50.31639</v>
+        <v>54.78611</v>
       </c>
       <c r="W86" t="n">
-        <v>-120.36472</v>
+        <v>-127.35861</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092ISE031</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++093</t>
         </is>
       </c>
     </row>
@@ -8721,30 +8721,30 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORY                       </t>
+          <t xml:space="preserve">PROMESTORA (L.3788)           </t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>093L  093</t>
+          <t>082KSW052</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Lake Kathlyn</t>
+          <t>Carrolls Landing</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>9.6</v>
+        <v>7.3</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Arsenic</t>
+          <t>Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8760,54 +8760,54 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>4 kt (assay)</t>
+          <t>8 t</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Ag 358.3g/t, Au 15.1g/t, Pb 6.4%, Zn 1.1%</t>
+          <t>Au 116g/t, Ag 212g/t</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>A 13 centimetre channel sample across the main zone assayed 14.4 grams per tonne gold, 501.9 grams per tonne silver, 23.45 per cent lead and 13.36 per cent zinc (Geological Survey of Canada Bulletin 1). A 56 centi- metre channel sample assayed 1.5 grams per tonne gold, 83.7 grams per tonne silver, 2.78 per cent lead, and 2.11 per cent zinc. The sample assayed 15.1 grams per tonne gold, 358.3 grams per tonne silver, 6.4 per cent lead and 1.1 per cent zinc (Geological Survey of Canada Bulletin 1, page 53). In 1987, assays from the underground sampling ranged from 3.4 to 34.28 grams per tonne silver and 0.2 to 1.5 per cent lead and zinc.</t>
+          <t>In 1958, a 15 centimetre sample of a heavily mineralized quartz vein from above the portal of the tunnel assayed 302 grams per tonne gold and 311 grams per tonne silver, whereas a 75 centimetre sample from a trench, located just west of the tunnel, assayed 116 grams per tonne gold and 113 grams per tonne silver (Property File - F.C. In 1949, a sample assayed 13.0 grams per tonne gold (Property File - Promistora Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>$310k</t>
+          <t>$288k</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P87" t="n">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>Geostar Mining Corp., Bishop Resources Development Ltd.; Duthie Holdings, Blue Pearl Mining Inc.</t>
+          <t>Falconbridge, Meadow Mountain Res., Nakusp Res.</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T87" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="U87" t="n">
         <v>62</v>
       </c>
       <c r="V87" t="n">
-        <v>54.78611</v>
+        <v>50.06278</v>
       </c>
       <c r="W87" t="n">
-        <v>-127.35861</v>
+        <v>-117.79889</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++093</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW052</t>
         </is>
       </c>
     </row>
@@ -8817,30 +8817,30 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROMESTORA (L.3788)           </t>
+          <t xml:space="preserve">BECA                          </t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>082KSW052</t>
+          <t>082M  055</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Carrolls Landing</t>
+          <t>Adams Lake</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>7.3</v>
+        <v>11.2</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc</t>
+          <t>Silver, Lead, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8856,17 +8856,17 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Au 116g/t, Ag 212g/t</t>
+          <t>Ag 342.8g/t, Au 16.5g/t, Cu 0.8%, Pb 1.9%, Zn 1.3%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>In 1958, a 15 centimetre sample of a heavily mineralized quartz vein from above the portal of the tunnel assayed 302 grams per tonne gold and 311 grams per tonne silver, whereas a 75 centimetre sample from a trench, located just west of the tunnel, assayed 116 grams per tonne gold and 113 grams per tonne silver (Property File - F.C. In 1949, a sample assayed 13.0 grams per tonne gold (Property File - Promistora Gold Mines Ltd.</t>
+          <t>Three typical samples gave average assay values of 16.5 grams per tonne gold, 342.8 grams per tonne silver, 1.9 per cent lead, 1.3 per cent zinc and 0.8 per cent copper (Assessment Report 6680). A minor showing 400 metres north of this showing consists of a 10 centimetre pyrite-galena bed assaying 2.75 per cent lead with only trace copper, zinc and silver (082M  111).</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -8875,35 +8875,35 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P88" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Falconbridge, Meadow Mountain Res., Nakusp Res.</t>
+          <t>Otterburn Resources Corp., Westmin Resources Ltd., Yale Resources Ltd.</t>
         </is>
       </c>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T88" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U88" t="n">
         <v>62</v>
       </c>
       <c r="V88" t="n">
-        <v>50.06278</v>
+        <v>51.04722</v>
       </c>
       <c r="W88" t="n">
-        <v>-117.79889</v>
+        <v>-119.71778</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082M++055</t>
         </is>
       </c>
     </row>
@@ -8913,30 +8913,30 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">BECA                          </t>
+          <t>BLUE HAWK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>082M  055</t>
+          <t>082ENW002</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Adams Lake</t>
+          <t>Wilson Landing</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>11.2</v>
+        <v>2</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Zinc, Gold</t>
+          <t>Gold, Silver, Lead, Copper, Zinc</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8952,54 +8952,54 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>4 t</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Ag 342.8g/t, Au 16.5g/t, Cu 0.8%, Pb 1.9%, Zn 1.3%</t>
+          <t>Au 11.4g/t</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Three typical samples gave average assay values of 16.5 grams per tonne gold, 342.8 grams per tonne silver, 1.9 per cent lead, 1.3 per cent zinc and 0.8 per cent copper (Assessment Report 6680). A minor showing 400 metres north of this showing consists of a 10 centimetre pyrite-galena bed assaying 2.75 per cent lead with only trace copper, zinc and silver (082M  111).</t>
+          <t>The best gold assays were associated with the north and northwest shear systems, and three areas were identified that produced gold assays greater than 34 grams per tonne (Property File - Dasler P.G., 1989). The average assay of 10 channel samples from Trench #1, all of which assayed greater than 3.4 grams per tonne gold, was 19.39 grams per tonne gold and 67.98 grams per tonne silver (Property File - Dasler P.G., 1989). results were poor, yielding a maximum of 0.565 gram per tonne gold over 1.00 metre in hole K93-02 (Assessment Report 23811). In 1967, Sampling of the D vein exposed in a short drift of the shaft is reported to have yielded 34.2 grams per tonne gold and 136.8 grams per tonne silver over 0.72 metre, whereas a chip sample from the same vein collected the previous year yielded</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>$288k</t>
+          <t>$277k</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P89" t="n">
         <v>2025</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Otterburn Resources Corp., Westmin Resources Ltd., Yale Resources Ltd.</t>
+          <t>RM Explorations Inc., Juan De Fuca Resources Ltd., Parkwood Resources</t>
         </is>
       </c>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T89" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U89" t="n">
         <v>62</v>
       </c>
       <c r="V89" t="n">
-        <v>51.04722</v>
+        <v>49.98389</v>
       </c>
       <c r="W89" t="n">
-        <v>-119.71778</v>
+        <v>-119.51944</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082M++055</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ENW002</t>
         </is>
       </c>
     </row>
@@ -9009,30 +9009,30 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BLUE HAWK</t>
+          <t>BLACK DIAMOND</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>082ENW002</t>
+          <t>082KSE049</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wilson Landing</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper, Zinc</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9048,54 +9048,54 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>4 t</t>
+          <t>43 t</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Au 11.4g/t</t>
+          <t>Ag 111g/t, Pb 4.34%, Zn 5.13%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>The best gold assays were associated with the north and northwest shear systems, and three areas were identified that produced gold assays greater than 34 grams per tonne (Property File - Dasler P.G., 1989). The average assay of 10 channel samples from Trench #1, all of which assayed greater than 3.4 grams per tonne gold, was 19.39 grams per tonne gold and 67.98 grams per tonne silver (Property File - Dasler P.G., 1989). results were poor, yielding a maximum of 0.565 gram per tonne gold over 1.00 metre in hole K93-02 (Assessment Report 23811). In 1967, Sampling of the D vein exposed in a short drift of the shaft is reported to have yielded 34.2 grams per tonne gold and 136.8 grams per tonne silver over 0.72 metre, whereas a chip sample from the same vein collected the previous year yielded</t>
+          <t>Results included drillhole BD12-01 intersecting 2.83 metres grading 4.34 per cent lead, 5.13 per cent zinc and 111.1 grams per tonne silver from 170.43 to 173.26 metres, with true thickness calculated to be 1.58 metres. The entire mineralized interval returned 3.98 per cent combined lead-zinc and 49.3 grams per tonne silver over 17.37 metres, with a true thickness of 9.8 metres (V STOCKWATCH, October 23, 2012).</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>$277k</t>
+          <t>$256k</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P90" t="n">
         <v>2025</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>RM Explorations Inc., Juan De Fuca Resources Ltd., Parkwood Resources</t>
+          <t>Eagle Plains Resources Ltd., Termuende, Tim J.; Walker</t>
         </is>
       </c>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T90" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="U90" t="n">
         <v>62</v>
       </c>
       <c r="V90" t="n">
-        <v>49.98389</v>
+        <v>50.37028</v>
       </c>
       <c r="W90" t="n">
-        <v>-119.51944</v>
+        <v>-116.39306</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ENW002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE049</t>
         </is>
       </c>
     </row>
@@ -9105,30 +9105,30 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BLACK DIAMOND</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>082KSE049</t>
+          <t>082FNW129</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Zinc, Lead, Silver, Gold, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9144,54 +9144,54 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>43 t</t>
+          <t>14 kt</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Ag 111g/t, Pb 4.34%, Zn 5.13%</t>
+          <t>Au 0.0g/t, Ag 320g/t, Cu 0.06%, Pb 3.91%, Zn 10.71%, Mo 0.32%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Results included drillhole BD12-01 intersecting 2.83 metres grading 4.34 per cent lead, 5.13 per cent zinc and 111.1 grams per tonne silver from 170.43 to 173.26 metres, with true thickness calculated to be 1.58 metres. The entire mineralized interval returned 3.98 per cent combined lead-zinc and 49.3 grams per tonne silver over 17.37 metres, with a true thickness of 9.8 metres (V STOCKWATCH, October 23, 2012).</t>
+          <t>A sample from the dump taken in 1987, assayed 320 grams per tonne silver, 0.03 grams per tonne gold, 0.0563 per cent copper, 7.8 per cent lead and 21.4 per cent zinc (Open File 1988-11). A sample taken 500 metres to the southwest assayed 0.32 per cent molybdenum, 0.024 per cent lead and 0.029 per cent zinc (Open File 1988-11).</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>$256k</t>
+          <t>$152k</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P91" t="n">
-        <v>2025</v>
+        <v>1991</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Termuende, Tim J.; Walker</t>
+          <t>Noranda Mining and Exploration Inc., Kokanee Explorations Ltd., Chapleau Resources Ltd.</t>
         </is>
       </c>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T91" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="U91" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V91" t="n">
-        <v>50.37028</v>
+        <v>49.72611</v>
       </c>
       <c r="W91" t="n">
-        <v>-116.39306</v>
+        <v>-117.41556</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE049</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW129</t>
         </is>
       </c>
     </row>
@@ -9201,30 +9201,30 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>SUSIE (L.1917)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>093L  063</t>
+          <t>082ESW090</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tatlow</t>
+          <t>Fairview</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>30.7</v>
+        <v>4.8</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Silver, Gold, Lead, Zinc, Copper, Silica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9240,33 +9240,33 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>750 kt</t>
+          <t>18 kt</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Ag 34.3g/t, Cu 1.50%</t>
+          <t>Au 21.1g/t, Ag 93.9g/t</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>In 1967, Norcan Mines Limited outlined an inferred reserve of 750,000 tonnes grading 34.3 grams per tonne silver and 1.50 per cent copper to a depth of 75 metres on the Santa Maria zone (Property File Cyprus Anvil C.J.</t>
+          <t>Surface sample 58955, the highest of all surface samples, yielded 9.01 grams per tonne gold, 185.83 grams per tonne silver and 0.48 per cent lead over 1.20 metre true thickness. From the upper levels, Sample 63094 yielded 21.12 grams per tonne gold, 93.94 grams per tonne silver and 0.1 per cent lead over a true thickness of 0.70 metre. Sample 57596, from the intermediate levels, yielded 18.31 grams per tonne gold and 217.37 grams per tonne silver over a true thickness of 1.00 metre. From the lower levels, Sample 57661 yielded 7.71 grams per tonne gold and 164.57 grams per tonne silver over a true thickness of 0.95 metre (Assessment Report 16779).</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>$332k</t>
+          <t>$151k</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P92" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Starr Peak Exploration Ltd., Lions Gate Energy Inc., Bearclaw Capital Corporation</t>
+          <t>Gila Bend Resources, British Newfoundland, Dyck</t>
         </is>
       </c>
       <c r="R92" t="inlineStr"/>
@@ -9280,14 +9280,14 @@
         <v>61</v>
       </c>
       <c r="V92" t="n">
-        <v>54.46667</v>
+        <v>49.21806</v>
       </c>
       <c r="W92" t="n">
-        <v>-127.37083</v>
+        <v>-119.59778</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++063</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ESW090</t>
         </is>
       </c>
     </row>
@@ -9297,30 +9297,30 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t xml:space="preserve">LUCKY JIM (L.723)             </t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>082FNW129</t>
+          <t>092K  015</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Silver, Gold, Copper, Molybdenum</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9336,54 +9336,54 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>14 kt</t>
+          <t>13 kt (indicated)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Au 0.0g/t, Ag 320g/t, Cu 0.06%, Pb 3.91%, Zn 10.71%, Mo 0.32%</t>
+          <t>Ag 17.14g/t, Au 10.97g/t, Cu 2%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>A sample from the dump taken in 1987, assayed 320 grams per tonne silver, 0.03 grams per tonne gold, 0.0563 per cent copper, 7.8 per cent lead and 21.4 per cent zinc (Open File 1988-11). A sample taken 500 metres to the southwest assayed 0.32 per cent molybdenum, 0.024 per cent lead and 0.029 per cent zinc (Open File 1988-11).</t>
+          <t>A 0.5 metre sample was taken near the top of the shaft and assayed 8.23 grams per tonne gold and 4.13 per cent copper (Geological Survey of Canada Summary Report 1913).</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>$152k</t>
+          <t>$108k</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P93" t="n">
-        <v>1991</v>
+        <v>2024</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Noranda Mining and Exploration Inc., Kokanee Explorations Ltd., Chapleau Resources Ltd.</t>
+          <t>Kikauka, Andris (FMC # 114051), Campbell</t>
         </is>
       </c>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U93" t="n">
         <v>61</v>
       </c>
       <c r="V93" t="n">
-        <v>49.72611</v>
+        <v>50.20528</v>
       </c>
       <c r="W93" t="n">
-        <v>-117.41556</v>
+        <v>-125.28</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW129</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++015</t>
         </is>
       </c>
     </row>
@@ -9393,30 +9393,30 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SUSIE (L.1917)</t>
+          <t xml:space="preserve">FRENCH                        </t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>082ESW090</t>
+          <t>092HSE059</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fairview</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc, Copper, Silica</t>
+          <t>Gold, Silver, Copper, Molybdenum, Tungsten</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9432,54 +9432,54 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>18 kt</t>
+          <t>78 kt (inferred)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Au 21.1g/t, Ag 93.9g/t</t>
+          <t>Ag 103g/t, Au 5.1g/t, Cu 2%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Surface sample 58955, the highest of all surface samples, yielded 9.01 grams per tonne gold, 185.83 grams per tonne silver and 0.48 per cent lead over 1.20 metre true thickness. From the upper levels, Sample 63094 yielded 21.12 grams per tonne gold, 93.94 grams per tonne silver and 0.1 per cent lead over a true thickness of 0.70 metre. Sample 57596, from the intermediate levels, yielded 18.31 grams per tonne gold and 217.37 grams per tonne silver over a true thickness of 1.00 metre. From the lower levels, Sample 57661 yielded 7.71 grams per tonne gold and 164.57 grams per tonne silver over a true thickness of 0.95 metre (Assessment Report 16779).</t>
+          <t>A chip sample taken over 0.91 metre assayed 1179.2 grams per tonne gold (Vancouver Stockwatch July 11, 1989). A total of 77,608 tonnes of ore averaging 20.66 grams per tonne gold was mined from three levels of underground workings over an elevation of 41 metres by Kelowna Mines Hedley Ltd.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>$151k</t>
+          <t>$93k</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="P94" t="n">
-        <v>2025</v>
+        <v>1986</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Gila Bend Resources, British Newfoundland, Dyck</t>
+          <t>Avenue Resources Inc., Placer Development Limited, Zurich Energy</t>
         </is>
       </c>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T94" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U94" t="n">
         <v>61</v>
       </c>
       <c r="V94" t="n">
-        <v>49.21806</v>
+        <v>49.32583</v>
       </c>
       <c r="W94" t="n">
-        <v>-119.59778</v>
+        <v>-120.02389</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ESW090</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE059</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCKY JIM (L.723)             </t>
+          <t xml:space="preserve">QUADRA COPPER                 </t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>092K  015</t>
+          <t>092K  060</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9503,16 +9503,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9528,54 +9528,54 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>13 kt (indicated)</t>
+          <t>83 kt (indicated)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ag 17.14g/t, Au 10.97g/t, Cu 2%</t>
+          <t>Ag 13.7g/t, Cu 2.44%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>A 0.5 metre sample was taken near the top of the shaft and assayed 8.23 grams per tonne gold and 4.13 per cent copper (Geological Survey of Canada Summary Report 1913).</t>
+          <t>Drill indicated reserves in West zone are 83,217 tonnes grading 13.7 grams per tonne silver and 4.1 per cent copper. Drill indicated reserves in the East zone are 68,114 tonnes grading 2.44 per cent copper and 13.7 grams per tonne silver (Statement of Material Facts July 24, 1972 - Univex Mining Corp.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>$108k</t>
+          <t>$83k</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P95" t="n">
         <v>2024</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Kikauka, Andris (FMC # 114051), Campbell</t>
+          <t>Hillside Energy Corporation, 543445 BC Ltd., Kikauka</t>
         </is>
       </c>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T95" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="U95" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V95" t="n">
-        <v>50.20528</v>
+        <v>50.20694</v>
       </c>
       <c r="W95" t="n">
-        <v>-125.28</v>
+        <v>-125.31028</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++060</t>
         </is>
       </c>
     </row>
@@ -9585,21 +9585,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRENCH                        </t>
+          <t xml:space="preserve">CENTRAL ZEBALLOS              </t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>092HSE059</t>
+          <t>092L  212</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Zeballos</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Molybdenum, Tungsten</t>
+          <t>Gold, Silver, Lead, Copper, Zinc</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9624,54 +9624,54 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>78 kt (inferred)</t>
+          <t>8 kt</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Ag 103g/t, Au 5.1g/t, Cu 2%</t>
+          <t>Au 12.0g/t</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>A chip sample taken over 0.91 metre assayed 1179.2 grams per tonne gold (Vancouver Stockwatch July 11, 1989). A total of 77,608 tonnes of ore averaging 20.66 grams per tonne gold was mined from three levels of underground workings over an elevation of 41 metres by Kelowna Mines Hedley Ltd.</t>
+          <t>In 1983, a sample (CA-001-83) across a 24-centimetre-wide mineralized vein assayed 12.1 grams per tonne gold, 4.0 grams per tonne silver and 0.200 per cent arsenic (Assessment Report 12077). 6 drift assayed 131.9 grams per tonne gold (Assessment Report 18556). In 1989, diamond drilling yielded intercepts of 17.7 grams per tonne gold over 0.22 metre in hole CZ-9-89-20 from the main vein on the No. 9 level and west of the raise yielding 25.6 grams per tonne gold over 0.23 metres and hole CZ-9-89-19 intersected a new vein structure, located 111.6 metres south of the main vein on the No. Possible reserves are 43 631 tonnes grading 12 grams per tonne gold and are estimates based on results from old mine data as supported by recent underground sampling and diamond drilling.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>$93k</t>
+          <t>$248k</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P96" t="n">
-        <v>1986</v>
+        <v>2021</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Avenue Resources Inc., Placer Development Limited, Zurich Energy</t>
+          <t>Canalaska Resources, Canalaska Ventures Ltd., Impact Res.</t>
         </is>
       </c>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T96" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U96" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="V96" t="n">
-        <v>49.32583</v>
+        <v>50.03583</v>
       </c>
       <c r="W96" t="n">
-        <v>-120.02389</v>
+        <v>-126.78333</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE059</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++212</t>
         </is>
       </c>
     </row>
@@ -9681,30 +9681,30 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUADRA COPPER                 </t>
+          <t xml:space="preserve">LUCKY SEVEN                   </t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>092K  060</t>
+          <t>103I  099</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Thornhill</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>7.3</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9720,54 +9720,54 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>83 kt (indicated)</t>
+          <t>91 t (assay)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Ag 13.7g/t, Cu 2.44%</t>
+          <t>Ag 38.3g/t, Au 7.16g/t, Cu 0.015%, Pb 0.246%, Zn 0.03%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Drill indicated reserves in West zone are 83,217 tonnes grading 13.7 grams per tonne silver and 4.1 per cent copper. Drill indicated reserves in the East zone are 68,114 tonnes grading 2.44 per cent copper and 13.7 grams per tonne silver (Statement of Material Facts July 24, 1972 - Univex Mining Corp.</t>
+          <t>Sample TT-9, from a quartz vein with galena, pyrite and chalcopyrite near the old adits assayed 7.16 grams per tonne gold, 38.3 grams per tonne silver, 0.246 per cent lead, 0.03 per cent zinc and 0.015 per cent copper. Another sample taken from the dump pile at an old open cut assayed 0.695 grams per tonne gold, 99.5 grams per tonne silver, 2.533 per cent lead, 0.035 per cent zinc and 0.161 per cent copper (Di Spirito, 1986). About 460 metres to the southwest of the old workings, a sample from a 4 metre wide quartz vein assayed 6.7 grams per tonne gold, 1049 grams epr tonne silver, 0.094 per cent lead, 0.032 per cent zinc, 0.024 per cent copper and 0.0012 per cent molybdenite (Assessment Report 13140).</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>$83k</t>
+          <t>$218k</t>
         </is>
       </c>
       <c r="O97" t="n">
         <v>6</v>
       </c>
       <c r="P97" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Hillside Energy Corporation, 543445 BC Ltd., Kikauka</t>
+          <t>Boga, Iqbal; Thorne Exploration Inc., Castello Resources</t>
         </is>
       </c>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T97" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="U97" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V97" t="n">
-        <v>50.20694</v>
+        <v>54.4775</v>
       </c>
       <c r="W97" t="n">
-        <v>-125.31028</v>
+        <v>-128.44611</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103I++099</t>
         </is>
       </c>
     </row>
@@ -9777,21 +9777,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHAPLEAU (L.4963)             </t>
+          <t xml:space="preserve">TRUE BLUE                     </t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>082FNW130</t>
+          <t>082LSE035</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Cherryville</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Silver, Zinc, Gold, Lead, Copper, Antimony</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9816,33 +9816,33 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>505 kt (indicated)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Au 8.1g/t, Ag 194g/t</t>
+          <t>Au 0.7g/t, Ag 269g/t, Cu 0.14%, Pb 0.24%, Zn 6.52%, Sb 0.10%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>In 1989, drilling outlined a reserve of 31,026 tonnes grading 8.1 grams per tonne gold and 194 grams per tonne silver (Assessment Report 22085). A vein sample taken in 1987 assayed 2.1 grams per tonne gold, 36 grams per tonne silver, 0.1 per cent lead and 0.15 per cent zinc (Open File 1988-11).</t>
+          <t>In 1992, a well-mineralized grab sample taken from the dump assayed 0.625 gram per tonne gold, 306.9 grams per tonne silver and 6.52 per cent zinc (Assessment Report 22223). In 2000, a rock sample (RA-320) from the main cut assayed 231.3 grams per tonne silver, 0.8 gram per tonne gold, 0.14 per cent copper, 0.24 per cent lead, and 0.1 per cent antimony over 0.3 metre (Assessment Report 26507).</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>$44k</t>
+          <t>$182k</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P98" t="n">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Bakus, John Nick, Julia Res.</t>
+          <t>Little Mountain Resources Ltd., Eagle Peak Resources Inc., Caldwell</t>
         </is>
       </c>
       <c r="R98" t="inlineStr"/>
@@ -9853,17 +9853,17 @@
         <v>25</v>
       </c>
       <c r="U98" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V98" t="n">
-        <v>49.73556</v>
+        <v>50.21028</v>
       </c>
       <c r="W98" t="n">
-        <v>-117.39528</v>
+        <v>-118.55111</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW130</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE035</t>
         </is>
       </c>
     </row>
@@ -9873,30 +9873,30 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENTRAL ZEBALLOS              </t>
+          <t xml:space="preserve">MABOU (L.8399)                </t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>092L  212</t>
+          <t>082FNW149</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Zeballos</t>
+          <t>Slocan</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper, Zinc</t>
+          <t>Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9912,54 +9912,54 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Au 12.0g/t</t>
+          <t>Ag 9100g/t, Pb 18.50%, Zn 17.00%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>In 1983, a sample (CA-001-83) across a 24-centimetre-wide mineralized vein assayed 12.1 grams per tonne gold, 4.0 grams per tonne silver and 0.200 per cent arsenic (Assessment Report 12077). 6 drift assayed 131.9 grams per tonne gold (Assessment Report 18556). In 1989, diamond drilling yielded intercepts of 17.7 grams per tonne gold over 0.22 metre in hole CZ-9-89-20 from the main vein on the No. 9 level and west of the raise yielding 25.6 grams per tonne gold over 0.23 metres and hole CZ-9-89-19 intersected a new vein structure, located 111.6 metres south of the main vein on the No. Possible reserves are 43 631 tonnes grading 12 grams per tonne gold and are estimates based on results from old mine data as supported by recent underground sampling and diamond drilling.</t>
+          <t>Assay results on a grab sample of the cleanest looking ore yielded trace of gold, 9100 grams per tonne silver, 18.5 per cent lead and 17 per cent zinc.</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>$248k</t>
+          <t>$178k</t>
         </is>
       </c>
       <c r="O99" t="n">
         <v>12</v>
       </c>
       <c r="P99" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Canalaska Resources, Canalaska Ventures Ltd., Impact Res.</t>
+          <t>Goldsmith, Locke B., Trac Resources Inc.</t>
         </is>
       </c>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T99" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U99" t="n">
         <v>58</v>
       </c>
       <c r="V99" t="n">
-        <v>50.03583</v>
+        <v>49.815</v>
       </c>
       <c r="W99" t="n">
-        <v>-126.78333</v>
+        <v>-117.34028</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++212</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW149</t>
         </is>
       </c>
     </row>
@@ -9969,30 +9969,30 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCKY SEVEN                   </t>
+          <t xml:space="preserve">WELLINGTON (L.553)            </t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>103I  099</t>
+          <t>082KSW030</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thornhill</t>
+          <t>Retallack</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Silver, Lead, Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10004,58 +10004,62 @@
         <v>0</v>
       </c>
       <c r="J100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>91 t (assay)</t>
+          <t>9 kt</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Ag 38.3g/t, Au 7.16g/t, Cu 0.015%, Pb 0.246%, Zn 0.03%</t>
+          <t>Ag 3570g/t, Pb 79.90%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Sample TT-9, from a quartz vein with galena, pyrite and chalcopyrite near the old adits assayed 7.16 grams per tonne gold, 38.3 grams per tonne silver, 0.246 per cent lead, 0.03 per cent zinc and 0.015 per cent copper. Another sample taken from the dump pile at an old open cut assayed 0.695 grams per tonne gold, 99.5 grams per tonne silver, 2.533 per cent lead, 0.035 per cent zinc and 0.161 per cent copper (Di Spirito, 1986). About 460 metres to the southwest of the old workings, a sample from a 4 metre wide quartz vein assayed 6.7 grams per tonne gold, 1049 grams epr tonne silver, 0.094 per cent lead, 0.032 per cent zinc, 0.024 per cent copper and 0.0012 per cent molybdenite (Assessment Report 13140).</t>
+          <t>In 1950, two samples (no.604 and 605) from the first drift assayed 1050 and 164 grams per tonne silver, 37.2 and 8.4 per cent lead with 21.3 and 14.3 per cent zinc over 5 and 57 centimetres, respectively (Property File - C.C. In 1975, a chip sample from near the face of the Matheson east drift assayed 344 grams per tonne silver, 12 per cent lead and 8.8 per cent zinc over 0.6 metre (Property File - Semco Mining Corp. 610) from a pit just east of the shaft assayed 3570 grams per tonne silver and 79.9 per cent lead over 20 centimetres (Property File - C.C. In 1979, underground sampling of a crosscut from the Hazel adit yielded 58.14 grams per tonne silver, 0.53 per cent lead and 4.0 per cent zinc over 3 metres (Property File - Semco Mining Corp. A potential underground mineralized zone in th</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>$218k</t>
+          <t>$176k</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P100" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Boga, Iqbal; Thorne Exploration Inc., Castello Resources</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
+          <t>Argentum Resources, Leontowicz, Peter</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Conditional Registration Reserve (Ski Development) — special process</t>
+        </is>
+      </c>
       <c r="S100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T100" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U100" t="n">
         <v>58</v>
       </c>
       <c r="V100" t="n">
-        <v>54.4775</v>
+        <v>50.05667</v>
       </c>
       <c r="W100" t="n">
-        <v>-128.44611</v>
+        <v>-117.14944</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103I++099</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW030</t>
         </is>
       </c>
     </row>
@@ -10065,21 +10069,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE BLUE                     </t>
+          <t xml:space="preserve">DUMAC                         </t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>082LSE035</t>
+          <t>082FNW232</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Cherryville</t>
+          <t>Slocan</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5</v>
+        <v>11.3</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10088,7 +10092,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Gold, Lead, Copper, Antimony</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -10104,54 +10108,54 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>5 t</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Ag 269g/t, Cu 0.14%, Pb 0.24%, Zn 6.52%, Sb 0.10%</t>
+          <t>Ag 384g/t, Pb 2.80%, Zn 4.00%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>In 1992, a well-mineralized grab sample taken from the dump assayed 0.625 gram per tonne gold, 306.9 grams per tonne silver and 6.52 per cent zinc (Assessment Report 22223). In 2000, a rock sample (RA-320) from the main cut assayed 231.3 grams per tonne silver, 0.8 gram per tonne gold, 0.14 per cent copper, 0.24 per cent lead, and 0.1 per cent antimony over 0.3 metre (Assessment Report 26507).</t>
+          <t>A 2.3-metre chip sample across the vein assayed 384 grams per tonne silver, 2.8 per cent lead and 4 per cent zinc (Annual Report 1932, page 179).</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>$182k</t>
+          <t>$171k</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P101" t="n">
-        <v>2010</v>
+        <v>2025</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Little Mountain Resources Ltd., Eagle Peak Resources Inc., Caldwell</t>
+          <t>Goldsmith, Locke B., Trac Resources Inc.</t>
         </is>
       </c>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T101" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U101" t="n">
         <v>58</v>
       </c>
       <c r="V101" t="n">
-        <v>50.21028</v>
+        <v>49.82583</v>
       </c>
       <c r="W101" t="n">
-        <v>-118.55111</v>
+        <v>-117.33694</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE035</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW232</t>
         </is>
       </c>
     </row>
@@ -10161,12 +10165,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">MABOU (L.8399)                </t>
+          <t xml:space="preserve">WESTMONT (L.8929)             </t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>082FNW149</t>
+          <t>082FNW145</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -10175,7 +10179,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>10.5</v>
+        <v>12.3</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10184,7 +10188,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead</t>
+          <t>Silver, Lead, Zinc, Gold, Cadmium, Copper</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10200,54 +10204,54 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>3 kt</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Ag 9100g/t, Pb 18.50%, Zn 17.00%</t>
+          <t>Au 1.0g/t, Ag 1826g/t, Cu 0.25%, Pb 7.80%, Zn 12.97%</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Assay results on a grab sample of the cleanest looking ore yielded trace of gold, 9100 grams per tonne silver, 18.5 per cent lead and 17 per cent zinc.</t>
+          <t>Two samples of vein material assayed 2363 and 1351 grams per tonne silver (Property File - Hoko Explorations [1981-04-04]: News Clippings - Westmont). In 1987, a sample (JL-125) assayed 2300 grams per tonne silver, 0.974 grams per tonne gold, 0.247 per cent copper, 7.8 per cent lead, and 12.97 per cent zinc (Open File 1988-11).</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>$178k</t>
+          <t>$166k</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P102" t="n">
         <v>2025</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Goldsmith, Locke B., Trac Resources Inc.</t>
+          <t>Trac Resources Inc., Hoko Exploration Ltd. (NPL), Bakus</t>
         </is>
       </c>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T102" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U102" t="n">
         <v>58</v>
       </c>
       <c r="V102" t="n">
-        <v>49.815</v>
+        <v>49.82944</v>
       </c>
       <c r="W102" t="n">
-        <v>-117.34028</v>
+        <v>-117.32472</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW149</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW145</t>
         </is>
       </c>
     </row>
@@ -10257,30 +10261,30 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WELLINGTON (L.553)            </t>
+          <t xml:space="preserve">DELOS (L. 3790)               </t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>082KSW030</t>
+          <t>082KNE030</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Retallack</t>
+          <t>Panorama</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -10292,62 +10296,58 @@
         <v>0</v>
       </c>
       <c r="J103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>9 kt</t>
+          <t>40 t (assay)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Ag 3570g/t, Pb 79.90%</t>
+          <t>Ag 27.43g/t, Au 0.69g/t, Cu 9.6%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>In 1950, two samples (no.604 and 605) from the first drift assayed 1050 and 164 grams per tonne silver, 37.2 and 8.4 per cent lead with 21.3 and 14.3 per cent zinc over 5 and 57 centimetres, respectively (Property File - C.C. In 1975, a chip sample from near the face of the Matheson east drift assayed 344 grams per tonne silver, 12 per cent lead and 8.8 per cent zinc over 0.6 metre (Property File - Semco Mining Corp. 610) from a pit just east of the shaft assayed 3570 grams per tonne silver and 79.9 per cent lead over 20 centimetres (Property File - C.C. In 1979, underground sampling of a crosscut from the Hazel adit yielded 58.14 grams per tonne silver, 0.53 per cent lead and 4.0 per cent zinc over 3 metres (Property File - Semco Mining Corp. A potential underground mineralized zone in th</t>
+          <t>A sample across 1 metre from one open cut yielded 0.69 gram per tonne gold, 27.43 grams per tonne silver and 9.6 per cent copper (Annual Report 1915, page 96).</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>$176k</t>
+          <t>$160k</t>
         </is>
       </c>
       <c r="O103" t="n">
+        <v>14</v>
+      </c>
+      <c r="P103" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Gold Ford Capital, Pochylko, William</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="n">
         <v>7</v>
       </c>
-      <c r="P103" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>Argentum Resources, Leontowicz, Peter</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>Conditional Registration Reserve (Ski Development) — special process</t>
-        </is>
-      </c>
-      <c r="S103" t="n">
-        <v>3</v>
-      </c>
       <c r="T103" t="n">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="U103" t="n">
         <v>58</v>
       </c>
       <c r="V103" t="n">
-        <v>50.05667</v>
+        <v>50.50778</v>
       </c>
       <c r="W103" t="n">
-        <v>-117.14944</v>
+        <v>-116.28861</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW030</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNE030</t>
         </is>
       </c>
     </row>
@@ -10357,12 +10357,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUMAC                         </t>
+          <t xml:space="preserve">REPUBLIC NO. 2 (L.5498)       </t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>082FNW232</t>
+          <t>082FNW168</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>11.3</v>
+        <v>3.7</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Silver, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10396,54 +10396,54 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>5 t</t>
+          <t>300 t</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Ag 384g/t, Pb 2.80%, Zn 4.00%</t>
+          <t>Au 2.9g/t, Ag 247g/t, Pb 0.06%</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>A 2.3-metre chip sample across the vein assayed 384 grams per tonne silver, 2.8 per cent lead and 4 per cent zinc (Annual Report 1932, page 179).</t>
+          <t>2 adit assayed 352.9 grams per tonne silver, 2.9 grams per tonne gold and 0.06 per cent lead (Property File - D.W. A sample (12578) assayed 142 grams per tonne silver (Morris, R.J.</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>$171k</t>
+          <t>$158k</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P104" t="n">
         <v>2025</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Goldsmith, Locke B., Trac Resources Inc.</t>
+          <t>Manny Consul., Bakus, John Nick</t>
         </is>
       </c>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T104" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="U104" t="n">
         <v>58</v>
       </c>
       <c r="V104" t="n">
-        <v>49.82583</v>
+        <v>49.8</v>
       </c>
       <c r="W104" t="n">
-        <v>-117.33694</v>
+        <v>-117.45278</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW232</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW168</t>
         </is>
       </c>
     </row>
@@ -10453,21 +10453,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WESTMONT (L.8929)             </t>
+          <t xml:space="preserve">LUCKY THOUGHT (L.10636)       </t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>082FNW145</t>
+          <t>082FNW063</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Slocan</t>
+          <t>Silverton</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>12.3</v>
+        <v>4.5</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Cadmium, Copper</t>
+          <t>Silver, Zinc, Lead, Gold, Cadmium, Copper</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10492,54 +10492,54 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>3 kt</t>
+          <t>9 kt</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Au 1.0g/t, Ag 1826g/t, Cu 0.25%, Pb 7.80%, Zn 12.97%</t>
+          <t>Au 0.7g/t, Ag 336g/t, Cu 0.25%, Pb 0.80%, Zn 25.50%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Two samples of vein material assayed 2363 and 1351 grams per tonne silver (Property File - Hoko Explorations [1981-04-04]: News Clippings - Westmont). In 1987, a sample (JL-125) assayed 2300 grams per tonne silver, 0.974 grams per tonne gold, 0.247 per cent copper, 7.8 per cent lead, and 12.97 per cent zinc (Open File 1988-11).</t>
+          <t>In 1949, a sample from the no.1 tunnel assayed 0.8 per cent lead, 19.9 per cent zinc and 34.2 grams per tonne silver, while a dump sample assayed 0.8 per cent lead, 35.7 per cent zinc and 397 grams per tonne silver (Property File - C.C. Also, at this time, a vein exposed in an open-cut, at an elevation of 1034 metres, assayed 274 grams per tonne silver, 2 per cent lead and 24 per cent zinc (Property File - T.D. In 1976, two chip samples (78LJ1 and 78LJ2) of mineralized quartz shear from the No.1 level workings yielded 0.7 and 0.7 gram per tonne gold, 377 and 1573 gram per tonne silver, 0.053 and 0.25 per cent copper, 13.1 and 27.0 per cent zinc with 3.75 and 0.51 per cent lead over 0.927 and 0.305 metre, respectively (Property File - T.D.</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>$166k</t>
+          <t>$152k</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P105" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Trac Resources Inc., Hoko Exploration Ltd. (NPL), Bakus</t>
+          <t>Klondike Silver Corp., Nord, Leigh</t>
         </is>
       </c>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T105" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U105" t="n">
         <v>58</v>
       </c>
       <c r="V105" t="n">
-        <v>49.82944</v>
+        <v>49.93611</v>
       </c>
       <c r="W105" t="n">
-        <v>-117.32472</v>
+        <v>-117.30028</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW145</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW063</t>
         </is>
       </c>
     </row>
@@ -10549,30 +10549,30 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELOS (L. 3790)               </t>
+          <t>SHANNON</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>082KNE030</t>
+          <t>082KSW060</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Panorama</t>
+          <t>Hills</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Silver, Lead, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10588,54 +10588,54 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>40 t (assay)</t>
+          <t>4 t</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Ag 27.43g/t, Au 0.69g/t, Cu 9.6%</t>
+          <t>Au 3.1g/t, Ag 375g/t, Cu 0.27%, Pb 8.54%, Zn 1.10%</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>A sample across 1 metre from one open cut yielded 0.69 gram per tonne gold, 27.43 grams per tonne silver and 9.6 per cent copper (Annual Report 1915, page 96).</t>
+          <t>Drillhole SH-24 intersected 4.4 metres grading 147 grams per tonne silver, 2.67 per cent lead, 1.1 per cent zinc and 0.27 per cent copper (Assessment Report 2966). The average of 3 samples taken in the east tunnel area about 1 metre is 3.09 grams per tonne gold, 603.43 grams per tonne silver, 14.4 per cent lead and 13.8 per cent zinc (Starr, 1929 (Property File)).</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>$160k</t>
+          <t>$150k</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P106" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Gold Ford Capital, Pochylko, William</t>
+          <t>Silvera Resources Ind., Anderson, Jeffrey David (Van Isle Prospecting)</t>
         </is>
       </c>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T106" t="n">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="U106" t="n">
         <v>58</v>
       </c>
       <c r="V106" t="n">
-        <v>50.50778</v>
+        <v>50.09361</v>
       </c>
       <c r="W106" t="n">
-        <v>-116.28861</v>
+        <v>-117.59167</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNE030</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW060</t>
         </is>
       </c>
     </row>
@@ -10645,30 +10645,30 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">REPUBLIC NO. 2 (L.5498)       </t>
+          <t xml:space="preserve">KING MIDAS NO. 1 VEIN         </t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>082FNW168</t>
+          <t>092L  020</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Slocan</t>
+          <t>Zeballos</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3.7</v>
+        <v>9.4</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc</t>
+          <t>Gold, Silver, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10684,54 +10684,54 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>300 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Au 2.9g/t, Ag 247g/t, Pb 0.06%</t>
+          <t>Au 97.4g/t, Ag 28.1g/t</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2 adit assayed 352.9 grams per tonne silver, 2.9 grams per tonne gold and 0.06 per cent lead (Property File - D.W. A sample (12578) assayed 142 grams per tonne silver (Morris, R.J.</t>
+          <t>In 1932, a sample assayed 97.38 grams per tonne gold and 28.11 grams per tonne silver (Geological Survey of Canada Summary Report 1932, Part A, II, pages 39-42).</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>$158k</t>
+          <t>$141k</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P107" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Manny Consul., Bakus, John Nick</t>
+          <t>Canalaska Resources, Canalaska Ventures Ltd., Richards</t>
         </is>
       </c>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T107" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U107" t="n">
         <v>58</v>
       </c>
       <c r="V107" t="n">
-        <v>49.8</v>
+        <v>50.06</v>
       </c>
       <c r="W107" t="n">
-        <v>-117.45278</v>
+        <v>-126.79222</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW168</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++020</t>
         </is>
       </c>
     </row>
@@ -10741,30 +10741,30 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCKY THOUGHT (L.10636)       </t>
+          <t>UNION (L.944)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>082FNW063</t>
+          <t>082FSW164</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Silverton</t>
+          <t>Oasis</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Gold, Cadmium, Copper</t>
+          <t>Lead, Zinc, Silver, Gold, Copper, Bismuth</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10780,54 +10780,54 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>9 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Ag 336g/t, Cu 0.25%, Pb 0.80%, Zn 25.50%</t>
+          <t>Au 3.2g/t, Ag 1310g/t, Cu 0.11%, Pb 6.00%, Zn 13.20%</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>In 1949, a sample from the no.1 tunnel assayed 0.8 per cent lead, 19.9 per cent zinc and 34.2 grams per tonne silver, while a dump sample assayed 0.8 per cent lead, 35.7 per cent zinc and 397 grams per tonne silver (Property File - C.C. Also, at this time, a vein exposed in an open-cut, at an elevation of 1034 metres, assayed 274 grams per tonne silver, 2 per cent lead and 24 per cent zinc (Property File - T.D. In 1976, two chip samples (78LJ1 and 78LJ2) of mineralized quartz shear from the No.1 level workings yielded 0.7 and 0.7 gram per tonne gold, 377 and 1573 gram per tonne silver, 0.053 and 0.25 per cent copper, 13.1 and 27.0 per cent zinc with 3.75 and 0.51 per cent lead over 0.927 and 0.305 metre, respectively (Property File - T.D.</t>
+          <t>The sample assayed 3.22 grams per tonne gold, 1310.0 grams per tonne silver, 6.0 per cent lead, 13.2 per cent zinc, and 0.11 per cent copper (Assessment Report 11618).</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>$152k</t>
+          <t>$132k</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P108" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Klondike Silver Corp., Nord, Leigh</t>
+          <t>Royal Can. Ventures, Fidelio Enterprise Corp., Rex Silver Mines Ltd.</t>
         </is>
       </c>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T108" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="U108" t="n">
         <v>58</v>
       </c>
       <c r="V108" t="n">
-        <v>49.93611</v>
+        <v>49.12278</v>
       </c>
       <c r="W108" t="n">
-        <v>-117.30028</v>
+        <v>-117.80278</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW063</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW164</t>
         </is>
       </c>
     </row>
@@ -10837,30 +10837,30 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SHANNON</t>
+          <t xml:space="preserve">EARLY BIRD                    </t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>082KSW060</t>
+          <t>103C  001</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Moresby Camp</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>7.7</v>
+        <v>14.3</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10876,54 +10876,54 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>4 t</t>
+          <t>171 t (assay)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Au 3.1g/t, Ag 375g/t, Cu 0.27%, Pb 8.54%, Zn 1.10%</t>
+          <t>Ag 3.4g/t, Au 8.57g/t</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Drillhole SH-24 intersected 4.4 metres grading 147 grams per tonne silver, 2.67 per cent lead, 1.1 per cent zinc and 0.27 per cent copper (Assessment Report 2966). The average of 3 samples taken in the east tunnel area about 1 metre is 3.09 grams per tonne gold, 603.43 grams per tonne silver, 14.4 per cent lead and 13.8 per cent zinc (Starr, 1929 (Property File)).</t>
+          <t>A 61-centimetre sample near the south end of the open stope in the lower adit assayed 8.57 grams per tonne gold and 3.4 grams per tonne silver (Bulletin 54, pages 217,218).</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>$150k</t>
+          <t>$124k</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P109" t="n">
-        <v>2025</v>
+        <v>1981</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Silvera Resources Ind., Anderson, Jeffrey David (Van Isle Prospecting)</t>
+          <t>Charlotte Resources Ltd.</t>
         </is>
       </c>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T109" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U109" t="n">
         <v>58</v>
       </c>
       <c r="V109" t="n">
-        <v>50.09361</v>
+        <v>52.95528</v>
       </c>
       <c r="W109" t="n">
-        <v>-117.59167</v>
+        <v>-132.17944</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++001</t>
         </is>
       </c>
     </row>
@@ -10933,30 +10933,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">KING MIDAS NO. 1 VEIN         </t>
+          <t xml:space="preserve">MONARCH (L.2082)              </t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>092L  020</t>
+          <t>082FSW282</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Zeballos</t>
+          <t>Beasley</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>9.4</v>
+        <v>1.9</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc, Lead</t>
+          <t>Copper, Silver, Gold, Molybdenum, Lead, Zinc</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10972,54 +10972,54 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Au 97.4g/t, Ag 28.1g/t</t>
+          <t>Ag 106.3g/t, Au 1.03g/t, Cu 7.89%</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>In 1932, a sample assayed 97.38 grams per tonne gold and 28.11 grams per tonne silver (Geological Survey of Canada Summary Report 1932, Part A, II, pages 39-42).</t>
+          <t>In 1918, a 153 tonne sample assayed 3 per cent copper, 201.6 grams per tonne silver and 3.428 grams per tonne gold (Minister of Mines Annual Report 1918, pages 173, 174, 197). In 1980, a grab sample from the main showing assayed 1.02 grams gold, 106.3 grams silver and 7.89 per cent copper (Assessment Report 8661).</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>$141k</t>
+          <t>$111k</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P110" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Canalaska Resources, Canalaska Ventures Ltd., Richards</t>
+          <t>394225 Alberta Ltd., Hall, James Douglas</t>
         </is>
       </c>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T110" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U110" t="n">
         <v>58</v>
       </c>
       <c r="V110" t="n">
-        <v>50.06</v>
+        <v>49.49333</v>
       </c>
       <c r="W110" t="n">
-        <v>-126.79222</v>
+        <v>-117.48444</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++020</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW282</t>
         </is>
       </c>
     </row>
@@ -11029,30 +11029,30 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>UNION (L.944)</t>
+          <t>SUNRISE (L.18S)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>082FSW164</t>
+          <t>082ESW015</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Oasis</t>
+          <t>Olalla</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Gold, Copper, Bismuth</t>
+          <t>Gold, Silver, Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -11068,54 +11068,54 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>2 kt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Au 3.2g/t, Ag 1310g/t, Cu 0.11%, Pb 6.00%, Zn 13.20%</t>
+          <t>Au 85.7g/t, Ag 33.9g/t</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>The sample assayed 3.22 grams per tonne gold, 1310.0 grams per tonne silver, 6.0 per cent lead, 13.2 per cent zinc, and 0.11 per cent copper (Assessment Report 11618).</t>
+          <t>Drillhole H-5 intersected 11.92 metres yielding 1.92 grams per tonne gold and 4.80 grams per tonne silver. Drillhole H-8 yielded 11.31 grams per tonne gold and 37.03 grams per tonne silver (Assessment Report 19963). The drilling work has indicated ore reserves of 2177 tonnes grading 33.94 grams per tonne silver and 85.71 grams per tonne gold (Assessment Report 19963).</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>$132k</t>
+          <t>$108k</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P111" t="n">
-        <v>2023</v>
+        <v>1997</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Royal Can. Ventures, Fidelio Enterprise Corp., Rex Silver Mines Ltd.</t>
+          <t>Brenda Mines Ltd. Exploration Group, Goldcliff Res., Goldcliff Resource Corporation</t>
         </is>
       </c>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T111" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="U111" t="n">
         <v>58</v>
       </c>
       <c r="V111" t="n">
-        <v>49.12278</v>
+        <v>49.26</v>
       </c>
       <c r="W111" t="n">
-        <v>-117.80278</v>
+        <v>-119.83278</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ESW015</t>
         </is>
       </c>
     </row>
@@ -11125,30 +11125,30 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">EARLY BIRD                    </t>
+          <t xml:space="preserve">BIG BEN                       </t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>103C  001</t>
+          <t>082FNW090</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Moresby Camp</t>
+          <t>Retallack</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>14.3</v>
+        <v>7.5</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Silver, Lead, Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -11164,54 +11164,54 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>171 t (assay)</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Ag 3.4g/t, Au 8.57g/t</t>
+          <t>Ag 1349.5g/t, Au 4.8g/t, Pb 70%</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>A 61-centimetre sample near the south end of the open stope in the lower adit assayed 8.57 grams per tonne gold and 3.4 grams per tonne silver (Bulletin 54, pages 217,218).</t>
+          <t>A grab sample of a mineralized stringer assayed 4.8 grams per tonne gold, 13,495 grams per tonne silver and 70 per cent lead (Minister of Mines Annual Report 1926).</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>$124k</t>
+          <t>$107k</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P112" t="n">
-        <v>1981</v>
+        <v>2014</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Charlotte Resources Ltd.</t>
+          <t>Hi Ho Silver Resources Inc., CAAS MINING CORP., Stryder Explorations Ltd.</t>
         </is>
       </c>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T112" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U112" t="n">
         <v>58</v>
       </c>
       <c r="V112" t="n">
-        <v>52.95528</v>
+        <v>49.99389</v>
       </c>
       <c r="W112" t="n">
-        <v>-132.17944</v>
+        <v>-117.07611</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++001</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW090</t>
         </is>
       </c>
     </row>
@@ -11221,21 +11221,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOLDEN NIB                    </t>
+          <t xml:space="preserve">PROVIDENCE (L.1737)           </t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>103I  095</t>
+          <t>092HNW030</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Thornhill</t>
+          <t>Silver River</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5.3</v>
+        <v>10.7</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -11260,54 +11260,54 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>27 t (assay)</t>
+          <t>91 t</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Ag 26.1g/t, Au 4.2g/t, Cu 1.2%</t>
+          <t>Au 56.4g/t</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Mineralization is erratic with lenses up to 2 metres and assays up to 7.7 grams per tonne gold and 14 grams per tonne silver (Assessment Report 11335). A grab sample assayed 4.2 grams per tonne gold, 26.1 grams per tonne silver and 1.20 per cent copper (Assessment Report 13104).</t>
+          <t>Reports of a 318 tonne shipment of ore assaying $37.49 per tonne (56.40 grams per tonne gold equivalent) to Tacoma from the period 1898-1899 have not be authenticated (Minister of Mines Annual Report 1929, page C399).</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>$112k</t>
+          <t>$96k</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P113" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Boga, Iqbal; Thorne Exploration Inc., McRae</t>
+          <t>Academy Ventures Inc., Shearer, Johan Tom (FMC 124452)</t>
         </is>
       </c>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T113" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U113" t="n">
         <v>58</v>
       </c>
       <c r="V113" t="n">
-        <v>54.49139</v>
+        <v>49.62167</v>
       </c>
       <c r="W113" t="n">
-        <v>-128.46833</v>
+        <v>-121.95028</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103I++095</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HNW030</t>
         </is>
       </c>
     </row>
@@ -11317,35 +11317,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONARCH (L.2082)              </t>
+          <t>HOLLIDAY (DISCOVERY)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>082FSW282</t>
+          <t>104O  001</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Beasley</t>
+          <t>Cassiar</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1.9</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum, Lead, Zinc</t>
+          <t>Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I114" t="b">
@@ -11356,54 +11356,54 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>36 kt</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Ag 106.3g/t, Au 1.03g/t, Cu 7.89%</t>
+          <t>Au 1.3g/t, Ag 532g/t, Cu 0.16%, Pb 29.10%, Zn 13.90%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>In 1918, a 153 tonne sample assayed 3 per cent copper, 201.6 grams per tonne silver and 3.428 grams per tonne gold (Minister of Mines Annual Report 1918, pages 173, 174, 197). In 1980, a grab sample from the main showing assayed 1.02 grams gold, 106.3 grams silver and 7.89 per cent copper (Assessment Report 8661).</t>
+          <t>A 14-tonne shipment in 1979, from the Pit (104O 017) and Discovery veins, assayed 1.30 grams per tonne gold, 532.01 grams per tonne silver, 29.1 per cent lead, 13.9 per cent zinc and 0.16 per cent copper (Department of Indian and Northern Affairs, 1983).</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>$111k</t>
+          <t>$95k</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P114" t="n">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>394225 Alberta Ltd., Hall, James Douglas</t>
+          <t>CMC Metals Ltd., Stibbard, Jeff</t>
         </is>
       </c>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T114" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U114" t="n">
         <v>58</v>
       </c>
       <c r="V114" t="n">
-        <v>49.49333</v>
+        <v>59.99556</v>
       </c>
       <c r="W114" t="n">
-        <v>-117.48444</v>
+        <v>-130.56278</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW282</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104O++001</t>
         </is>
       </c>
     </row>
@@ -11413,21 +11413,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SUNRISE (L.18S)</t>
+          <t xml:space="preserve">SPOKANE                       </t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>082ESW015</t>
+          <t>082FSE032</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Olalla</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.7</v>
+        <v>19.7</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead, Zinc</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -11457,49 +11457,49 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Au 85.7g/t, Ag 33.9g/t</t>
+          <t>Pb 48.90%, Zn 1.60%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Drillhole H-5 intersected 11.92 metres yielding 1.92 grams per tonne gold and 4.80 grams per tonne silver. Drillhole H-8 yielded 11.31 grams per tonne gold and 37.03 grams per tonne silver (Assessment Report 19963). The drilling work has indicated ore reserves of 2177 tonnes grading 33.94 grams per tonne silver and 85.71 grams per tonne gold (Assessment Report 19963).</t>
+          <t>Variable values in gold (up to 20.5 grams per tonne) and silver (up to 1405 grams per tonne) are associated with the sulphides, which assay up to 48.9 per cent lead and 1.6 per cent zinc (Minister of Mines Annual Report 1915, page 173).</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>$108k</t>
+          <t>$86k</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P115" t="n">
-        <v>1997</v>
+        <v>2014</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Brenda Mines Ltd. Exploration Group, Goldcliff Res., Goldcliff Resource Corporation</t>
+          <t>Yellowstone Resources Ltd., 500374 Mines</t>
         </is>
       </c>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T115" t="n">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="U115" t="n">
         <v>58</v>
       </c>
       <c r="V115" t="n">
-        <v>49.26</v>
+        <v>49.18333</v>
       </c>
       <c r="W115" t="n">
-        <v>-119.83278</v>
+        <v>-116.99444</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ESW015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSE032</t>
         </is>
       </c>
     </row>
@@ -11509,30 +11509,30 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIG BEN                       </t>
+          <t xml:space="preserve">RACHEL                        </t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>082FNW090</t>
+          <t>082FSW299</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Retallack</t>
+          <t>Thrums</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Silver, Lead, Gold, Zinc, Copper</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -11548,33 +11548,33 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>14 t (assay)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Ag 1349.5g/t, Au 4.8g/t, Pb 70%</t>
+          <t>Ag 331.5g/t, Au 174.5g/t, Pb 10.05%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>A grab sample of a mineralized stringer assayed 4.8 grams per tonne gold, 13,495 grams per tonne silver and 70 per cent lead (Minister of Mines Annual Report 1926).</t>
+          <t>In 1980, Kimberley Gold Mines removed 14 tonnes of high grade ore from the adit, yielding an average assay of 66.64 grams per tonne gold, 271.5 grams per tonne silver, and 9.42 per cent lead (Assessment Report 19021). A grab sample taken in 1989 from the middle of the adit assayed 174.5 grams per tonne gold, 331.5 grams per tonne silver and 10.05 per cent lead (Assessment Report 19021). A grab sample taken in 1984 assayed 4.94 grams per tonne gold, 65.13 grams per tonne silver, 2.42 per cent lead (Assessment Report 19021).</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>$107k</t>
+          <t>$84k</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P116" t="n">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Hi Ho Silver Resources Inc., CAAS MINING CORP., Stryder Explorations Ltd.</t>
+          <t>Northwind Ventures, Murray, Kenneth Edward</t>
         </is>
       </c>
       <c r="R116" t="inlineStr"/>
@@ -11588,14 +11588,14 @@
         <v>58</v>
       </c>
       <c r="V116" t="n">
-        <v>49.99389</v>
+        <v>49.29278</v>
       </c>
       <c r="W116" t="n">
-        <v>-117.07611</v>
+        <v>-117.45833</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW090</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW299</t>
         </is>
       </c>
     </row>
@@ -11605,17 +11605,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVIDENCE (L.1737)           </t>
+          <t xml:space="preserve">MONTEZUMA (L.2041)            </t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>092HNW030</t>
+          <t>082FNW091</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Silver River</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11644,54 +11644,54 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>91 t</t>
+          <t>90 t (assay)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Au 56.4g/t</t>
+          <t>Ag 446g/t, Pb 12.85%, Zn 0.4%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Reports of a 318 tonne shipment of ore assaying $37.49 per tonne (56.40 grams per tonne gold equivalent) to Tacoma from the period 1898-1899 have not be authenticated (Minister of Mines Annual Report 1929, page C399).</t>
+          <t>A grab sample from the dump near the portal of the upper adit assayed 446 grams per tonne silver, 12.85 per cent lead and 0.4 per cent zinc. A chip sample taken from the mineralized porphyritic dike assayed 46 grams per tonne silver, 0.15 per cent lead and 0.3 per cent zinc across 1.5 metres (Property File - Prospectus, Hilroy Mines Ltd., 1967).</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>$96k</t>
+          <t>$82k</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P117" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Academy Ventures Inc., Shearer, Johan Tom (FMC 124452)</t>
+          <t>Spey Resources Corp., Denny, Jack Norman</t>
         </is>
       </c>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T117" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U117" t="n">
         <v>58</v>
       </c>
       <c r="V117" t="n">
-        <v>49.62167</v>
+        <v>49.94222</v>
       </c>
       <c r="W117" t="n">
-        <v>-121.95028</v>
+        <v>-117.05639</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HNW030</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW091</t>
         </is>
       </c>
     </row>
@@ -11701,35 +11701,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HOLLIDAY (DISCOVERY)</t>
+          <t xml:space="preserve">FLORENCE                      </t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>104O  001</t>
+          <t>092F  147</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cassiar</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>88.40000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I118" t="b">
@@ -11740,54 +11740,54 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>36 kt</t>
+          <t>39 t (assay)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 532g/t, Cu 0.16%, Pb 29.10%, Zn 13.90%</t>
+          <t>Ag 320.86g/t, Au 0.68g/t, Cad 0.16%, Cu 9.26%, Zn 32.87%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>A 14-tonne shipment in 1979, from the Pit (104O 017) and Discovery veins, assayed 1.30 grams per tonne gold, 532.01 grams per tonne silver, 29.1 per cent lead, 13.9 per cent zinc and 0.16 per cent copper (Department of Indian and Northern Affairs, 1983).</t>
+          <t>A grab sample from the adit assayed 32.87 per cent zinc, 9.26 per cent copper, 320.86 grams per tonne silver, 0.16 per cent cadmium and 0.68 grams per tonne gold (Assessment Report 4961).</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>$95k</t>
+          <t>$78k</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P118" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>CMC Metals Ltd., Stibbard, Jeff</t>
+          <t>Longbar Minerals Limited, Aquarius Resources Limited, Geiger</t>
         </is>
       </c>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T118" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U118" t="n">
         <v>58</v>
       </c>
       <c r="V118" t="n">
-        <v>59.99556</v>
+        <v>49.94667</v>
       </c>
       <c r="W118" t="n">
-        <v>-130.56278</v>
+        <v>-124.69694</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104O++001</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++147</t>
         </is>
       </c>
     </row>
@@ -11797,21 +11797,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPOKANE                       </t>
+          <t xml:space="preserve">NOBLE FIVE                    </t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>082FSE032</t>
+          <t>082KNW153</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ymir</t>
+          <t>Five Mile</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>19.7</v>
+        <v>9.6</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11836,54 +11836,54 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2 kt</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Pb 48.90%, Zn 1.60%</t>
+          <t>Ag 4022g/t, Au 12.34g/t, Pb 16%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Variable values in gold (up to 20.5 grams per tonne) and silver (up to 1405 grams per tonne) are associated with the sulphides, which assay up to 48.9 per cent lead and 1.6 per cent zinc (Minister of Mines Annual Report 1915, page 173).</t>
+          <t>An average sample across the vein over 0.46 metre at the face of the adit assayed 12.34 grams per tonne gold, 4022 grams per tonne silver and 16 per cent lead. They contain galena and pyrite and a sample collected in 1914 assayed 15.77 grams per tonne gold, 672 grams per tonne silver and 14.3 per cent lead.</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>$86k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P119" t="n">
-        <v>2014</v>
+        <v>2026</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Yellowstone Resources Ltd., 500374 Mines</t>
+          <t>Spey Resources Corp., Denny, Bob Ian; Denny</t>
         </is>
       </c>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T119" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U119" t="n">
         <v>58</v>
       </c>
       <c r="V119" t="n">
-        <v>49.18333</v>
+        <v>50.61917</v>
       </c>
       <c r="W119" t="n">
-        <v>-116.99444</v>
+        <v>-117.33611</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSE032</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW153</t>
         </is>
       </c>
     </row>
@@ -11893,30 +11893,30 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">RACHEL                        </t>
+          <t xml:space="preserve">FLINT                         </t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>082FSW299</t>
+          <t>082FNW083</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Thrums</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Silver, Lead, Zinc, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -11932,54 +11932,54 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>14 t (assay)</t>
+          <t>177 t (assay)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Ag 331.5g/t, Au 174.5g/t, Pb 10.05%</t>
+          <t>Ag 576g/t, WO3 4.88%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>In 1980, Kimberley Gold Mines removed 14 tonnes of high grade ore from the adit, yielding an average assay of 66.64 grams per tonne gold, 271.5 grams per tonne silver, and 9.42 per cent lead (Assessment Report 19021). A grab sample taken in 1989 from the middle of the adit assayed 174.5 grams per tonne gold, 331.5 grams per tonne silver and 10.05 per cent lead (Assessment Report 19021). A grab sample taken in 1984 assayed 4.94 grams per tonne gold, 65.13 grams per tonne silver, 2.42 per cent lead (Assessment Report 19021).</t>
+          <t>A grab sample taken from the vein in the uppermost adit assayed 576 grams per tonne silver and 4.88 per cent tungsten but later sampling of the vein failed to duplicate the tungsten assay.</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>$84k</t>
+          <t>$69k</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Northwind Ventures, Murray, Kenneth Edward</t>
+          <t>Cream Minerals Ltd.</t>
         </is>
       </c>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T120" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U120" t="n">
         <v>58</v>
       </c>
       <c r="V120" t="n">
-        <v>49.29278</v>
+        <v>49.93083</v>
       </c>
       <c r="W120" t="n">
-        <v>-117.45833</v>
+        <v>-117.10556</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW299</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW083</t>
         </is>
       </c>
     </row>
@@ -11989,30 +11989,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEZUMA (L.2041)            </t>
+          <t xml:space="preserve">MARY                          </t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>082FNW091</t>
+          <t>082FNW208</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>10.7</v>
+        <v>13.7</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -12028,54 +12028,54 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>90 t (assay)</t>
+          <t>53 t</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Ag 446g/t, Pb 12.85%, Zn 0.4%</t>
+          <t>Au 4.2g/t, Ag 51.0g/t</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>A grab sample from the dump near the portal of the upper adit assayed 446 grams per tonne silver, 12.85 per cent lead and 0.4 per cent zinc. A chip sample taken from the mineralized porphyritic dike assayed 46 grams per tonne silver, 0.15 per cent lead and 0.3 per cent zinc across 1.5 metres (Property File - Prospectus, Hilroy Mines Ltd., 1967).</t>
+          <t>In 1967, diamond drilling is reported to have yielded up to 0.30 per cent lead, 4.70 per cent zinc, 6.8 grams per tonne gold and 271.9 grams per tonne silver over 75 centimetres in hole no.4 (Property File - R.W. 29229) from the south end of a trench located approximately 100 metres south of the adit assayed 27.40 per cent lead, 20.5 grams per tonne gold and 807.1 grams per tonne silver over 0.6 metre (Property File - R.W. In 1983, sampling yielded up to 8.2 grams per tonne gold with 26.0 grams per tonne silver over 2 metres (sample J69) from the third adit and 2.7 grams per tonne gold with 76.0 grams per tonne silver over 1.5 metres (sample J72) from the second adit, whereas sample (J64) from a shear exposed in a trench assayed 4.15 grams per tonne gold with 32.0 grams per tonne silver ov</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>$82k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P121" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Spey Resources Corp., Denny, Jack Norman</t>
+          <t>Siscoe Callahan Min., Bakus, John Nick</t>
         </is>
       </c>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T121" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U121" t="n">
         <v>58</v>
       </c>
       <c r="V121" t="n">
-        <v>49.94222</v>
+        <v>49.80361</v>
       </c>
       <c r="W121" t="n">
-        <v>-117.05639</v>
+        <v>-117.28389</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW091</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW208</t>
         </is>
       </c>
     </row>
@@ -12085,30 +12085,30 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORENCE                      </t>
+          <t xml:space="preserve">HOPE                          </t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>092F  147</t>
+          <t>082FSE044</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>toxʷnač</t>
+          <t>Boswell</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver, Lead, Cadmium, Gold</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -12124,54 +12124,54 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>39 t (assay)</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Ag 320.86g/t, Au 0.68g/t, Cad 0.16%, Cu 9.26%, Zn 32.87%</t>
+          <t>Ag 263g/t, Pb 13.4%, Zn 14.9%</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>A grab sample from the adit assayed 32.87 per cent zinc, 9.26 per cent copper, 320.86 grams per tonne silver, 0.16 per cent cadmium and 0.68 grams per tonne gold (Assessment Report 4961).</t>
+          <t>The best sample over 0.7 metre assayed 387 grams per tonne silver, 19.0 per cent lead and 18.7 per cent zinc; in 1990 confirmed recorded assays ranging from 0.14 to 0.47 gram per tonne gold (this would have been nil to trace in earlier assays), 77.5 to 1213 grams per tonne silver, 2.04 to 71.2 per cent lead and 1.83 to 18.1 per cent zinc. an average of three samples over a width of 0.5 metre and strike length of 20 metres was 263 grams per tonne silver, 13.4 per cent lead and 14.9 per cent zinc.</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>$78k</t>
+          <t>$60k</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P122" t="n">
-        <v>2023</v>
+        <v>1994</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Longbar Minerals Limited, Aquarius Resources Limited, Geiger</t>
+          <t>Forbes Resources Ltd., Dobrana Resources Ltd.</t>
         </is>
       </c>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T122" t="n">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="U122" t="n">
         <v>58</v>
       </c>
       <c r="V122" t="n">
-        <v>49.94667</v>
+        <v>49.45333</v>
       </c>
       <c r="W122" t="n">
-        <v>-124.69694</v>
+        <v>-116.71278</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++147</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSE044</t>
         </is>
       </c>
     </row>
@@ -12181,30 +12181,30 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOBLE FIVE                    </t>
+          <t xml:space="preserve">PARK                          </t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>082KNW153</t>
+          <t>082GNW012</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Five Mile</t>
+          <t>Marysville</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Lead, Silver</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -12220,54 +12220,54 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Ag 4022g/t, Au 12.34g/t, Pb 16%</t>
+          <t>Pb 71.00%</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>An average sample across the vein over 0.46 metre at the face of the adit assayed 12.34 grams per tonne gold, 4022 grams per tonne silver and 16 per cent lead. They contain galena and pyrite and a sample collected in 1914 assayed 15.77 grams per tonne gold, 672 grams per tonne silver and 14.3 per cent lead.</t>
+          <t>Assays indicate 100 to 200 grams of silver and from 18 to 71 per cent lead but these are probably from hand-cobbed ore material.</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$59k</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P123" t="n">
-        <v>2026</v>
+        <v>1973</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Spey Resources Corp., Denny, Bob Ian; Denny</t>
+          <t>Cominco Ltd., Imperial Oil</t>
         </is>
       </c>
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T123" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U123" t="n">
         <v>58</v>
       </c>
       <c r="V123" t="n">
-        <v>50.61917</v>
+        <v>49.65083</v>
       </c>
       <c r="W123" t="n">
-        <v>-117.33611</v>
+        <v>-115.91583</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW153</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082GNW012</t>
         </is>
       </c>
     </row>
@@ -12277,30 +12277,30 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLINT                         </t>
+          <t xml:space="preserve">GEILER (L.1369)               </t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>082FNW083</t>
+          <t>092K  010</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Tungsten</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -12312,58 +12312,62 @@
         <v>0</v>
       </c>
       <c r="J124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>177 t (assay)</t>
+          <t>108 t (assay)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Ag 576g/t, WO3 4.88%</t>
+          <t>Au 8.9g/t</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>A grab sample taken from the vein in the uppermost adit assayed 576 grams per tonne silver and 4.88 per cent tungsten but later sampling of the vein failed to duplicate the tungsten assay.</t>
+          <t>One sample assayed 1.0 gram per tonne gold (Minister of Mines Annual Report 1913). One 1.5 metre sample across the dip of numerous quartz stringers in greenstone assayed 8.9 grams per tonne gold (Stevenson, J.D., 1938). One chip across 30 centimetres of decomposed and oxidized shear assayed 48.0 grams per tonne gold and 0.4 per cent copper (Stevenson, J.D., 1938).</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>$69k</t>
+          <t>$53k</t>
         </is>
       </c>
       <c r="O124" t="n">
+        <v>5</v>
+      </c>
+      <c r="P124" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Kikauka, Andris (FMC # 114051), Oppelt</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>abuts Main Lake Park boundary</t>
+        </is>
+      </c>
+      <c r="S124" t="n">
         <v>1</v>
       </c>
-      <c r="P124" t="n">
-        <v>2006</v>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>Cream Minerals Ltd.</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="n">
-        <v>2</v>
-      </c>
       <c r="T124" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U124" t="n">
         <v>58</v>
       </c>
       <c r="V124" t="n">
-        <v>49.93083</v>
+        <v>50.19111</v>
       </c>
       <c r="W124" t="n">
-        <v>-117.10556</v>
+        <v>-125.26111</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW083</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++010</t>
         </is>
       </c>
     </row>
@@ -12373,30 +12377,30 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARY                          </t>
+          <t>ED</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>082FNW208</t>
+          <t>082FSW003</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Nelway</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>13.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Lead, Zinc, Silver, Cadmium</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -12412,33 +12416,33 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>53 t</t>
+          <t>2 t</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Au 4.2g/t, Ag 51.0g/t</t>
+          <t>Pb 2.52%, Zn 10.84%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>In 1967, diamond drilling is reported to have yielded up to 0.30 per cent lead, 4.70 per cent zinc, 6.8 grams per tonne gold and 271.9 grams per tonne silver over 75 centimetres in hole no.4 (Property File - R.W. 29229) from the south end of a trench located approximately 100 metres south of the adit assayed 27.40 per cent lead, 20.5 grams per tonne gold and 807.1 grams per tonne silver over 0.6 metre (Property File - R.W. In 1983, sampling yielded up to 8.2 grams per tonne gold with 26.0 grams per tonne silver over 2 metres (sample J69) from the third adit and 2.7 grams per tonne gold with 76.0 grams per tonne silver over 1.5 metres (sample J72) from the second adit, whereas sample (J64) from a shear exposed in a trench assayed 4.15 grams per tonne gold with 32.0 grams per tonne silver ov</t>
+          <t>In 1990, a chip sample (LR-3) from a trench located near the former adit and shaft yielded 9.99 per cent zinc, 2.71 per cent lead, 0.11 per cent cadmium and 5.6 grams per tonne silver over 0.50 metre, whereas a chip sample (LR-2) from the shaft assayed 8.85 per cent zinc and 2.52 per cent lead over 0.7 metre (Assessment Report 20376). In 1991, a chip sample (5963) from the shaft assayed 20.70 per cent lead, 6.24 per cent zinc and 15.0 grams per tonne silver over 0.7 metre (Assessment Report 21705). In 1993, diamond drilling yielded intercepts of up to 0.307 per cent lead over 0.3 metre in hole LB93-8 (Assessment Report 23397). In 1991, chip sampling (PR-8 and 5965) yielded from 29.38 per cent zinc over 1.5 metres to 12.82 per cent zinc over 4.0 metres, whereas grab samples (PR-3) yielded u</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P125" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Siscoe Callahan Min., Bakus, John Nick</t>
+          <t>Timmax Resources Corp., Consolidated Ramrod Gold Corp., Guinet Management Inc.; Guinet</t>
         </is>
       </c>
       <c r="R125" t="inlineStr"/>
@@ -12449,17 +12453,17 @@
         <v>50</v>
       </c>
       <c r="U125" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V125" t="n">
-        <v>49.80361</v>
+        <v>49.005</v>
       </c>
       <c r="W125" t="n">
-        <v>-117.28389</v>
+        <v>-117.18611</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW208</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW003</t>
         </is>
       </c>
     </row>
@@ -12469,30 +12473,30 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">HOPE                          </t>
+          <t>SUNRO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>082FSE044</t>
+          <t>092C  073</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Boswell</t>
+          <t>River Jordan</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Gold, Silver, Molybdenum, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -12504,58 +12508,62 @@
         <v>0</v>
       </c>
       <c r="J126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Ag 263g/t, Pb 13.4%, Zn 14.9%</t>
+          <t>Cu 1.98%</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>The best sample over 0.7 metre assayed 387 grams per tonne silver, 19.0 per cent lead and 18.7 per cent zinc; in 1990 confirmed recorded assays ranging from 0.14 to 0.47 gram per tonne gold (this would have been nil to trace in earlier assays), 77.5 to 1213 grams per tonne silver, 2.04 to 71.2 per cent lead and 1.83 to 18.1 per cent zinc. an average of three samples over a width of 0.5 metre and strike length of 20 metres was 263 grams per tonne silver, 13.4 per cent lead and 14.9 per cent zinc.</t>
+          <t>In 1973, drilling on the River “C” zone yielded 2.07 per cent copper over 2.7 metres in hole U-703 and  1.06 per cent copper over 6.9 metres in hole U-704, while a hole (U-703) near the River “A” zone yielded 1.98 per cent copper over 15.6 metres (Property File - Jordan River Mines Ltd. In 2000, a 0.25- metre grab sample (170502) from the River adit assayed 2.42 per cent copper, 8.4 grams per tonne silver and 0.57 gram per tonne gold (Property File - EMPR [2000-04-28]: Assays - Sunro). In 2004, a rock sample (S-04-AR-3) assayed greater than 1 per cent copper with 21.6 grams per tonne silver and 0.72 gram per tonne gold (Assessment Report 27472). In 1973, a sample from the Centre tunnel portal yielded 3.4 per cent copper over 2.4 metres, while diamond drilling yielded up to 2.37 per cent co</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>$60k</t>
+          <t>$122k</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P126" t="n">
-        <v>1994</v>
+        <v>2025</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Forbes Resources Ltd., Dobrana Resources Ltd.</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr"/>
+          <t>New Sunro Copper Ltd., Kikauka, Andris (FMC # 114051)</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Release Required (Conditional) (Hydro Project) — special process</t>
+        </is>
+      </c>
       <c r="S126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T126" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="U126" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V126" t="n">
-        <v>49.45333</v>
+        <v>48.44833</v>
       </c>
       <c r="W126" t="n">
-        <v>-116.71278</v>
+        <v>-124.03306</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSE044</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092C++073</t>
         </is>
       </c>
     </row>
@@ -12565,30 +12573,30 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARK                          </t>
+          <t>ALPHA-BETA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>082GNW012</t>
+          <t>092C  039</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Marysville</t>
+          <t>Mesachie Lake</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3.4</v>
+        <v>8.9</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lead, Silver</t>
+          <t>Copper, Silver, Gold, Iron</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -12604,54 +12612,54 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>11 kt</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Pb 71.00%</t>
+          <t>Cu 5.80%</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Assays indicate 100 to 200 grams of silver and from 18 to 71 per cent lead but these are probably from hand-cobbed ore material.</t>
+          <t>A high grade series of ore shoots on a parallel zone averaged 8.60 per cent copper over a 1.4 metre true width, as ascertained from 5 diamond-drill holes. In 2008, assays of tailings yielded values up to 9.1 per cent copper (Assessment Report 30705). In 2011, samples of chalcopyrite assayed 24.37 per cent copper and 27.9 per cent iron, while samples of magnetite assayed 1.62 oer cent copper and 38.25 per cent iron (Assessment Report 32286). Ore sections opened up in the mineralized area shows some continuity for nearly 120 metres underground, averaging 1.4 to 3.0 per cent copper over widths averaging 1.5 to 1.8 metres.</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>$59k</t>
+          <t>$43k</t>
         </is>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P127" t="n">
-        <v>1973</v>
+        <v>2022</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Cominco Ltd., Imperial Oil</t>
+          <t>Arbic, Dean Michael, Phillips</t>
         </is>
       </c>
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T127" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="U127" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V127" t="n">
-        <v>49.65083</v>
+        <v>48.73333</v>
       </c>
       <c r="W127" t="n">
-        <v>-115.91583</v>
+        <v>-124.09139</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082GNW012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092C++039</t>
         </is>
       </c>
     </row>
@@ -12661,30 +12669,30 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEILER (L.1369)               </t>
+          <t>IOTA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>092K  010</t>
+          <t>092HSE119</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Silver, Lead, Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -12696,62 +12704,58 @@
         <v>0</v>
       </c>
       <c r="J128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>108 t (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Au 8.9g/t</t>
+          <t>Au 0.7g/t, Ag 854g/t, Pb 0.90%</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>One sample assayed 1.0 gram per tonne gold (Minister of Mines Annual Report 1913). One 1.5 metre sample across the dip of numerous quartz stringers in greenstone assayed 8.9 grams per tonne gold (Stevenson, J.D., 1938). One chip across 30 centimetres of decomposed and oxidized shear assayed 48.0 grams per tonne gold and 0.4 per cent copper (Stevenson, J.D., 1938).</t>
+          <t>Samples comprised of limestone, containing black quartz stringers and massive quartz, assayed 233 to 854 grams per tonne silver (Minister of Mines Annual report 1947, page 147). A 0.91- metre chip sample across black quartz assayed trace gold, 854 grams per tonne silver and 0.6 per cent lead, and a 0.79-metre chip sample across black quartz and limestone breccia assayed 0.69 gram per tonne gold, 542 grams per tonne silver and 1.2 per cent lead (Minister of Mines Annual Report 1947, page 147).</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>$53k</t>
+          <t>$45k</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P128" t="n">
-        <v>2024</v>
+        <v>2008</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Kikauka, Andris (FMC # 114051), Oppelt</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>abuts Main Lake Park boundary</t>
-        </is>
-      </c>
+          <t>Cons. Sea Gold, Viscount Resources Limited, Crooker</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr"/>
       <c r="S128" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T128" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="U128" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="V128" t="n">
-        <v>50.19111</v>
+        <v>49.395</v>
       </c>
       <c r="W128" t="n">
-        <v>-125.26111</v>
+        <v>-120.105</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE119</t>
         </is>
       </c>
     </row>
@@ -12761,30 +12765,30 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t xml:space="preserve">SKYLARK &amp; RANGER              </t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>082FSW003</t>
+          <t>082FNW189</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Nelway</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>8.300000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Cadmium</t>
+          <t>Silver, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -12800,33 +12804,33 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Pb 2.52%, Zn 10.84%</t>
+          <t>Au 36.2g/t, Ag 757g/t</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>In 1990, a chip sample (LR-3) from a trench located near the former adit and shaft yielded 9.99 per cent zinc, 2.71 per cent lead, 0.11 per cent cadmium and 5.6 grams per tonne silver over 0.50 metre, whereas a chip sample (LR-2) from the shaft assayed 8.85 per cent zinc and 2.52 per cent lead over 0.7 metre (Assessment Report 20376). In 1991, a chip sample (5963) from the shaft assayed 20.70 per cent lead, 6.24 per cent zinc and 15.0 grams per tonne silver over 0.7 metre (Assessment Report 21705). In 1993, diamond drilling yielded intercepts of up to 0.307 per cent lead over 0.3 metre in hole LB93-8 (Assessment Report 23397). In 1991, chip sampling (PR-8 and 5965) yielded from 29.38 per cent zinc over 1.5 metres to 12.82 per cent zinc over 4.0 metres, whereas grab samples (PR-3) yielded u</t>
+          <t>A 20-centimetre sample assayed 36.2 grams per tonne gold and 757 grams per tonne silver (GCNL #229(Nov.25), 1985).</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$44k</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P129" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Timmax Resources Corp., Consolidated Ramrod Gold Corp., Guinet Management Inc.; Guinet</t>
+          <t>Bakus, John Nick, Julia Res.</t>
         </is>
       </c>
       <c r="R129" t="inlineStr"/>
@@ -12837,17 +12841,17 @@
         <v>25</v>
       </c>
       <c r="U129" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="V129" t="n">
-        <v>49.005</v>
+        <v>49.74056</v>
       </c>
       <c r="W129" t="n">
-        <v>-117.18611</v>
+        <v>-117.39583</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW003</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW189</t>
         </is>
       </c>
     </row>
@@ -12857,21 +12861,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SUNRO</t>
+          <t xml:space="preserve">AJAX                          </t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>092C  073</t>
+          <t>092K  116</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>River Jordan</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12880,7 +12884,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Nickel, Cobalt</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -12892,62 +12896,58 @@
         <v>0</v>
       </c>
       <c r="J130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>30 t</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Cu 1.98%</t>
+          <t>Cu 25.00%</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>In 1973, drilling on the River “C” zone yielded 2.07 per cent copper over 2.7 metres in hole U-703 and  1.06 per cent copper over 6.9 metres in hole U-704, while a hole (U-703) near the River “A” zone yielded 1.98 per cent copper over 15.6 metres (Property File - Jordan River Mines Ltd. In 2000, a 0.25- metre grab sample (170502) from the River adit assayed 2.42 per cent copper, 8.4 grams per tonne silver and 0.57 gram per tonne gold (Property File - EMPR [2000-04-28]: Assays - Sunro). In 2004, a rock sample (S-04-AR-3) assayed greater than 1 per cent copper with 21.6 grams per tonne silver and 0.72 gram per tonne gold (Assessment Report 27472). In 1973, a sample from the Centre tunnel portal yielded 3.4 per cent copper over 2.4 metres, while diamond drilling yielded up to 2.37 per cent co</t>
+          <t>About 30 tonnes of ore were taken out prior to 1902, assaying over 25 per cent copper.</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>$122k</t>
+          <t>$40k</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P130" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>New Sunro Copper Ltd., Kikauka, Andris (FMC # 114051)</t>
-        </is>
-      </c>
-      <c r="R130" t="inlineStr">
-        <is>
-          <t>Release Required (Conditional) (Hydro Project) — special process</t>
-        </is>
-      </c>
+          <t>543445 BC Ltd., Kikauka, Andris (FMC # 114051)</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr"/>
       <c r="S130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T130" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U130" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="V130" t="n">
-        <v>48.44833</v>
+        <v>50.18861</v>
       </c>
       <c r="W130" t="n">
-        <v>-124.03306</v>
+        <v>-125.30861</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092C++073</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++116</t>
         </is>
       </c>
     </row>
@@ -12957,21 +12957,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ALPHA-BETA</t>
+          <t>YOUNG</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>092C  039</t>
+          <t>082KNE022</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mesachie Lake</t>
+          <t>Castledale</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>8.9</v>
+        <v>25.9</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Iron</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -12996,54 +12996,54 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>11 kt</t>
+          <t>31 t</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Cu 5.80%</t>
+          <t>Cu 9.90%</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>A high grade series of ore shoots on a parallel zone averaged 8.60 per cent copper over a 1.4 metre true width, as ascertained from 5 diamond-drill holes. In 2008, assays of tailings yielded values up to 9.1 per cent copper (Assessment Report 30705). In 2011, samples of chalcopyrite assayed 24.37 per cent copper and 27.9 per cent iron, while samples of magnetite assayed 1.62 oer cent copper and 38.25 per cent iron (Assessment Report 32286). Ore sections opened up in the mineralized area shows some continuity for nearly 120 metres underground, averaging 1.4 to 3.0 per cent copper over widths averaging 1.5 to 1.8 metres.</t>
+          <t>Hole B5 intersected 12 metres yielding 0.46 per cent copper (Property File - A.C.A Howe [1966-10-20]: Report on the Westgate Mines Ltd. In 1967, a channel sample from the Middle Lead assayed 0.90 per cent copper over 3.6 metres, while a grab sample from the Upper Lead yielded up to 9.90 per cent copper (Property File - S.J.</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>$43k</t>
+          <t>$40k</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P131" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Arbic, Dean Michael, Phillips</t>
+          <t>Palermo Res., Kobi, Daniel Harold</t>
         </is>
       </c>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T131" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U131" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="V131" t="n">
-        <v>48.73333</v>
+        <v>50.83</v>
       </c>
       <c r="W131" t="n">
-        <v>-124.09139</v>
+        <v>-116.73444</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092C++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNE022</t>
         </is>
       </c>
     </row>
@@ -13053,30 +13053,30 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>IOTA</t>
+          <t xml:space="preserve">LANARK (L.1592A)              </t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>092HSE119</t>
+          <t>082N  012</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Flat Creek</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper</t>
+          <t>Lead, Silver, Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -13092,54 +13092,54 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Ag 854g/t, Pb 0.90%</t>
+          <t>Ag 504.9g/t, Pb 11.5%, Zn 15.3%</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Samples comprised of limestone, containing black quartz stringers and massive quartz, assayed 233 to 854 grams per tonne silver (Minister of Mines Annual report 1947, page 147). A 0.91- metre chip sample across black quartz assayed trace gold, 854 grams per tonne silver and 0.6 per cent lead, and a 0.79-metre chip sample across black quartz and limestone breccia assayed 0.69 gram per tonne gold, 542 grams per tonne silver and 1.2 per cent lead (Minister of Mines Annual Report 1947, page 147).</t>
+          <t>A channel sample across 0.33 metre of massive galena from a trench in the vicinity of the Lanark shaft analysed 504.9 grams per tonne silver, 15.3 per cent zinc and 11.5 per cent lead.</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>$45k</t>
+          <t>$39k</t>
         </is>
       </c>
       <c r="O132" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="P132" t="n">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Cons. Sea Gold, Viscount Resources Limited, Crooker</t>
+          <t>Adrian Resources Ltd., Liberty International Mineral Corp, 0911325 BC Ltd.</t>
         </is>
       </c>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T132" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="U132" t="n">
         <v>54</v>
       </c>
       <c r="V132" t="n">
-        <v>49.395</v>
+        <v>51.2225</v>
       </c>
       <c r="W132" t="n">
-        <v>-120.105</v>
+        <v>-117.73139</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE119</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082N++012</t>
         </is>
       </c>
     </row>
@@ -13149,30 +13149,30 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMBRIAN CHIEFTAN             </t>
+          <t xml:space="preserve">BIG SLIDE                     </t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>092GNW011</t>
+          <t>092INW036</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Doriston</t>
+          <t>Hilltop</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -13188,38 +13188,38 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>1 kt (assay)</t>
+          <t>7 kt (indicated)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Ag 106g/t, Cu 9.4%, Zn 0.5%</t>
+          <t>Ag 42.1g/t, Au 16.2g/t</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>A chip sample taken across a width of 4.6 metres assayed 5.8 grams per tonne silver, 0.19 per cent copper and 13.5 per cent zinc (Assessment Report 3757, Map 2, Sample 2).</t>
+          <t>Material taken by Dawson from the concentrates assayed 13.9 grams per tonne gold and 31.9 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>$44k</t>
+          <t>$37k</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P133" t="n">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Markevitch, J., Sauer</t>
+          <t>Ashworth Explorations Ltd., Gust, Nicholas</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Conditional Registration Reserve (Trans. Line) — special process · abuts Spipiyus Park boundary</t>
+          <t>abuts Edge Hills Park boundary</t>
         </is>
       </c>
       <c r="S133" t="n">
@@ -13232,14 +13232,14 @@
         <v>54</v>
       </c>
       <c r="V133" t="n">
-        <v>49.68139</v>
+        <v>50.95611</v>
       </c>
       <c r="W133" t="n">
-        <v>-123.93944</v>
+        <v>-121.86806</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNW011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092INW036</t>
         </is>
       </c>
     </row>
@@ -13249,21 +13249,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKYLARK &amp; RANGER              </t>
+          <t xml:space="preserve">COMSTOCK-VIRGINIA             </t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>082FNW189</t>
+          <t>082FNW080</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -13288,33 +13288,33 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>5 t (assay)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Au 36.2g/t, Ag 757g/t</t>
+          <t>Ag 9052g/t, Pb 28.9%, Zn 29.1%</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>A 20-centimetre sample assayed 36.2 grams per tonne gold and 757 grams per tonne silver (GCNL #229(Nov.25), 1985).</t>
+          <t>A grab sample taken from the middle adit assayed 9052 grams per tonne silver, 28.9 per cent lead and 29.1 per cent zinc (Property File - Ash, W.M., 1988).</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>$44k</t>
+          <t>$37k</t>
         </is>
       </c>
       <c r="O134" t="n">
         <v>3</v>
       </c>
       <c r="P134" t="n">
-        <v>2025</v>
+        <v>1989</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Bakus, John Nick, Julia Res.</t>
+          <t>Canfic Silver Mines Ltd., Nautilus Resources Ltd., South Kootenay Goldfields Inc.</t>
         </is>
       </c>
       <c r="R134" t="inlineStr"/>
@@ -13328,14 +13328,14 @@
         <v>54</v>
       </c>
       <c r="V134" t="n">
-        <v>49.74056</v>
+        <v>49.9175</v>
       </c>
       <c r="W134" t="n">
-        <v>-117.39583</v>
+        <v>-117.16333</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW189</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW080</t>
         </is>
       </c>
     </row>
@@ -13345,30 +13345,30 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAJOR                         </t>
+          <t xml:space="preserve">PAVILION                      </t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>092L  149</t>
+          <t>092INW083</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Zeballos</t>
+          <t>Moran</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>9.6</v>
+        <v>3.1</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Cobalt</t>
+          <t>Gold, Silver, Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -13384,54 +13384,54 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Au 16.0g/t</t>
+          <t>Ag 15g/t, Au 2.02g/t, Cu 1.1%, Pb 0.5%, Zn 12.6%</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>In 1938, a sample from the lower vein assayed 4.4 grams per tonne gold over 0.3 metre (Property File - C.C. In 1940, a selected sample assayed 16.0 grams per tonne gold (GSC Paper 40-12, page 36). In 1995, a float sample (599534) assayed 0.46 gram per tonne gold, 2.8 grams per tonne silver and 0.188 per cent copper, whereas another float sample (599537) assayed 0.326 per cent copper and 0.196 per cent cobalt (Assessment Report 24184).</t>
+          <t>During shaft sinking operations, an intersection assaying 68.5 grams per tonne gold over 0.9 metre was reported.</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>$42k</t>
+          <t>$30k</t>
         </is>
       </c>
       <c r="O135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P135" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>640895 BC Ltd., A25 Gold Producers Corp.; Global Silver Producers Ltd., Orvana Minerals Corp.</t>
+          <t>Ashworth Explorations Ltd., Amey, William Larry</t>
         </is>
       </c>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T135" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U135" t="n">
         <v>54</v>
       </c>
       <c r="V135" t="n">
-        <v>50.03472</v>
+        <v>50.94389</v>
       </c>
       <c r="W135" t="n">
-        <v>-126.73944</v>
+        <v>-121.86028</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++149</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092INW083</t>
         </is>
       </c>
     </row>
@@ -13441,21 +13441,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">AJAX                          </t>
+          <t xml:space="preserve">HUMMING BIRD (L.4815A)        </t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>092K  116</t>
+          <t>092K  047</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>toqʷanan</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5</v>
+        <v>14.4</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -13480,54 +13480,54 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>30 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Cu 25.00%</t>
+          <t>Ag 320.175g/t, Cu 17.4%</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>About 30 tonnes of ore were taken out prior to 1902, assaying over 25 per cent copper.</t>
+          <t>In 1983, a chip sample over unknown length assayed 17.40 per cent copper and 320.17 grams per tonne silver (Assessment Report 11884). One hundred and forty tonnes of ore are quoted as being mined and shipped several years before 1928 assaying 8 to 11 per cent copper, 240 to 685 grams per tonne silver and minor gold (Minister of Mines Annual Report 1928).</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>$40k</t>
+          <t>$25k</t>
         </is>
       </c>
       <c r="O136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P136" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>543445 BC Ltd., Kikauka, Andris (FMC # 114051)</t>
+          <t>Corinth Resources Ltd., Delisle, Denis</t>
         </is>
       </c>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U136" t="n">
         <v>54</v>
       </c>
       <c r="V136" t="n">
-        <v>50.18861</v>
+        <v>50.085</v>
       </c>
       <c r="W136" t="n">
-        <v>-125.30861</v>
+        <v>-124.4475</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++116</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++047</t>
         </is>
       </c>
     </row>
@@ -13537,30 +13537,30 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YOUNG</t>
+          <t>ELIZA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>082KNE022</t>
+          <t>092E  043</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Castledale</t>
+          <t>Queens Cove</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>25.9</v>
+        <v>3.1</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -13576,54 +13576,54 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>31 t</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Cu 9.90%</t>
+          <t>Au 55.7g/t, Ag 21.0g/t</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Hole B5 intersected 12 metres yielding 0.46 per cent copper (Property File - A.C.A Howe [1966-10-20]: Report on the Westgate Mines Ltd. In 1967, a channel sample from the Middle Lead assayed 0.90 per cent copper over 3.6 metres, while a grab sample from the Upper Lead yielded up to 9.90 per cent copper (Property File - S.J.</t>
+          <t>In 1938, surface sampling of a stringer zone in the hangingwall assayed up to 771.1 grams per tonne gold over 0.1 metres (Sanft, G.F. In 1986, sampling of the Upper zone yielded values from 8.3 to 55.7 grams per tonne gold and 2.3 to 21.0 grams per tonne silver over widths from 0.1 to 0.5 metres (Assessment Report 14796). Both channel samples returned significant results: Chip 1 returned 24.9 grams per tonne gold and 16.4 silver over an approximate vein width of 0.6 metres; and Channel two returned 4.3 grams per tonne gold over an approximate 1.2 metres.</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>$40k</t>
+          <t>$24k</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P137" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Palermo Res., Kobi, Daniel Harold</t>
+          <t>Harlingten, Caisey, HQ Minerals Ltd.</t>
         </is>
       </c>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T137" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U137" t="n">
         <v>54</v>
       </c>
       <c r="V137" t="n">
-        <v>50.83</v>
+        <v>49.89222</v>
       </c>
       <c r="W137" t="n">
-        <v>-116.73444</v>
+        <v>-127.02583</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNE022</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++043</t>
         </is>
       </c>
     </row>
@@ -13633,30 +13633,30 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">LANARK (L.1592A)              </t>
+          <t xml:space="preserve">WHITE ELEPHANT (L. 4880)      </t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>082N  012</t>
+          <t>082LSW042</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Flat Creek</t>
+          <t>Fintry</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold, Copper</t>
+          <t>Gold, Silver, Bismuth, Tellurium, Tungsten</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -13672,54 +13672,54 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>5 kt</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Ag 504.9g/t, Pb 11.5%, Zn 15.3%</t>
+          <t>Au 12.7g/t</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>A channel sample across 0.33 metre of massive galena from a trench in the vicinity of the Lanark shaft analysed 504.9 grams per tonne silver, 15.3 per cent zinc and 11.5 per cent lead.</t>
+          <t>In 1988, a 1.0 metre chip sample (31839) from a quartz body containing a 0.5 metre sulphide bleb assayed 51.98 grams per tonne gold, 10.9 grams per tonne silver and 0.136 per cent bismuth, whereas grab samples from a dump pile yielded up to 35.6 grams per tonne gold and 27.0 grams per tonne silver (Property File - C.J. Prior to closing, in 1935, underground development on the 300-foot level is reported to have averaged 12.7 grams per tonne gold over 2.1 metres (Property File - C.J.</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>$39k</t>
+          <t>$21k</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P138" t="n">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Adrian Resources Ltd., Liberty International Mineral Corp, 0911325 BC Ltd.</t>
+          <t>Hurd, Daniel Gordon; Langille, Micheal Scott; Sebastien Latour; Wright</t>
         </is>
       </c>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T138" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U138" t="n">
         <v>54</v>
       </c>
       <c r="V138" t="n">
-        <v>51.2225</v>
+        <v>50.14806</v>
       </c>
       <c r="W138" t="n">
-        <v>-117.73139</v>
+        <v>-119.55694</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082N++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW042</t>
         </is>
       </c>
     </row>
@@ -13729,30 +13729,30 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIG SLIDE                     </t>
+          <t>SILVER BELL (L.4329)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>092INW036</t>
+          <t>082LSE011</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Hilltop</t>
+          <t>Cherryville</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4.3</v>
+        <v>13.4</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Silver, Gold, Lead, Copper, Zinc</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -13764,62 +13764,58 @@
         <v>0</v>
       </c>
       <c r="J139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>7 kt (indicated)</t>
+          <t>14 t</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Ag 42.1g/t, Au 16.2g/t</t>
+          <t>Au 51.5g/t, Ag 433g/t</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Material taken by Dawson from the concentrates assayed 13.9 grams per tonne gold and 31.9 grams per tonne silver.</t>
+          <t>The pay streak is up to 30 centimetres wide and samples have assayed as high as 20,568 grams per tonne silver and 69 grams per tonne gold (Minister of Mines Annual Report 1914, page 360). A grab sample taken in assayed 297.6 grams per tonne silver and 34.0 grams per tonne gold (Assessment Report 23401).</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>$37k</t>
+          <t>$18k</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P139" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Ashworth Explorations Ltd., Gust, Nicholas</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>abuts Edge Hills Park boundary</t>
-        </is>
-      </c>
+          <t>Crowe, G.G., Mielniczuk</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T139" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U139" t="n">
         <v>54</v>
       </c>
       <c r="V139" t="n">
-        <v>50.95611</v>
+        <v>50.20111</v>
       </c>
       <c r="W139" t="n">
-        <v>-121.86806</v>
+        <v>-118.4275</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092INW036</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE011</t>
         </is>
       </c>
     </row>
@@ -13829,30 +13825,30 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMSTOCK-VIRGINIA             </t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>082FNW080</t>
+          <t>092K  018</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Thurlow</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -13868,54 +13864,54 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>5 t (assay)</t>
+          <t>383 t</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Ag 9052g/t, Pb 28.9%, Zn 29.1%</t>
+          <t>Au 39.1g/t, Ag 151g/t, Cu 3.27%</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>A grab sample taken from the middle adit assayed 9052 grams per tonne silver, 28.9 per cent lead and 29.1 per cent zinc (Property File - Ash, W.M., 1988).</t>
+          <t>A 1936 assay from massive pyrite was 189.91 grams per tonne gold and 150.83 grams per tonne silver. Another assay of mixed chalcopyrite and pyrite with a little quartz was 39.08 grams per tonne gold, 246.82 grams per tonne silver and 6.5 per cent copper (Minister of Mines Annual Report 1936, page F21). In 1980 a grab sample of mostly quartz with some pyrite from a dump assayed 4.11 grams per tonne gold, 4.80 grams per tonne silver and 0.05 per cent copper (Assessment Report 7959).</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>$37k</t>
+          <t>$14k</t>
         </is>
       </c>
       <c r="O140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P140" t="n">
-        <v>1989</v>
+        <v>1980</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Canfic Silver Mines Ltd., Nautilus Resources Ltd., South Kootenay Goldfields Inc.</t>
+          <t>Grandora Ex., Chinook Construction and Engineering Ltd.</t>
         </is>
       </c>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T140" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U140" t="n">
         <v>54</v>
       </c>
       <c r="V140" t="n">
-        <v>49.9175</v>
+        <v>50.41472</v>
       </c>
       <c r="W140" t="n">
-        <v>-117.16333</v>
+        <v>-125.33972</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW080</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++018</t>
         </is>
       </c>
     </row>
@@ -13925,21 +13921,21 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAVILION                      </t>
+          <t xml:space="preserve">LOUGHBOROUGH GOLD             </t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>092INW083</t>
+          <t>092K  048</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Moran</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13948,7 +13944,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead, Zinc</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -13969,49 +13965,49 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Au 2.02g/t, Cu 1.1%, Pb 0.5%, Zn 12.6%</t>
+          <t>Ag 137.12g/t, Au 26.7384g/t</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>During shaft sinking operations, an intersection assaying 68.5 grams per tonne gold over 0.9 metre was reported.</t>
+          <t>The sample assayed 26.74 grams per tonne gold and 137.12 grams per tonne silver over 91 centimetres (Minister of Mines Annual Report 1936, page F19).</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>$30k</t>
+          <t>$10k</t>
         </is>
       </c>
       <c r="O141" t="n">
         <v>3</v>
       </c>
       <c r="P141" t="n">
-        <v>2012</v>
+        <v>1986</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Ashworth Explorations Ltd., Amey, William Larry</t>
+          <t>Iron River Resources Ltd., Triako Int. Ent., Medalion Mines</t>
         </is>
       </c>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T141" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U141" t="n">
         <v>54</v>
       </c>
       <c r="V141" t="n">
-        <v>50.94389</v>
+        <v>50.52833</v>
       </c>
       <c r="W141" t="n">
-        <v>-121.86028</v>
+        <v>-125.52194</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092INW083</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++048</t>
         </is>
       </c>
     </row>
@@ -14021,30 +14017,30 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMMING BIRD (L.4815A)        </t>
+          <t xml:space="preserve">SILVER HILL (L.2852)          </t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>092K  047</t>
+          <t>082FNE084</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>toqʷanan</t>
+          <t>Gray Creek</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>14.4</v>
+        <v>13</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Silver, Lead, Zinc, Copper, Gold, Antimony</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -14060,33 +14056,33 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>2 kt</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Ag 320.175g/t, Cu 17.4%</t>
+          <t>Ag 1180g/t, Cu 1.50%, Pb 5.80%, Zn 5.10%</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>In 1983, a chip sample over unknown length assayed 17.40 per cent copper and 320.17 grams per tonne silver (Assessment Report 11884). One hundred and forty tonnes of ore are quoted as being mined and shipped several years before 1928 assaying 8 to 11 per cent copper, 240 to 685 grams per tonne silver and minor gold (Minister of Mines Annual Report 1928).</t>
+          <t>In 2008, 11 samples averaged 1179.8 grams per tonne silver, 1.5 per cent copper, 5.8 per cent lead and 5.1 per cent zinc, while a 20- centimetre wide sample (52007) of vein material from the adit assayed 5732.9 grams per tonne silver, 0.68 grams per tonne gold, 9.47 per cent copper, 10.69 per cent lead, 3.25 per cent zinc and 2.40 per cent antimony (Assessment Report 30211). A sample from the second vein assayed 428.3 grams per tonne silver,  3.14 per cent lead, 0.24 per cent copper and 0.13 per cent zinc (Assessment Report 30211).</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>$25k</t>
+          <t>$7k</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P142" t="n">
-        <v>2025</v>
+        <v>2008</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Corinth Resources Ltd., Delisle, Denis</t>
+          <t>Kent Explorations Inc</t>
         </is>
       </c>
       <c r="R142" t="inlineStr"/>
@@ -14100,14 +14096,14 @@
         <v>54</v>
       </c>
       <c r="V142" t="n">
-        <v>50.085</v>
+        <v>49.70972</v>
       </c>
       <c r="W142" t="n">
-        <v>-124.4475</v>
+        <v>-116.64917</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++047</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE084</t>
         </is>
       </c>
     </row>
@@ -14117,21 +14113,21 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ELIZA</t>
+          <t>DOUGLAS PINE (L.271)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>092E  043</t>
+          <t>092K  035</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Queens Cove</t>
+          <t>Thurlow</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14156,54 +14152,54 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>310 t</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Au 55.7g/t, Ag 21.0g/t</t>
+          <t>Au 3.6g/t, Ag 24.6g/t, Cu 0.25%</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>In 1938, surface sampling of a stringer zone in the hangingwall assayed up to 771.1 grams per tonne gold over 0.1 metres (Sanft, G.F. In 1986, sampling of the Upper zone yielded values from 8.3 to 55.7 grams per tonne gold and 2.3 to 21.0 grams per tonne silver over widths from 0.1 to 0.5 metres (Assessment Report 14796). Both channel samples returned significant results: Chip 1 returned 24.9 grams per tonne gold and 16.4 silver over an approximate vein width of 0.6 metres; and Channel two returned 4.3 grams per tonne gold over an approximate 1.2 metres.</t>
+          <t>An assay of 34.28 grams per tonne gold, 47.992 grams per tonne silver and 0.15 per cent copper is recorded from a channel sample across 47.72 centimetres (Property File, O'Grady, B.T., 1936). In 1982, a dump sample assayed 133.4 grams per tonne gold, while an underground sample, from the 285 metre adit, assayed 34.2 grams per tonne gold (Assessment Report 11608). In 1983, eleven samples from the 285 metre level adit yielded an average of 0.06 per cent copper, 33.3 grams per tonne silver and 2.06 grams per tonne gold over a width of 1.27 metres. At the same time, seven samples from the 305 metre level adit yielded an average of 0.447 per cent copper, 16 grams per tonne silver and 3.58 grams per tonne gold (Assessment Report 11608).</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>$24k</t>
+          <t>$7k</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P143" t="n">
-        <v>2016</v>
+        <v>1983</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Harlingten, Caisey, HQ Minerals Ltd.</t>
+          <t>Amalgamated Mining Western Ltd.</t>
         </is>
       </c>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T143" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="U143" t="n">
         <v>54</v>
       </c>
       <c r="V143" t="n">
-        <v>49.89222</v>
+        <v>50.45194</v>
       </c>
       <c r="W143" t="n">
-        <v>-127.02583</v>
+        <v>-125.35528</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++043</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++035</t>
         </is>
       </c>
     </row>
@@ -14213,30 +14209,30 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WHITE ELEPHANT (L. 4880)      </t>
+          <t>CORDILLERA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>082LSW042</t>
+          <t>103I  040</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Fintry</t>
+          <t>Usk</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Gold, Silver, Bismuth, Tellurium, Tungsten</t>
+          <t>Copper, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -14252,33 +14248,33 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>5 kt</t>
+          <t>73 t</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Au 12.7g/t</t>
+          <t>Au 6.6g/t, Ag 94.0g/t, Cu 3.90%</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>In 1988, a 1.0 metre chip sample (31839) from a quartz body containing a 0.5 metre sulphide bleb assayed 51.98 grams per tonne gold, 10.9 grams per tonne silver and 0.136 per cent bismuth, whereas grab samples from a dump pile yielded up to 35.6 grams per tonne gold and 27.0 grams per tonne silver (Property File - C.J. Prior to closing, in 1935, underground development on the 300-foot level is reported to have averaged 12.7 grams per tonne gold over 2.1 metres (Property File - C.J.</t>
+          <t>A 1.0-metre sample of one vein assayed 13.7 grams per tonne gold, 130.3 grams per tonne silver and 7.1 per cent copper (Geological Survey of Canada Summary Report 1925A). The resultant weight-corrected average grade returned 6.64 grams per tonne gold, 94.0 grams per tonne silver and 3.9 per cent copper, which is similar in grade and composition to the weight-corrected average grade result obtained from the Lucky Luke (103I 039) ore dump 820 metres southwest (Press Release - Argonaut Exploration Inc., December 14, 2012).</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>$21k</t>
+          <t>$7k</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P144" t="n">
-        <v>2025</v>
+        <v>1989</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Hurd, Daniel Gordon; Langille, Micheal Scott; Sebastien Latour; Wright</t>
+          <t>Kelly Creek Resources</t>
         </is>
       </c>
       <c r="R144" t="inlineStr"/>
@@ -14292,14 +14288,14 @@
         <v>54</v>
       </c>
       <c r="V144" t="n">
-        <v>50.14806</v>
+        <v>54.62889</v>
       </c>
       <c r="W144" t="n">
-        <v>-119.55694</v>
+        <v>-128.43917</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW042</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103I++040</t>
         </is>
       </c>
     </row>
@@ -14309,30 +14305,30 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SILVER BELL (L.4329)</t>
+          <t xml:space="preserve">LUCKY LUKE (L.7424)           </t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>082LSE011</t>
+          <t>103I  039</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Cherryville</t>
+          <t>Usk</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>13.4</v>
+        <v>2.7</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Copper, Zinc</t>
+          <t>Copper, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -14348,54 +14344,54 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>14 t</t>
+          <t>90 t</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Au 51.5g/t, Ag 433g/t</t>
+          <t>Au 29.4g/t, Ag 69.0g/t, Cu 2.78%</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>The pay streak is up to 30 centimetres wide and samples have assayed as high as 20,568 grams per tonne silver and 69 grams per tonne gold (Minister of Mines Annual Report 1914, page 360). A grab sample taken in assayed 297.6 grams per tonne silver and 34.0 grams per tonne gold (Assessment Report 23401).</t>
+          <t>A 51-centimetre channel sample of schist assayed 8.9 grams per tonne gold and 57.7 grams per tonne silver, and a 1.6-kilogram sample from an old ore bin assayed 50 grams per tonne gold, 80.2 grams per tonne silver and 2.78 per cent copper (Geological Survey of Canada Memoir 205).</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>$18k</t>
+          <t>$6k</t>
         </is>
       </c>
       <c r="O145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P145" t="n">
-        <v>2023</v>
+        <v>1967</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Crowe, G.G., Mielniczuk</t>
+          <t>New Gold Star Mines</t>
         </is>
       </c>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T145" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U145" t="n">
         <v>54</v>
       </c>
       <c r="V145" t="n">
-        <v>50.20111</v>
+        <v>54.62194</v>
       </c>
       <c r="W145" t="n">
-        <v>-118.4275</v>
+        <v>-128.44333</v>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103I++039</t>
         </is>
       </c>
     </row>
@@ -14405,21 +14401,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>BOWENA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>092K  018</t>
+          <t>092GSW004</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Thurlow</t>
+          <t>Seymour Landing</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14428,7 +14424,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -14444,54 +14440,54 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>383 t</t>
+          <t>54 t</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Au 39.1g/t, Ag 151g/t, Cu 3.27%</t>
+          <t>Au 4.1g/t, Ag 39.8g/t, Cu 3.38%</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>A 1936 assay from massive pyrite was 189.91 grams per tonne gold and 150.83 grams per tonne silver. Another assay of mixed chalcopyrite and pyrite with a little quartz was 39.08 grams per tonne gold, 246.82 grams per tonne silver and 6.5 per cent copper (Minister of Mines Annual Report 1936, page F21). In 1980 a grab sample of mostly quartz with some pyrite from a dump assayed 4.11 grams per tonne gold, 4.80 grams per tonne silver and 0.05 per cent copper (Assessment Report 7959).</t>
+          <t>In 1917, a trial shipment of about 9 tonnes of sorted ore assayed 3.38 per cent copper, 39.77 grams per tonne silver and 4.11 grams per tonne gold (Minister of Mines Annual Report 1917, page 297).</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>$14k</t>
+          <t>$5k</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P146" t="n">
-        <v>1980</v>
+        <v>1967</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Grandora Ex., Chinook Construction and Engineering Ltd.</t>
+          <t>Concorde Ex.</t>
         </is>
       </c>
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T146" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U146" t="n">
         <v>54</v>
       </c>
       <c r="V146" t="n">
-        <v>50.41472</v>
+        <v>49.35917</v>
       </c>
       <c r="W146" t="n">
-        <v>-125.33972</v>
+        <v>-123.33889</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++018</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GSW004</t>
         </is>
       </c>
     </row>
@@ -14501,30 +14497,30 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOUGHBOROUGH GOLD             </t>
+          <t xml:space="preserve">GRIDIRON                      </t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>092K  048</t>
+          <t>104M  001</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Pavey</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Silver, Gold, Lead, Arsenic, Zinc</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -14540,54 +14536,54 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>68 t</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Ag 137.12g/t, Au 26.7384g/t</t>
+          <t>Au 3.2g/t, Ag 315g/t, Pb 2.05%, As 1.34%</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>The sample assayed 26.74 grams per tonne gold and 137.12 grams per tonne silver over 91 centimetres (Minister of Mines Annual Report 1936, page F19).</t>
+          <t>A sample of the quartz vein taken in 1982 assayed 3.2 grams per tonne gold, 315 grams per tonne silver, 2.05 per cent lead and 1.34 per cent arsenic (Assessment Report 10425).</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>$10k</t>
+          <t>$5k</t>
         </is>
       </c>
       <c r="O147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P147" t="n">
-        <v>1986</v>
+        <v>2020</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Iron River Resources Ltd., Triako Int. Ent., Medalion Mines</t>
+          <t>Rosenblat, Robert Samuel</t>
         </is>
       </c>
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T147" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="U147" t="n">
         <v>54</v>
       </c>
       <c r="V147" t="n">
-        <v>50.52833</v>
+        <v>59.93222</v>
       </c>
       <c r="W147" t="n">
-        <v>-125.52194</v>
+        <v>-134.93944</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++048</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104M++001</t>
         </is>
       </c>
     </row>
@@ -14597,21 +14593,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER HILL (L.2852)          </t>
+          <t>MOLLY HUGHES (L.2106)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>082FNE084</t>
+          <t>082KSW002</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Gray Creek</t>
+          <t>New Denver</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>13</v>
+        <v>1.5</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14620,7 +14616,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper, Gold, Antimony</t>
+          <t>Silver, Lead, Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -14636,54 +14632,54 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2 kt</t>
+          <t>9 kt (inferred)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Ag 1180g/t, Cu 1.50%, Pb 5.80%, Zn 5.10%</t>
+          <t>Ag 1282.4g/t, Au 5.8g/t</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>In 2008, 11 samples averaged 1179.8 grams per tonne silver, 1.5 per cent copper, 5.8 per cent lead and 5.1 per cent zinc, while a 20- centimetre wide sample (52007) of vein material from the adit assayed 5732.9 grams per tonne silver, 0.68 grams per tonne gold, 9.47 per cent copper, 10.69 per cent lead, 3.25 per cent zinc and 2.40 per cent antimony (Assessment Report 30211). A sample from the second vein assayed 428.3 grams per tonne silver,  3.14 per cent lead, 0.24 per cent copper and 0.13 per cent zinc (Assessment Report 30211).</t>
+          <t>Inferred ore reserves of 9072 tonnes at a grade of 5.8 grams per tonne gold and 1282 grams per tonne silver were estimated by Sadlier-Brown and Nevin (1978), based on a sampling program, assuming a deposit dimension of 122 by 122 by 0.2 metres, and allowing for dilution over a 1.2-metre mining width.</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>$7k</t>
+          <t>$3k</t>
         </is>
       </c>
       <c r="O148" t="n">
         <v>1</v>
       </c>
       <c r="P148" t="n">
-        <v>2008</v>
+        <v>1973</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Kent Explorations Inc</t>
+          <t>Dyke Mines</t>
         </is>
       </c>
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T148" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="U148" t="n">
         <v>54</v>
       </c>
       <c r="V148" t="n">
-        <v>49.70972</v>
+        <v>50.00472</v>
       </c>
       <c r="W148" t="n">
-        <v>-116.64917</v>
+        <v>-117.38056</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE084</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW002</t>
         </is>
       </c>
     </row>
@@ -14693,30 +14689,30 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DOUGLAS PINE (L.271)</t>
+          <t xml:space="preserve">EMPIRE                        </t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>092K  035</t>
+          <t>093L  116</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Thurlow</t>
+          <t>Lake Kathlyn</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Silver, Lead, Zinc, Gold, Copper, Cadmium, Antimony</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -14732,54 +14728,54 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>310 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Au 3.6g/t, Ag 24.6g/t, Cu 0.25%</t>
+          <t>Ag 1449.9g/t, Au 1.02g/t, Cad 0.01%, Cu 0.44%, Pb 6.14%</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>An assay of 34.28 grams per tonne gold, 47.992 grams per tonne silver and 0.15 per cent copper is recorded from a channel sample across 47.72 centimetres (Property File, O'Grady, B.T., 1936). In 1982, a dump sample assayed 133.4 grams per tonne gold, while an underground sample, from the 285 metre adit, assayed 34.2 grams per tonne gold (Assessment Report 11608). In 1983, eleven samples from the 285 metre level adit yielded an average of 0.06 per cent copper, 33.3 grams per tonne silver and 2.06 grams per tonne gold over a width of 1.27 metres. At the same time, seven samples from the 305 metre level adit yielded an average of 0.447 per cent copper, 16 grams per tonne silver and 3.58 grams per tonne gold (Assessment Report 11608).</t>
+          <t>A selected high grade sample of galena and sphalerite from the 30 centimetre wide quartz vein assayed 2.05 grams per tonne gold, 7096 grams per tonne silver, 25.3 per cent lead, and 18.6 per cent zinc (1914) (Minister of Mines Annual Report 1914, page 225). In 1986, five chip samples were collected and assayed 0.6 to 3.3 grams per tonne gold, 57.9 to 1450 grams per tonne silver, 0.32 to 9.74 per cent lead, 0.22 to 8.47 per cent zinc with minor copper and cadmium values (Assessment Report 15140). In 1986, three chip samples were taken across the vein as well as a high grade sample from the dump and assays ranged between 1.03 to 4.46 grams per tonne gold, 213.9 to 1292 grams per tonne silver, 7.5 to 36.67 per cent lead, 10.49 to 34.01 per cent zinc, 0.26 to 0.36 per cent copper, 0.07 to 0.23</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>$7k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O149" t="n">
         <v>1</v>
       </c>
       <c r="P149" t="n">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Amalgamated Mining Western Ltd.</t>
+          <t>Holland, Robert</t>
         </is>
       </c>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T149" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="U149" t="n">
         <v>54</v>
       </c>
       <c r="V149" t="n">
-        <v>50.45194</v>
+        <v>54.78333</v>
       </c>
       <c r="W149" t="n">
-        <v>-125.35528</v>
+        <v>-127.28222</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++035</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++116</t>
         </is>
       </c>
     </row>
@@ -14789,30 +14785,30 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CORDILLERA</t>
+          <t xml:space="preserve">PORTO RICO (L.2385)           </t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>103I  040</t>
+          <t>082FSW189</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Usk</t>
+          <t>Porto Rico</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Tungsten</t>
+          <t>Gold, Silver, Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -14828,33 +14824,33 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>73 t</t>
+          <t>6 kt</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Au 6.6g/t, Ag 94.0g/t, Cu 3.90%</t>
+          <t>Au 24.3g/t, Ag 3.8g/t</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>A 1.0-metre sample of one vein assayed 13.7 grams per tonne gold, 130.3 grams per tonne silver and 7.1 per cent copper (Geological Survey of Canada Summary Report 1925A). The resultant weight-corrected average grade returned 6.64 grams per tonne gold, 94.0 grams per tonne silver and 3.9 per cent copper, which is similar in grade and composition to the weight-corrected average grade result obtained from the Lucky Luke (103I 039) ore dump 820 metres southwest (Press Release - Argonaut Exploration Inc., December 14, 2012).</t>
+          <t>Samples assayed 11.65 to 24.34 grams per tonne gold and 3.42 to 3.77 grams per tonne silver (Assessment Report 7702).</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>$7k</t>
+          <t>$525</t>
         </is>
       </c>
       <c r="O150" t="n">
         <v>1</v>
       </c>
       <c r="P150" t="n">
-        <v>1989</v>
+        <v>1979</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Kelly Creek Resources</t>
+          <t>Mirko, John M.</t>
         </is>
       </c>
       <c r="R150" t="inlineStr"/>
@@ -14865,17 +14861,17 @@
         <v>25</v>
       </c>
       <c r="U150" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="V150" t="n">
-        <v>54.62889</v>
+        <v>49.3175</v>
       </c>
       <c r="W150" t="n">
-        <v>-128.43917</v>
+        <v>-117.32528</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103I++040</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW189</t>
         </is>
       </c>
     </row>
@@ -14885,30 +14881,30 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCKY LUKE (L.7424)           </t>
+          <t xml:space="preserve">BALTIMORE (L.10060)           </t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>103I  039</t>
+          <t>082FNW109</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Usk</t>
+          <t>Mirror Lake</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2.7</v>
+        <v>13</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Tungsten</t>
+          <t>Silver, Lead, Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -14920,58 +14916,52 @@
         <v>0</v>
       </c>
       <c r="J151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>90 t</t>
+          <t>60 t (assay)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Au 29.4g/t, Ag 69.0g/t, Cu 2.78%</t>
+          <t>Ag 2600g/t, Au 1.1g/t, Pb 1.24%, Zn 1.4%, Cu 0.0577%</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>A 51-centimetre channel sample of schist assayed 8.9 grams per tonne gold and 57.7 grams per tonne silver, and a 1.6-kilogram sample from an old ore bin assayed 50 grams per tonne gold, 80.2 grams per tonne silver and 2.78 per cent copper (Geological Survey of Canada Memoir 205).</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>$6k</t>
-        </is>
-      </c>
+          <t>A sample of the vein assayed 2600 grams per tonne silver, 1.1 grams per tonne gold, 1.24 per cent lead, 1.4 per cent zinc and 0.0577 per cent coppper (Open File 1988-11).</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>abuts Kokanee Glacier Park boundary</t>
+        </is>
+      </c>
+      <c r="S151" t="n">
         <v>1</v>
       </c>
-      <c r="P151" t="n">
-        <v>1967</v>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>New Gold Star Mines</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="n">
-        <v>2</v>
-      </c>
       <c r="T151" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U151" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="V151" t="n">
-        <v>54.62194</v>
+        <v>49.81444</v>
       </c>
       <c r="W151" t="n">
-        <v>-128.44333</v>
+        <v>-117.05472</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103I++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW109</t>
         </is>
       </c>
     </row>
@@ -14981,21 +14971,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">GRIDIRON                      </t>
+          <t xml:space="preserve">PONTIAC (L.2265)              </t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>104M  001</t>
+          <t>082FNW111</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Pavey</t>
+          <t>Ainsworth Hot Springs</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1.2</v>
+        <v>12</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15004,7 +14994,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Arsenic, Zinc</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -15016,58 +15006,52 @@
         <v>0</v>
       </c>
       <c r="J152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>68 t</t>
+          <t>1 kt</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Au 3.2g/t, Ag 315g/t, Pb 2.05%, As 1.34%</t>
+          <t>Au 41.0g/t, Ag 220g/t, Pb 12.30%, Zn 5.60%</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>A sample of the quartz vein taken in 1982 assayed 3.2 grams per tonne gold, 315 grams per tonne silver, 2.05 per cent lead and 1.34 per cent arsenic (Assessment Report 10425).</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>$5k</t>
-        </is>
-      </c>
+          <t>A sample taken in 1987 from the Pontiac lower portal assayed 41 grams per tonne gold, 220 grams per tonne silver, 12.3 per cent lead and 5.6 per cent zinc (Open File 1988-11).</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>abuts Kokanee Glacier Park boundary</t>
+        </is>
+      </c>
+      <c r="S152" t="n">
         <v>1</v>
       </c>
-      <c r="P152" t="n">
-        <v>2020</v>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>Rosenblat, Robert Samuel</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="n">
-        <v>4</v>
-      </c>
       <c r="T152" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U152" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="V152" t="n">
-        <v>59.93222</v>
+        <v>49.79056</v>
       </c>
       <c r="W152" t="n">
-        <v>-134.93944</v>
+        <v>-117.05222</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104M++001</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW111</t>
         </is>
       </c>
     </row>
@@ -15077,21 +15061,21 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MOLLY HUGHES (L.2106)</t>
+          <t xml:space="preserve">MIDNIGHT                      </t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>082KSW002</t>
+          <t>093L  117</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>New Denver</t>
+          <t>Lake Kathlyn</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15112,58 +15096,52 @@
         <v>0</v>
       </c>
       <c r="J153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>9 kt (inferred)</t>
+          <t>39 t (assay)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Ag 1282.4g/t, Au 5.8g/t</t>
+          <t>Ag 2890g/t, Au 3.8g/t, Cu 1.35%, Pb 46.3%, Zn 8.22%</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Inferred ore reserves of 9072 tonnes at a grade of 5.8 grams per tonne gold and 1282 grams per tonne silver were estimated by Sadlier-Brown and Nevin (1978), based on a sampling program, assuming a deposit dimension of 122 by 122 by 0.2 metres, and allowing for dilution over a 1.2-metre mining width.</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>$3k</t>
-        </is>
-      </c>
+          <t>A sample assayed 7.2 grams per tonne gold, 5235.7 grams per tonne silver, 43.9 per cent lead, 9.71 per cent zinc, and 0.7 per cent copper. A 23 centi- metre wide massive sulphide vein, exposed 92 metres north of the old workings, assayed 3.8 grams per tonne gold, 2890 grams per tonne silver, 46.3 per cent lead, 8.22 per cent zinc, and 1.35 per cent copper.</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="n">
-        <v>1</v>
-      </c>
-      <c r="P153" t="n">
-        <v>1973</v>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>Dyke Mines</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Conditional Registration Reserve (Ski Development) — special process</t>
+        </is>
+      </c>
       <c r="S153" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T153" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="U153" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="V153" t="n">
-        <v>50.00472</v>
+        <v>54.78528</v>
       </c>
       <c r="W153" t="n">
-        <v>-117.38056</v>
+        <v>-127.25583</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++117</t>
         </is>
       </c>
     </row>
@@ -15173,21 +15151,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPIRE                        </t>
+          <t xml:space="preserve">SILVER STAR                   </t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>093L  116</t>
+          <t>082ESW150</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Lake Kathlyn</t>
+          <t>Chopaka</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15196,7 +15174,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper, Cadmium, Antimony</t>
+          <t>Silver, Copper, Lead, Zinc, Molybdenum, Gold, Antimony</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -15212,54 +15190,44 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>12 t</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Ag 1449.9g/t, Au 1.02g/t, Cad 0.01%, Cu 0.44%, Pb 6.14%</t>
+          <t>Au 0.7g/t, Ag 712g/t, Cu 0.90%, Pb 0.14%, Zn 0.20%, Sb 0.10%</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>A selected high grade sample of galena and sphalerite from the 30 centimetre wide quartz vein assayed 2.05 grams per tonne gold, 7096 grams per tonne silver, 25.3 per cent lead, and 18.6 per cent zinc (1914) (Minister of Mines Annual Report 1914, page 225). In 1986, five chip samples were collected and assayed 0.6 to 3.3 grams per tonne gold, 57.9 to 1450 grams per tonne silver, 0.32 to 9.74 per cent lead, 0.22 to 8.47 per cent zinc with minor copper and cadmium values (Assessment Report 15140). In 1986, three chip samples were taken across the vein as well as a high grade sample from the dump and assays ranged between 1.03 to 4.46 grams per tonne gold, 213.9 to 1292 grams per tonne silver, 7.5 to 36.67 per cent lead, 10.49 to 34.01 per cent zinc, 0.26 to 0.36 per cent copper, 0.07 to 0.23</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>In 1984, a 0.6-metre chip sample (84014) from a bull quartz vein exposed in the upper adit assayed 19.2 grams per tonne silver, while a select grab sample from a former sorting pile yielded 0.7 gram per tonne gold, 1404 grams per tonne silver, 0.900 per cent copper, 0.145 per cent lead, 0.200 per cent zinc and greater than 0.1 per cent antimony (Property File - unknown [1984-07-30]: Notes and Maps - Golden Valley Prospect and Silver Star Mine).</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="n">
-        <v>1</v>
-      </c>
-      <c r="P154" t="n">
-        <v>1986</v>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>Holland, Robert</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T154" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U154" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="V154" t="n">
-        <v>54.78333</v>
+        <v>49.0725</v>
       </c>
       <c r="W154" t="n">
-        <v>-127.28222</v>
+        <v>-119.73778</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++116</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ESW150</t>
         </is>
       </c>
     </row>
@@ -15269,21 +15237,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORTO RICO (L.2385)           </t>
+          <t xml:space="preserve">HAYDEN BAY GOLD (L.803)       </t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>082FSW189</t>
+          <t>092K  038</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Porto Rico</t>
+          <t>Heydon Bay</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15292,7 +15260,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -15308,54 +15276,44 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>6 kt</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Au 24.3g/t, Ag 3.8g/t</t>
+          <t>Au 51.42g/t</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Samples assayed 11.65 to 24.34 grams per tonne gold and 3.42 to 3.77 grams per tonne silver (Assessment Report 7702).</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>$525</t>
-        </is>
-      </c>
+          <t>The sulphides in the quartz vein near the beach assayed 51.42 grams per tonne gold from sorted ore (Minister of Mines Annual Report 1933, page A256).</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="n">
-        <v>1</v>
-      </c>
-      <c r="P155" t="n">
-        <v>1979</v>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>Mirko, John M.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T155" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="U155" t="n">
         <v>52</v>
       </c>
       <c r="V155" t="n">
-        <v>49.3175</v>
+        <v>50.58083</v>
       </c>
       <c r="W155" t="n">
-        <v>-117.32528</v>
+        <v>-125.57306</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FSW189</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++038</t>
         </is>
       </c>
     </row>
@@ -15425,10 +15383,10 @@
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T156" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="U156" t="n">
         <v>52</v>
@@ -15442,448 +15400,6 @@
       <c r="X156" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++026</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIDNIGHT                      </t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>093L  117</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Lake Kathlyn</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Silver, Lead, Zinc, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Past Producer       </t>
-        </is>
-      </c>
-      <c r="I157" t="b">
-        <v>0</v>
-      </c>
-      <c r="J157" t="b">
-        <v>1</v>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>39 t (assay)</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>Ag 2890g/t, Au 3.8g/t, Cu 1.35%, Pb 46.3%, Zn 8.22%</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>A sample assayed 7.2 grams per tonne gold, 5235.7 grams per tonne silver, 43.9 per cent lead, 9.71 per cent zinc, and 0.7 per cent copper. A 23 centi- metre wide massive sulphide vein, exposed 92 metres north of the old workings, assayed 3.8 grams per tonne gold, 2890 grams per tonne silver, 46.3 per cent lead, 8.22 per cent zinc, and 1.35 per cent copper.</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>Conditional Registration Reserve (Ski Development) — special process</t>
-        </is>
-      </c>
-      <c r="S157" t="n">
-        <v>2</v>
-      </c>
-      <c r="T157" t="n">
-        <v>50</v>
-      </c>
-      <c r="U157" t="n">
-        <v>52</v>
-      </c>
-      <c r="V157" t="n">
-        <v>54.78528</v>
-      </c>
-      <c r="W157" t="n">
-        <v>-127.25583</v>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++117</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BALTIMORE (L.10060)           </t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>082FNW109</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Mirror Lake</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>13</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Silver, Lead, Gold, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Past Producer       </t>
-        </is>
-      </c>
-      <c r="I158" t="b">
-        <v>0</v>
-      </c>
-      <c r="J158" t="b">
-        <v>1</v>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>60 t (assay)</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>Ag 2600g/t, Au 1.1g/t, Pb 1.24%, Zn 1.4%, Cu 0.0577%</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>A sample of the vein assayed 2600 grams per tonne silver, 1.1 grams per tonne gold, 1.24 per cent lead, 1.4 per cent zinc and 0.0577 per cent coppper (Open File 1988-11).</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>abuts Kokanee Glacier Park boundary</t>
-        </is>
-      </c>
-      <c r="S158" t="n">
-        <v>1</v>
-      </c>
-      <c r="T158" t="n">
-        <v>25</v>
-      </c>
-      <c r="U158" t="n">
-        <v>52</v>
-      </c>
-      <c r="V158" t="n">
-        <v>49.81444</v>
-      </c>
-      <c r="W158" t="n">
-        <v>-117.05472</v>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW109</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HAYDEN BAY GOLD (L.803)       </t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>092K  038</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Heydon Bay</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Past Producer       </t>
-        </is>
-      </c>
-      <c r="I159" t="b">
-        <v>0</v>
-      </c>
-      <c r="J159" t="b">
-        <v>0</v>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>Au 51.42g/t</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>The sulphides in the quartz vein near the beach assayed 51.42 grams per tonne gold from sorted ore (Minister of Mines Annual Report 1933, page A256).</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="n">
-        <v>7</v>
-      </c>
-      <c r="T159" t="n">
-        <v>175</v>
-      </c>
-      <c r="U159" t="n">
-        <v>52</v>
-      </c>
-      <c r="V159" t="n">
-        <v>50.58083</v>
-      </c>
-      <c r="W159" t="n">
-        <v>-125.57306</v>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++038</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PONTIAC (L.2265)              </t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>082FNW111</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Ainsworth Hot Springs</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>12</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Silver, Lead, Zinc, Gold</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Past Producer       </t>
-        </is>
-      </c>
-      <c r="I160" t="b">
-        <v>0</v>
-      </c>
-      <c r="J160" t="b">
-        <v>1</v>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>1 kt</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>Au 41.0g/t, Ag 220g/t, Pb 12.30%, Zn 5.60%</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>A sample taken in 1987 from the Pontiac lower portal assayed 41 grams per tonne gold, 220 grams per tonne silver, 12.3 per cent lead and 5.6 per cent zinc (Open File 1988-11).</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>abuts Kokanee Glacier Park boundary</t>
-        </is>
-      </c>
-      <c r="S160" t="n">
-        <v>1</v>
-      </c>
-      <c r="T160" t="n">
-        <v>25</v>
-      </c>
-      <c r="U160" t="n">
-        <v>52</v>
-      </c>
-      <c r="V160" t="n">
-        <v>49.79056</v>
-      </c>
-      <c r="W160" t="n">
-        <v>-117.05222</v>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNW111</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER STAR                   </t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>082ESW150</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Chopaka</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Silver, Copper, Lead, Zinc, Molybdenum, Gold, Antimony</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Past Producer       </t>
-        </is>
-      </c>
-      <c r="I161" t="b">
-        <v>0</v>
-      </c>
-      <c r="J161" t="b">
-        <v>0</v>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>12 t</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>Au 0.7g/t, Ag 712g/t, Cu 0.90%, Pb 0.14%, Zn 0.20%, Sb 0.10%</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>In 1984, a 0.6-metre chip sample (84014) from a bull quartz vein exposed in the upper adit assayed 19.2 grams per tonne silver, while a select grab sample from a former sorting pile yielded 0.7 gram per tonne gold, 1404 grams per tonne silver, 0.900 per cent copper, 0.145 per cent lead, 0.200 per cent zinc and greater than 0.1 per cent antimony (Property File - unknown [1984-07-30]: Notes and Maps - Golden Valley Prospect and Silver Star Mine).</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="n">
-        <v>9</v>
-      </c>
-      <c r="T161" t="n">
-        <v>225</v>
-      </c>
-      <c r="U161" t="n">
-        <v>52</v>
-      </c>
-      <c r="V161" t="n">
-        <v>49.0725</v>
-      </c>
-      <c r="W161" t="n">
-        <v>-119.73778</v>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082ESW150</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="British Columbia" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="British Columbia" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13543,7 +13543,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sampling of the mineralized muscovite granite yielded up to 0.21 per cent copper and 0.01 per cent molybdenum (Assessment Report 752)
+          <t xml:space="preserve">Sampling of the mineralized muscovite granite yielded up to 0.21 per cent copper and 0.01 per cent molybdenum (Assessment Report 752)
 In 1983, a sample from the main adit assayed 15.16 per cent copper and 194.8 grams per tonne silver, while a sample of molybdenite bearing quartz vein near the adit assayed 0.13 per cent molybdenum (Assessment Report 11619). In 2005, a select sample (HC-05-01) of bornite vein material from the main adit dump assayed greater than 50 per cent copper, 603 grams per tonne silver and 0.98 gram per tonne gold, while a 0.5 metre chip sample (HC JL-02), taken from the adit portal vein the following year, assayed 0.52 gram per tonne gold, 931 grams per tonne silver, 48.7 per cent copper and 0.521 per cent bismuth (Assessment Report 29487). In 1965, seven samples, </t>
         </is>
       </c>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t xml:space="preserve">SILVER BELT (L.5695)          </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>082KNW159</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Five Mile</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.7</v>
+        <v>10.6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,46 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3 t</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Au 15.1g/t</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$2.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Mineral Mountain Resources Ltd., Denny, Jack Norman; Mirko</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U7" t="n">
         <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>49.27111</v>
+        <v>50.61639</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.73167</v>
+        <v>-117.32333</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW159</t>
         </is>
       </c>
     </row>
@@ -1146,30 +1138,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAYBEE (L. 3226)</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104A  202</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Germansen Landing</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>63.7</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1185,33 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 0.3g/t, Ag 217g/t, Cu 0.40%, Pb 11.80%, Zn 2.76%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>In 2005, a chip sample (73110) across 30 centimetres of the Maybe Vein assayed 217 grams per tonne silver, 0.275 gram per tonne gold, 11.8 per cent lead, 2.76 per cent zinc, and 0.4 per cent copper (Assessment Report 28115). One vein consisted of a footwall section of approximately 1 metre of massive galena, sphalerite and pyrite and minor chalcopyrite with a quartz-barite gangue followed by a middle section of 2.5 metres of mixed quartz, barite and minor jasper and about 2 per cent mixed sulphides, and a hangingwall section and about one metre of massive sulphides.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$3.1M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Mountain Boy Minerals Ltd.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>56.15333</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-123.92278</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104A++202</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,33 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1321,14 +1313,14 @@
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1434,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">HILL 60                       </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>082KSW168</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Retallack</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 146g/t, Pb 8.78%, Zn 6.31%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>The weighted average of 16 channel samples taken at surface over an average width of 50.5 centimetres and a strike length of 48 metres is 6.31 per cent zinc, 8.78 per cent lead and 146.4 grams per tonne silver (Assessment Report 13246).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$361k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Cavan Ventures Ltd., Baraniuk, Lawrence Nester</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>50.02583</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-117.02278</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW168</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.5</v>
+        <v>11.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1761,54 +1753,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>1986</v>
+        <v>1999</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>49.30889</v>
+        <v>52.85806</v>
       </c>
       <c r="W14" t="n">
-        <v>-120.00417</v>
+        <v>-132.15722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -1997,92 +1989,6 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SLOCOMB 5                     </t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>094E  227</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fort Ware</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Silver, Zinc, Lead, Copper</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Ag 272g/t, Cu 0.10%, Pb 1.55%, Zn 3.97%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Assay results from this sample were 3.97 per cent zinc, 1.55 per cent lead, 0.10 per cent copper and 272.23 grams per tonne silver (Assessment Report 19583).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>325</v>
-      </c>
-      <c r="U17" t="n">
-        <v>55</v>
-      </c>
-      <c r="V17" t="n">
-        <v>57.85639</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-126.31361</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094E++227</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELT (L.5695)          </t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>082KNW159</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Five Mile</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.6</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,46 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>3 t</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Au 15.1g/t</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$2.2M</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Mineral Mountain Resources Ltd., Denny, Jack Norman; Mirko</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
         <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>50.61639</v>
+        <v>49.27111</v>
       </c>
       <c r="W7" t="n">
-        <v>-117.32333</v>
+        <v>-125.73167</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW159</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1138,30 +1146,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>MAYBEE (L. 3226)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104A  202</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Germansen Landing</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>63.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1177,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 0.3g/t, Ag 217g/t, Cu 0.40%, Pb 11.80%, Zn 2.76%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 2005, a chip sample (73110) across 30 centimetres of the Maybe Vein assayed 217 grams per tonne silver, 0.275 gram per tonne gold, 11.8 per cent lead, 2.76 per cent zinc, and 0.4 per cent copper (Assessment Report 28115). One vein consisted of a footwall section of approximately 1 metre of massive galena, sphalerite and pyrite and minor chalcopyrite with a quartz-barite gangue followed by a middle section of 2.5 metres of mixed quartz, barite and minor jasper and about 2 per cent mixed sulphides, and a hangingwall section and about one metre of massive sulphides.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$3.1M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Mountain Boy Minerals Ltd.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>56.15333</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-123.92278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104A++202</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1281,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1313,14 +1321,14 @@
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1434,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">HILL 60                       </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>082KSW168</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Retallack</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 146g/t, Pb 8.78%, Zn 6.31%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The weighted average of 16 channel samples taken at surface over an average width of 50.5 centimetres and a strike length of 48 metres is 6.31 per cent zinc, 8.78 per cent lead and 146.4 grams per tonne silver (Assessment Report 13246).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$361k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Cavan Ventures Ltd., Baraniuk, Lawrence Nester</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>50.02583</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-117.02278</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW168</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11.4</v>
+        <v>7.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1753,54 +1761,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>1999</v>
+        <v>1986</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>52.85806</v>
+        <v>49.30889</v>
       </c>
       <c r="W14" t="n">
-        <v>-132.15722</v>
+        <v>-120.00417</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -1989,6 +1997,92 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLOCOMB 5                     </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>094E  227</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fort Ware</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Silver, Zinc, Lead, Copper</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Ag 272g/t, Cu 0.10%, Pb 1.55%, Zn 3.97%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Assay results from this sample were 3.97 per cent zinc, 1.55 per cent lead, 0.10 per cent copper and 272.23 grams per tonne silver (Assessment Report 19583).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>325</v>
+      </c>
+      <c r="U17" t="n">
+        <v>55</v>
+      </c>
+      <c r="V17" t="n">
+        <v>57.85639</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-126.31361</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094E++227</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAYBEE (L. 3226)</t>
+          <t>BRIAN BORU (L. 607, 608)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104A  202</t>
+          <t>093M  064</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Germansen Landing</t>
+          <t>Red Rose</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>63.7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,28 +1190,28 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 0.3g/t, Ag 217g/t, Cu 0.40%, Pb 11.80%, Zn 2.76%</t>
+          <t>Au 1.1g/t, Ag 143g/t, Cu 0.13%, Pb 1.84%, Zn 16.77%, Co 0.02%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>In 2005, a chip sample (73110) across 30 centimetres of the Maybe Vein assayed 217 grams per tonne silver, 0.275 gram per tonne gold, 11.8 per cent lead, 2.76 per cent zinc, and 0.4 per cent copper (Assessment Report 28115). One vein consisted of a footwall section of approximately 1 metre of massive galena, sphalerite and pyrite and minor chalcopyrite with a quartz-barite gangue followed by a middle section of 2.5 metres of mixed quartz, barite and minor jasper and about 2 per cent mixed sulphides, and a hangingwall section and about one metre of massive sulphides.</t>
+          <t>A 15-centimetre channel sample taken from one vein assayed trace gold, 220.5 grams per tonne silver, 1.84 per cent lead, and 11.27 per cent zinc (Geological Survey of Canada Memoir 223). Samples 23201 and 23176 assayed 0.10 and 1.11 grams per tonne gold, 152.0 and 66.0 grams per tonne silver, 0.50 and 0.13 per cent copper, 14.26 and 22.27 per cent zinc with 0.013 and 0.019 per cent cobalt, respectively (Assessment Report 30431).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$3.1M</t>
+          <t>$1.5M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
         <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Mountain Boy Minerals Ltd.</t>
+          <t>Duncastle Gold Corp., Hardy, Samuel Anthony Kyler; Johnson</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1225,14 +1225,14 @@
         <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>56.15333</v>
+        <v>55.07806</v>
       </c>
       <c r="W8" t="n">
-        <v>-123.92278</v>
+        <v>-127.60611</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104A++202</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++064</t>
         </is>
       </c>
     </row>
@@ -1242,30 +1242,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>31.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1281,33 +1281,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1318,17 +1318,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>58.90944</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-129.09278</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1417,14 +1417,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1434,35 +1434,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1530,30 +1530,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1569,54 +1569,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>49.47472</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-121.51417</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1626,30 +1626,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25.2</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1665,54 +1665,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1989</v>
+        <v>2010</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>53.09694</v>
+        <v>49.47472</v>
       </c>
       <c r="W13" t="n">
-        <v>-128.335</v>
+        <v>-121.51417</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1722,35 +1722,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.5</v>
+        <v>25.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1761,54 +1761,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O14" t="n">
         <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>49.30889</v>
+        <v>53.09694</v>
       </c>
       <c r="W14" t="n">
-        <v>-120.00417</v>
+        <v>-128.335</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>37.4</v>
+        <v>2.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,29 +1857,33 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>1966</v>
+        <v>2019</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1890,17 +1894,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>58.88222</v>
+        <v>55.22278</v>
       </c>
       <c r="W15" t="n">
-        <v>-132.1175</v>
+        <v>-127.56333</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -1910,35 +1914,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">KENALLAN                      </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>082LSW045</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Westwold</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.6</v>
+        <v>37.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1949,54 +1953,50 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>67 t (assay)</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Mo 3.61%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$21k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2022</v>
+        <v>1966</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="V16" t="n">
-        <v>50.43917</v>
+        <v>58.88222</v>
       </c>
       <c r="W16" t="n">
-        <v>-119.81833</v>
+        <v>-132.1175</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2006,30 +2006,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLOCOMB 5                     </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>094E  227</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fort Ware</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>62.5</v>
+        <v>6.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 272g/t, Cu 0.10%, Pb 1.55%, Zn 3.97%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Assay results from this sample were 3.97 per cent zinc, 1.55 per cent lead, 0.10 per cent copper and 272.23 grams per tonne silver (Assessment Report 19583).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2075,14 +2075,358 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>57.85639</v>
+        <v>55.99139</v>
       </c>
       <c r="W17" t="n">
-        <v>-126.31361</v>
+        <v>-130.03694</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094E++227</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LAST SHOT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>103O  003</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
+        <v>55</v>
+      </c>
+      <c r="V18" t="n">
+        <v>55.9975</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-130.05694</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>300</v>
+      </c>
+      <c r="U19" t="n">
+        <v>55</v>
+      </c>
+      <c r="V19" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>092B  060</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>13</v>
+      </c>
+      <c r="T20" t="n">
+        <v>325</v>
+      </c>
+      <c r="U20" t="n">
+        <v>55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>11</v>
+      </c>
+      <c r="T21" t="n">
+        <v>275</v>
+      </c>
+      <c r="U21" t="n">
+        <v>55</v>
+      </c>
+      <c r="V21" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -954,21 +954,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUNTER                        </t>
+          <t>CHARLIE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>103H  034</t>
+          <t>092O  043</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Nemaiah Valley</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21.7</v>
+        <v>36.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -977,12 +977,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>94 kt (uncategorized)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 12g/t</t>
+          <t>Au 16.0g/t, Ag 224g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Six samples taken across this width over a 17.4 metre length averaged 35.35 grams per tonne gold and 87.1 grams per tonne silver (Assessment Report 13398). The vein is commonly 8 to 20 centimetres thick and 6 samples along a 12.5-metre length averaged 67.0 grams per tonne gold, 32.57 grams per tonne silver and 0.67 per cent copper over an average width of 0.19 metre (Assessment Report 11937). Unclassified reserves for the Hunter property are 94,338 tonnes grading 12 grams per tonne gold, diluted to a 1.2 metre mining width (George Cross News Letter June 13, 1984).</t>
+          <t>A chip sample assayed 279.9 grams per tonne silver, 10.6 grams per tonne gold and 13.68 per cent copper (Bulletin 81). The following year, samples from the East vein area assayed up to 0.48 per cent copper, 1.0 gram per tonne gold and 14.3 grams per tonne silver (Assessment Report 12105). In 1987, chip samples from the Charlie vein, taken over a length of 20 metres and width of 20 centimetres, averaged 22.1 grams per tonne gold and 224.0 grams per tonne silver, while a sample (AB 245B) of the DK vein assayed 9.9 grams per tonne gold, 95.8 grams per tonne silver and 0.14 per cent lead (Assessment Report 17038). A 20- centimetre sample of massive sulphide from the Big vein assayed 8.2 grams per tonne gold, 8557 grams per tonne silver and 26.0 per cent copper (Assessment Report 17038). In 199</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$281k</t>
+          <t>$6.3M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>1984</v>
+        <v>2013</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Du-Well Res., Arnhem Resources Inc.</t>
+          <t>Galore Resources Inc., Suncor, Galore Resources Inc.; Zelon Enterprises Ltd.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U6" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="V6" t="n">
-        <v>53.19417</v>
+        <v>51.18028</v>
       </c>
       <c r="W6" t="n">
-        <v>-128.385</v>
+        <v>-123.67083</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++034</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092O++043</t>
         </is>
       </c>
     </row>
@@ -1050,21 +1050,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t xml:space="preserve">HUNTER                        </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>103H  034</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.7</v>
+        <v>21.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>94 kt (uncategorized)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Au 12g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>Six samples taken across this width over a 17.4 metre length averaged 35.35 grams per tonne gold and 87.1 grams per tonne silver (Assessment Report 13398). The vein is commonly 8 to 20 centimetres thick and 6 samples along a 12.5-metre length averaged 67.0 grams per tonne gold, 32.57 grams per tonne silver and 0.67 per cent copper over an average width of 0.19 metre (Assessment Report 11937). Unclassified reserves for the Hunter property are 94,338 tonnes grading 12 grams per tonne gold, diluted to a 1.2 metre mining width (George Cross News Letter June 13, 1984).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$281k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2023</v>
+        <v>1984</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Du-Well Res., Arnhem Resources Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V7" t="n">
-        <v>49.27111</v>
+        <v>53.19417</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.73167</v>
+        <v>-128.385</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++034</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BRIAN BORU (L. 607, 608)</t>
+          <t xml:space="preserve">SILVER BELT (L.5695)          </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>093M  064</t>
+          <t>082KNW159</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Red Rose</t>
+          <t>Five Mile</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>10.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Copper</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1188,51 +1188,43 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Au 1.1g/t, Ag 143g/t, Cu 0.13%, Pb 1.84%, Zn 16.77%, Co 0.02%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>A 15-centimetre channel sample taken from one vein assayed trace gold, 220.5 grams per tonne silver, 1.84 per cent lead, and 11.27 per cent zinc (Geological Survey of Canada Memoir 223). Samples 23201 and 23176 assayed 0.10 and 1.11 grams per tonne gold, 152.0 and 66.0 grams per tonne silver, 0.50 and 0.13 per cent copper, 14.26 and 22.27 per cent zinc with 0.013 and 0.019 per cent cobalt, respectively (Assessment Report 30431).</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.5M</t>
+          <t>$2.2M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Duncastle Gold Corp., Hardy, Samuel Anthony Kyler; Johnson</t>
+          <t>Mineral Mountain Resources Ltd., Denny, Jack Norman; Mirko</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V8" t="n">
-        <v>55.07806</v>
+        <v>50.61639</v>
       </c>
       <c r="W8" t="n">
-        <v>-127.60611</v>
+        <v>-117.32333</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++064</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW159</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31.5</v>
+        <v>16.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1273,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V9" t="n">
-        <v>58.90944</v>
+        <v>49.27111</v>
       </c>
       <c r="W9" t="n">
-        <v>-129.09278</v>
+        <v>-125.73167</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1338,30 +1330,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>MAYBEE (L. 3226)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104A  202</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Germansen Landing</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>63.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1377,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 0.3g/t, Ag 217g/t, Cu 0.40%, Pb 11.80%, Zn 2.76%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 2005, a chip sample (73110) across 30 centimetres of the Maybe Vein assayed 217 grams per tonne silver, 0.275 gram per tonne gold, 11.8 per cent lead, 2.76 per cent zinc, and 0.4 per cent copper (Assessment Report 28115). One vein consisted of a footwall section of approximately 1 metre of massive galena, sphalerite and pyrite and minor chalcopyrite with a quartz-barite gangue followed by a middle section of 2.5 metres of mixed quartz, barite and minor jasper and about 2 per cent mixed sulphides, and a hangingwall section and about one metre of massive sulphides.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$3.1M</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Mountain Boy Minerals Ltd.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1414,17 +1406,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>56.15333</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-123.92278</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104A++202</t>
         </is>
       </c>
     </row>
@@ -1434,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,33 +1465,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1513,14 +1505,14 @@
         <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1530,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1569,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1626,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1665,54 +1657,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V13" t="n">
-        <v>49.47472</v>
+        <v>54.94444</v>
       </c>
       <c r="W13" t="n">
-        <v>-121.51417</v>
+        <v>-126.15722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25.2</v>
+        <v>36</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,12 +1737,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1761,33 +1753,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>1989</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1801,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>53.09694</v>
+        <v>58.185</v>
       </c>
       <c r="W14" t="n">
-        <v>-128.335</v>
+        <v>-125.30611</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1818,21 +1810,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.7</v>
+        <v>25.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1841,12 +1833,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,33 +1849,33 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O15" t="n">
         <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2019</v>
+        <v>1989</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1894,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>55.22278</v>
+        <v>53.09694</v>
       </c>
       <c r="W15" t="n">
-        <v>-127.56333</v>
+        <v>-128.335</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1906,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37.4</v>
+        <v>6.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,50 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>4.3 Mt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1966</v>
+        <v>2010</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U16" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V16" t="n">
-        <v>58.88222</v>
+        <v>49.47472</v>
       </c>
       <c r="W16" t="n">
-        <v>-132.1175</v>
+        <v>-121.51417</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -2006,35 +2002,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.6</v>
+        <v>37.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2045,25 +2041,31 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>13</v>
@@ -2072,17 +2074,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V17" t="n">
-        <v>55.99139</v>
+        <v>58.88222</v>
       </c>
       <c r="W17" t="n">
-        <v>-130.03694</v>
+        <v>-132.1175</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2092,21 +2094,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAST SHOT</t>
+          <t>SCOUT ADIT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>103O  003</t>
+          <t>092HSW176</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Harrison Mills</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2115,7 +2117,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
+          <t>Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2136,20 +2138,30 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
+          <t>Ag 1870g/t, Cu 1.11%, Zn 0.24%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>In 2013, two samples (A-1 and A-2) of mineralized vein material assayed 0.306 and 0.236 per cent zinc and 1.565 and 1.11 per cent copper with 2660 and 1870 grams per tonne silver, respectively (Assessment Report 34753).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$34k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2014</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Reimer, Abram</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2158,17 +2170,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V18" t="n">
-        <v>55.9975</v>
+        <v>49.24611</v>
       </c>
       <c r="W18" t="n">
-        <v>-130.05694</v>
+        <v>-121.92</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW176</t>
         </is>
       </c>
     </row>
@@ -2178,30 +2190,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t xml:space="preserve">KENALLAN                      </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>082LSW045</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Westwold</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2217,216 +2229,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>67 t (assay)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Mo 3.61%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$21k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V19" t="n">
-        <v>48.61472</v>
+        <v>50.43917</v>
       </c>
       <c r="W19" t="n">
-        <v>-123.59222</v>
+        <v>-119.81833</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>092B  060</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>13</v>
-      </c>
-      <c r="T20" t="n">
-        <v>325</v>
-      </c>
-      <c r="U20" t="n">
-        <v>55</v>
-      </c>
-      <c r="V20" t="n">
-        <v>48.6075</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-123.57111</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CORMORANT                     </t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>092K  098</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Granite Bay</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>11</v>
-      </c>
-      <c r="T21" t="n">
-        <v>275</v>
-      </c>
-      <c r="U21" t="n">
-        <v>55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>50.18694</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-125.28056</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -954,21 +954,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHARLIE</t>
+          <t xml:space="preserve">HUNTER                        </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092O  043</t>
+          <t>103H  034</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nemaiah Valley</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>36.9</v>
+        <v>21.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -977,12 +977,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>94 kt (uncategorized)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 16.0g/t, Ag 224g/t</t>
+          <t>Au 12g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>A chip sample assayed 279.9 grams per tonne silver, 10.6 grams per tonne gold and 13.68 per cent copper (Bulletin 81). The following year, samples from the East vein area assayed up to 0.48 per cent copper, 1.0 gram per tonne gold and 14.3 grams per tonne silver (Assessment Report 12105). In 1987, chip samples from the Charlie vein, taken over a length of 20 metres and width of 20 centimetres, averaged 22.1 grams per tonne gold and 224.0 grams per tonne silver, while a sample (AB 245B) of the DK vein assayed 9.9 grams per tonne gold, 95.8 grams per tonne silver and 0.14 per cent lead (Assessment Report 17038). A 20- centimetre sample of massive sulphide from the Big vein assayed 8.2 grams per tonne gold, 8557 grams per tonne silver and 26.0 per cent copper (Assessment Report 17038). In 199</t>
+          <t>Six samples taken across this width over a 17.4 metre length averaged 35.35 grams per tonne gold and 87.1 grams per tonne silver (Assessment Report 13398). The vein is commonly 8 to 20 centimetres thick and 6 samples along a 12.5-metre length averaged 67.0 grams per tonne gold, 32.57 grams per tonne silver and 0.67 per cent copper over an average width of 0.19 metre (Assessment Report 11937). Unclassified reserves for the Hunter property are 94,338 tonnes grading 12 grams per tonne gold, diluted to a 1.2 metre mining width (George Cross News Letter June 13, 1984).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$6.3M</t>
+          <t>$281k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2013</v>
+        <v>1984</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Galore Resources Inc., Suncor, Galore Resources Inc.; Zelon Enterprises Ltd.</t>
+          <t>Du-Well Res., Arnhem Resources Inc.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="V6" t="n">
-        <v>51.18028</v>
+        <v>53.19417</v>
       </c>
       <c r="W6" t="n">
-        <v>-123.67083</v>
+        <v>-128.385</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092O++043</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++034</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUNTER                        </t>
+          <t>MAYBEE (L. 3226)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>103H  034</t>
+          <t>104A  202</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Germansen Landing</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21.7</v>
+        <v>63.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Zinc, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,33 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94 kt (uncategorized)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 12g/t</t>
+          <t>Au 0.3g/t, Ag 217g/t, Cu 0.40%, Pb 11.80%, Zn 2.76%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Six samples taken across this width over a 17.4 metre length averaged 35.35 grams per tonne gold and 87.1 grams per tonne silver (Assessment Report 13398). The vein is commonly 8 to 20 centimetres thick and 6 samples along a 12.5-metre length averaged 67.0 grams per tonne gold, 32.57 grams per tonne silver and 0.67 per cent copper over an average width of 0.19 metre (Assessment Report 11937). Unclassified reserves for the Hunter property are 94,338 tonnes grading 12 grams per tonne gold, diluted to a 1.2 metre mining width (George Cross News Letter June 13, 1984).</t>
+          <t>In 2005, a chip sample (73110) across 30 centimetres of the Maybe Vein assayed 217 grams per tonne silver, 0.275 gram per tonne gold, 11.8 per cent lead, 2.76 per cent zinc, and 0.4 per cent copper (Assessment Report 28115). One vein consisted of a footwall section of approximately 1 metre of massive galena, sphalerite and pyrite and minor chalcopyrite with a quartz-barite gangue followed by a middle section of 2.5 metres of mixed quartz, barite and minor jasper and about 2 per cent mixed sulphides, and a hangingwall section and about one metre of massive sulphides.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$281k</t>
+          <t>$3.1M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1984</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Du-Well Res., Arnhem Resources Inc.</t>
+          <t>Mountain Boy Minerals Ltd.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>53.19417</v>
+        <v>56.15333</v>
       </c>
       <c r="W7" t="n">
-        <v>-128.385</v>
+        <v>-123.92278</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++034</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104A++202</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELT (L.5695)          </t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>082KNW159</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Five Mile</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,46 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>118 kt (assay)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$2.2M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2025</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Mineral Mountain Resources Ltd., Denny, Jack Norman; Mirko</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>50.61639</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-117.32333</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW159</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1242,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16.7</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1257,12 +1265,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.27111</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.73167</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MAYBEE (L. 3226)</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>104A  202</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Germansen Landing</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63.7</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 0.3g/t, Ag 217g/t, Cu 0.40%, Pb 11.80%, Zn 2.76%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 2005, a chip sample (73110) across 30 centimetres of the Maybe Vein assayed 217 grams per tonne silver, 0.275 gram per tonne gold, 11.8 per cent lead, 2.76 per cent zinc, and 0.4 per cent copper (Assessment Report 28115). One vein consisted of a footwall section of approximately 1 metre of massive galena, sphalerite and pyrite and minor chalcopyrite with a quartz-barite gangue followed by a middle section of 2.5 metres of mixed quartz, barite and minor jasper and about 2 per cent mixed sulphides, and a hangingwall section and about one metre of massive sulphides.</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$3.1M</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Mountain Boy Minerals Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>56.15333</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-123.92278</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104A++202</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1434,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.8</v>
+        <v>36</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,7 +1457,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1465,33 +1473,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1502,17 +1510,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>50.53139</v>
+        <v>58.185</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.2025</v>
+        <v>-125.30611</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1530,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.8</v>
+        <v>25.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,33 +1569,33 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2018</v>
+        <v>1989</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1598,17 +1606,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>49.73278</v>
+        <v>53.09694</v>
       </c>
       <c r="W12" t="n">
-        <v>-125.21139</v>
+        <v>-128.335</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1626,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1657,54 +1665,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="V13" t="n">
-        <v>54.94444</v>
+        <v>49.47472</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.15722</v>
+        <v>-121.51417</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>6.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1737,7 +1745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1753,33 +1761,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1790,17 +1798,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>58.185</v>
+        <v>50.37417</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.30611</v>
+        <v>-116.36167</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1810,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25.2</v>
+        <v>37.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1849,33 +1857,29 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>215 t</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>1989</v>
+        <v>1966</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1890,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V15" t="n">
-        <v>53.09694</v>
+        <v>58.88222</v>
       </c>
       <c r="W15" t="n">
-        <v>-128.335</v>
+        <v>-132.1175</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -1906,35 +1910,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>082LSE063</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Cherryville</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1945,54 +1949,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P16" t="n">
-        <v>2010</v>
+        <v>2026</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="U16" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>49.47472</v>
+        <v>50.17861</v>
       </c>
       <c r="W16" t="n">
-        <v>-121.51417</v>
+        <v>-118.54</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
         </is>
       </c>
     </row>
@@ -2002,35 +2006,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">KENALLAN                      </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>082LSW045</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Westwold</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37.4</v>
+        <v>4.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2041,50 +2045,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>67 t (assay)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Mo 3.61%</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$21k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1966</v>
+        <v>2022</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="V17" t="n">
-        <v>58.88222</v>
+        <v>50.43917</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.1175</v>
+        <v>-119.81833</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
         </is>
       </c>
     </row>
@@ -2094,30 +2102,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SCOUT ADIT</t>
+          <t xml:space="preserve">WHIRLWIND (L.1866S)           </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092HSW176</t>
+          <t>092HSE066</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Harrison Mills</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2133,150 +2141,54 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 1870g/t, Cu 1.11%, Zn 0.24%</t>
+          <t>Au 11.3g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>In 2013, two samples (A-1 and A-2) of mineralized vein material assayed 0.306 and 0.236 per cent zinc and 1.565 and 1.11 per cent copper with 2660 and 1870 grams per tonne silver, respectively (Assessment Report 34753).</t>
+          <t>2 level assayed trace to 29 grams per tonne gold and up to 1.4 grams per tonne silver (Minister of Mines Annual Report 1947, page 150). A hole drilled in 1926 encountered 1.0 metre grading 11.3 grams per tonne gold (Minister of Mines Annual Report 1933, page 171). Grab samples of sulphide-rich material collected from the dump at the old workings gave maximum assay values of 29 grams of gold and 16 grams of silver per tonne, with 0.52 per cent copper and 2.5 per cent arsenic (Paper 1989-3, page 30).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$34k</t>
+          <t>$12k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2014</v>
+        <v>1988</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Reimer, Abram</t>
+          <t>Hedley-Sterling Ex., Lawrence Mining Corp.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U18" t="n">
         <v>57</v>
       </c>
       <c r="V18" t="n">
-        <v>49.24611</v>
+        <v>49.37306</v>
       </c>
       <c r="W18" t="n">
-        <v>-121.92</v>
+        <v>-120.08194</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW176</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KENALLAN                      </t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>082LSW045</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Westwold</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Molybdenum</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Molybdenum, Copper, Gold</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>67 t (assay)</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Mo 3.61%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$21k</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>9</v>
-      </c>
-      <c r="T19" t="n">
-        <v>225</v>
-      </c>
-      <c r="U19" t="n">
-        <v>57</v>
-      </c>
-      <c r="V19" t="n">
-        <v>50.43917</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-119.81833</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE066</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAYBEE (L. 3226)</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104A  202</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Germansen Landing</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.7</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver, Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 0.3g/t, Ag 217g/t, Cu 0.40%, Pb 11.80%, Zn 2.76%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>In 2005, a chip sample (73110) across 30 centimetres of the Maybe Vein assayed 217 grams per tonne silver, 0.275 gram per tonne gold, 11.8 per cent lead, 2.76 per cent zinc, and 0.4 per cent copper (Assessment Report 28115). One vein consisted of a footwall section of approximately 1 metre of massive galena, sphalerite and pyrite and minor chalcopyrite with a quartz-barite gangue followed by a middle section of 2.5 metres of mixed quartz, barite and minor jasper and about 2 per cent mixed sulphides, and a hangingwall section and about one metre of massive sulphides.</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$3.1M</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Mountain Boy Minerals Ltd.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>56.15333</v>
+        <v>49.27111</v>
       </c>
       <c r="W7" t="n">
-        <v>-123.92278</v>
+        <v>-125.73167</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104A++202</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1434,30 +1434,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>INTERNATIONAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>082KNE058</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Poplar Creek</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>18.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1478,28 +1478,28 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 562g/t, Pb 39.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>The sample assayed 445.72 grams per tonne silver, 37.7 per cent lead and 1.2 per cent zinc (Minister of Mines Annual Report 1918, page 162). The average grades of 562.3 grams per tonne silver and 39.2 per cent lead are fairly typical of historical assays from old workings going back to the early 1900’s (V STOCKWATCH, March 29, 2012). A sample taken across 0.9 metre from the face of the east drift yielded 384 grams per tonne silver and 30 per cent lead (Starr, 1926 (Property File)).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$346k</t>
         </is>
       </c>
       <c r="O11" t="n">
         <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Canadian Critical Minerals Inc. (FMC #278750), Canadian Critical Minerals Inc. (FMC #278750); Johnston, David W.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1513,14 +1513,14 @@
         <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>58.185</v>
+        <v>50.53278</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.30611</v>
+        <v>-116.94528</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNE058</t>
         </is>
       </c>
     </row>
@@ -1901,294 +1901,6 @@
       <c r="X15" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>082LSE063</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Cherryville</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>$47k</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>9</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>150</v>
-      </c>
-      <c r="U16" t="n">
-        <v>57</v>
-      </c>
-      <c r="V16" t="n">
-        <v>50.17861</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-118.54</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KENALLAN                      </t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>082LSW045</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Westwold</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Molybdenum</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Molybdenum, Copper, Gold</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>67 t (assay)</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Mo 3.61%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$21k</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>225</v>
-      </c>
-      <c r="U17" t="n">
-        <v>57</v>
-      </c>
-      <c r="V17" t="n">
-        <v>50.43917</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-119.81833</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WHIRLWIND (L.1866S)           </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>092HSE066</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Hedley</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper, Zinc</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Au 11.3g/t</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 level assayed trace to 29 grams per tonne gold and up to 1.4 grams per tonne silver (Minister of Mines Annual Report 1947, page 150). A hole drilled in 1926 encountered 1.0 metre grading 11.3 grams per tonne gold (Minister of Mines Annual Report 1933, page 171). Grab samples of sulphide-rich material collected from the dump at the old workings gave maximum assay values of 29 grams of gold and 16 grams of silver per tonne, with 0.52 per cent copper and 2.5 per cent arsenic (Paper 1989-3, page 30).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$12k</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1988</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Hedley-Sterling Ex., Lawrence Mining Corp.</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>175</v>
-      </c>
-      <c r="U18" t="n">
-        <v>57</v>
-      </c>
-      <c r="V18" t="n">
-        <v>49.37306</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-120.08194</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE066</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t xml:space="preserve">EDYE PASS                     </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>103J  015</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Hunts Inlet</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,54 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>226 kt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 29.0g/t, Ag 10.0g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.8M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>54.0275</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-130.585</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>BRIAN BORU (L. 607, 608)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093M  064</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Red Rose</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,33 +1281,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 1.1g/t, Ag 143g/t, Cu 0.13%, Pb 1.84%, Zn 16.77%, Co 0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A 15-centimetre channel sample taken from one vein assayed trace gold, 220.5 grams per tonne silver, 1.84 per cent lead, and 11.27 per cent zinc (Geological Survey of Canada Memoir 223). Samples 23201 and 23176 assayed 0.10 and 1.11 grams per tonne gold, 152.0 and 66.0 grams per tonne silver, 0.50 and 0.13 per cent copper, 14.26 and 22.27 per cent zinc with 0.013 and 0.019 per cent cobalt, respectively (Assessment Report 30431).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$1.5M</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Duncastle Gold Corp., Hardy, Samuel Anthony Kyler; Johnson</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1318,17 +1318,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>55.07806</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-127.60611</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++064</t>
         </is>
       </c>
     </row>
@@ -1338,21 +1338,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1434,35 +1434,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INTERNATIONAL</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>082KNE058</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Poplar Creek</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18.6</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,33 +1473,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 562g/t, Pb 39.20%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The sample assayed 445.72 grams per tonne silver, 37.7 per cent lead and 1.2 per cent zinc (Minister of Mines Annual Report 1918, page 162). The average grades of 562.3 grams per tonne silver and 39.2 per cent lead are fairly typical of historical assays from old workings going back to the early 1900’s (V STOCKWATCH, March 29, 2012). A sample taken across 0.9 metre from the face of the east drift yielded 384 grams per tonne silver and 30 per cent lead (Starr, 1926 (Property File)).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$346k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Canadian Critical Minerals Inc. (FMC #278750), Canadian Critical Minerals Inc. (FMC #278750); Johnston, David W.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1510,17 +1510,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>50.53278</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-116.94528</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>25.2</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1569,54 +1569,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1989</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>53.09694</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-128.335</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,54 +1665,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.47472</v>
+        <v>58.73611</v>
       </c>
       <c r="W13" t="n">
-        <v>-121.51417</v>
+        <v>-133.27</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1722,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>ZOHINI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>104K  052</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>16.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1761,33 +1761,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 2.5g/t, Ag 403g/t, Pb 2.40%, Zn 3.30%, Sb 4.20%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>A 1.8 metre chip sample assayed 10.6 grams per tonne gold, 1664 grams per tonne silver, 5.12 per cent lead, 0.16 per cent zinc, and 1.89 per cent arsenic. All of the drillholes encountered the shear zone and the best intersection was 2.4 metres of 4.73 grams per tonne gold, 600.69 grams per tonne silver, 6.54 per cent lead, 0.66 per cent zinc and 4.55 per cent antimony (Assessment Report 23858). The weighted average of channel sampling over a 3.9 metre footwall section gave 1.7 grams per tonne gold, 617.1 grams per tonne silver, 2.1 per cent lead, 6.3 per cent zinc, and 1.5 per cent antimony. On the hangingwall section, a 1.8 metre section averaged 3.4 grams per tonne gold, 188.56 grams per tonne silver, 2.7 per cent lead, 3.3 per cent zinc, and 4.2 per cent antimony (New Taku Mines Ltd.).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$491k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Firesteel Resources Inc., Xplorer Minerals Inc., Stow Resources Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1798,17 +1798,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>50.37417</v>
+        <v>58.71361</v>
       </c>
       <c r="W14" t="n">
-        <v>-116.36167</v>
+        <v>-133.31944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++052</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>37.4</v>
+        <v>25.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,29 +1857,33 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>215 t</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>1966</v>
+        <v>1989</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1890,17 +1894,933 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
+        <v>65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>53.09694</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-128.335</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PRIDE OF EMORY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>092HSW004</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Dogwood Valley</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Past Producer       </t>
+        </is>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>4.3 Mt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>$234k</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>200</v>
+      </c>
+      <c r="U16" t="n">
+        <v>64</v>
+      </c>
+      <c r="V16" t="n">
+        <v>49.47472</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-121.51417</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DALEY WEST</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>093M  053</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New Hazelton</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$193k</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>325</v>
+      </c>
+      <c r="U17" t="n">
+        <v>61</v>
+      </c>
+      <c r="V17" t="n">
+        <v>55.22278</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-127.56333</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACE                           </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>104K  025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Callison Ranch</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Asbestos</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Prospect  </t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
         <v>60</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V18" t="n">
         <v>58.88222</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W18" t="n">
         <v>-132.1175</v>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SCOUT ADIT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>092HSW176</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Harrison Mills</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Copper, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 1870g/t, Cu 1.11%, Zn 0.24%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>In 2013, two samples (A-1 and A-2) of mineralized vein material assayed 0.306 and 0.236 per cent zinc and 1.565 and 1.11 per cent copper with 2660 and 1870 grams per tonne silver, respectively (Assessment Report 34753).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$34k</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Reimer, Abram</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="n">
+        <v>325</v>
+      </c>
+      <c r="U19" t="n">
+        <v>57</v>
+      </c>
+      <c r="V19" t="n">
+        <v>49.24611</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-121.92</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW176</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KENALLAN                      </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>082LSW045</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Westwold</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Molybdenum</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Molybdenum, Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>67 t (assay)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Mo 3.61%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$21k</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>200</v>
+      </c>
+      <c r="U20" t="n">
+        <v>57</v>
+      </c>
+      <c r="V20" t="n">
+        <v>50.43917</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-119.81833</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SPRING</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>104K  096</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tulsequah</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Silver, Zinc, Copper, Gold, Lead</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 0.2g/t, Ag 357g/t, Cu 0.12%, Zn 5.31%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>One of these samples was a grab from a sulphide lens which assayed 0.17 gram per tonne gold, 356.6 grams per tonne silver, 10.3 per cent zinc, and 0.12 per cent copper (Assessment Report 9106). The only noteworthy mineralization intersected was from 57.61 to 59.13 metres (1.52 metres) which analysed 0.31 per cent zinc (Assessment Report 22164).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$6k</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1988</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Georgia Resources Inc.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>325</v>
+      </c>
+      <c r="U21" t="n">
+        <v>57</v>
+      </c>
+      <c r="V21" t="n">
+        <v>58.56778</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-133.48722</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++096</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FISH CREEK</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>103O  005</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
+        <v>55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>55.99139</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-130.03694</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
+        <v>55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LAST SHOT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>103O  003</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>55.9975</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-130.05694</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.7</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2023</v>
+        <v>1987</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>49.27111</v>
+        <v>50.53139</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.73167</v>
+        <v>-125.2025</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDYE PASS                     </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>103J  015</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hunts Inlet</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.7</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,54 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>226 kt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 29.0g/t, Ag 10.0g/t</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.8M</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>54.0275</v>
+        <v>49.73278</v>
       </c>
       <c r="W8" t="n">
-        <v>-130.585</v>
+        <v>-125.21139</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BRIAN BORU (L. 607, 608)</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093M  064</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Red Rose</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 1.1g/t, Ag 143g/t, Cu 0.13%, Pb 1.84%, Zn 16.77%, Co 0.02%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A 15-centimetre channel sample taken from one vein assayed trace gold, 220.5 grams per tonne silver, 1.84 per cent lead, and 11.27 per cent zinc (Geological Survey of Canada Memoir 223). Samples 23201 and 23176 assayed 0.10 and 1.11 grams per tonne gold, 152.0 and 66.0 grams per tonne silver, 0.50 and 0.13 per cent copper, 14.26 and 22.27 per cent zinc with 0.013 and 0.019 per cent cobalt, respectively (Assessment Report 30431).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$1.5M</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Duncastle Gold Corp., Hardy, Samuel Anthony Kyler; Johnson</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>55.07806</v>
+        <v>54.94444</v>
       </c>
       <c r="W9" t="n">
-        <v>-127.60611</v>
+        <v>-126.15722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++064</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1338,21 +1338,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>25.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1414,17 +1414,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>53.09694</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-128.335</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -1434,35 +1434,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>49.47472</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-121.51417</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>6.1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1569,54 +1569,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>50.37417</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-116.36167</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>37.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,33 +1665,29 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>2007</v>
+        <v>1966</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1702,17 +1698,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V13" t="n">
-        <v>58.73611</v>
+        <v>58.88222</v>
       </c>
       <c r="W13" t="n">
-        <v>-133.27</v>
+        <v>-132.1175</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1718,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZOHINI</t>
+          <t xml:space="preserve">CUBA                          </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104K  052</t>
+          <t>082KSE031</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Birchdale</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>16.2</v>
+        <v>3.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1761,54 +1757,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 2.5g/t, Ag 403g/t, Pb 2.40%, Zn 3.30%, Sb 4.20%</t>
+          <t>Ag 423g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A 1.8 metre chip sample assayed 10.6 grams per tonne gold, 1664 grams per tonne silver, 5.12 per cent lead, 0.16 per cent zinc, and 1.89 per cent arsenic. All of the drillholes encountered the shear zone and the best intersection was 2.4 metres of 4.73 grams per tonne gold, 600.69 grams per tonne silver, 6.54 per cent lead, 0.66 per cent zinc and 4.55 per cent antimony (Assessment Report 23858). The weighted average of channel sampling over a 3.9 metre footwall section gave 1.7 grams per tonne gold, 617.1 grams per tonne silver, 2.1 per cent lead, 6.3 per cent zinc, and 1.5 per cent antimony. On the hangingwall section, a 1.8 metre section averaged 3.4 grams per tonne gold, 188.56 grams per tonne silver, 2.7 per cent lead, 3.3 per cent zinc, and 4.2 per cent antimony (New Taku Mines Ltd.).</t>
+          <t>A grab sample from the vein near the shaft assayed 423 grams per tonne silver (Assessment Report 9598).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$491k</t>
+          <t>$5k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2007</v>
+        <v>1982</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Firesteel Resources Inc., Xplorer Minerals Inc., Stow Resources Ltd.</t>
+          <t>Amore Res., Amore Mineral Inc.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="V14" t="n">
-        <v>58.71361</v>
+        <v>50.03639</v>
       </c>
       <c r="W14" t="n">
-        <v>-133.31944</v>
+        <v>-116.9125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE031</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1814,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25.2</v>
+        <v>6.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,35 +1853,25 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>$212k</t>
-        </is>
-      </c>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1989</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
         <v>13</v>
@@ -1894,17 +1880,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>53.09694</v>
+        <v>55.99139</v>
       </c>
       <c r="W15" t="n">
-        <v>-128.335</v>
+        <v>-130.03694</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1900,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>LAST SHOT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>103O  003</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,874 +1939,44 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>$234k</t>
-        </is>
-      </c>
+          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>4</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2010</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>49.47472</v>
+        <v>55.9975</v>
       </c>
       <c r="W16" t="n">
-        <v>-121.51417</v>
+        <v>-130.05694</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DALEY WEST</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>093M  053</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>New Hazelton</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$193k</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>325</v>
-      </c>
-      <c r="U17" t="n">
-        <v>61</v>
-      </c>
-      <c r="V17" t="n">
-        <v>55.22278</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-127.56333</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACE                           </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>104K  025</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Callison Ranch</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Asbestos</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Developed Prospect  </t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>325</v>
-      </c>
-      <c r="U18" t="n">
-        <v>60</v>
-      </c>
-      <c r="V18" t="n">
-        <v>58.88222</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-132.1175</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SCOUT ADIT</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>092HSW176</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Harrison Mills</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Copper, Zinc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ag 1870g/t, Cu 1.11%, Zn 0.24%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>In 2013, two samples (A-1 and A-2) of mineralized vein material assayed 0.306 and 0.236 per cent zinc and 1.565 and 1.11 per cent copper with 2660 and 1870 grams per tonne silver, respectively (Assessment Report 34753).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$34k</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2014</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Reimer, Abram</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>13</v>
-      </c>
-      <c r="T19" t="n">
-        <v>325</v>
-      </c>
-      <c r="U19" t="n">
-        <v>57</v>
-      </c>
-      <c r="V19" t="n">
-        <v>49.24611</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-121.92</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW176</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KENALLAN                      </t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>082LSW045</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Westwold</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Molybdenum</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Molybdenum, Copper, Gold</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>67 t (assay)</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Mo 3.61%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$21k</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>8</v>
-      </c>
-      <c r="T20" t="n">
-        <v>200</v>
-      </c>
-      <c r="U20" t="n">
-        <v>57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>50.43917</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-119.81833</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SPRING</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>104K  096</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Tulsequah</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Silver, Zinc, Copper, Gold, Lead</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Au 0.2g/t, Ag 357g/t, Cu 0.12%, Zn 5.31%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>One of these samples was a grab from a sulphide lens which assayed 0.17 gram per tonne gold, 356.6 grams per tonne silver, 10.3 per cent zinc, and 0.12 per cent copper (Assessment Report 9106). The only noteworthy mineralization intersected was from 57.61 to 59.13 metres (1.52 metres) which analysed 0.31 per cent zinc (Assessment Report 22164).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$6k</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1988</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Georgia Resources Inc.</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>325</v>
-      </c>
-      <c r="U21" t="n">
-        <v>57</v>
-      </c>
-      <c r="V21" t="n">
-        <v>58.56778</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-133.48722</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++096</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>FISH CREEK</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>103O  005</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LAST SHOT</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>103O  003</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>55.9975</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-130.05694</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>093M  076</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Kispiox</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>1987</v>
+        <v>2023</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>50.53139</v>
+        <v>49.27111</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.2025</v>
+        <v>-125.73167</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">EDYE PASS                     </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>103J  015</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Hunts Inlet</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>10.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,54 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>226 kt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 29.0g/t, Ag 10.0g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$1.8M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P8" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.73278</v>
+        <v>54.0275</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.21139</v>
+        <v>-130.585</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>BRIAN BORU (L. 607, 608)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>093M  064</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Red Rose</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 1.1g/t, Ag 143g/t, Cu 0.13%, Pb 1.84%, Zn 16.77%, Co 0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A 15-centimetre channel sample taken from one vein assayed trace gold, 220.5 grams per tonne silver, 1.84 per cent lead, and 11.27 per cent zinc (Geological Survey of Canada Memoir 223). Samples 23201 and 23176 assayed 0.10 and 1.11 grams per tonne gold, 152.0 and 66.0 grams per tonne silver, 0.50 and 0.13 per cent copper, 14.26 and 22.27 per cent zinc with 0.013 and 0.019 per cent cobalt, respectively (Assessment Report 30431).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$1.5M</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Duncastle Gold Corp., Hardy, Samuel Anthony Kyler; Johnson</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="V9" t="n">
-        <v>54.94444</v>
+        <v>55.07806</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.15722</v>
+        <v>-127.60611</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++064</t>
         </is>
       </c>
     </row>
@@ -1338,21 +1338,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>25.2</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1414,17 +1414,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>53.09694</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-128.335</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1434,35 +1434,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>49.47472</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-121.51417</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1569,54 +1569,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>50.37417</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-116.36167</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>37.4</v>
+        <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,29 +1665,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>1966</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1698,17 +1702,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.88222</v>
+        <v>58.73611</v>
       </c>
       <c r="W13" t="n">
-        <v>-132.1175</v>
+        <v>-133.27</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1718,30 +1722,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUBA                          </t>
+          <t>ZOHINI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSE031</t>
+          <t>104K  052</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Birchdale</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.2</v>
+        <v>16.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1757,54 +1761,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 423g/t</t>
+          <t>Au 2.5g/t, Ag 403g/t, Pb 2.40%, Zn 3.30%, Sb 4.20%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A grab sample from the vein near the shaft assayed 423 grams per tonne silver (Assessment Report 9598).</t>
+          <t>A 1.8 metre chip sample assayed 10.6 grams per tonne gold, 1664 grams per tonne silver, 5.12 per cent lead, 0.16 per cent zinc, and 1.89 per cent arsenic. All of the drillholes encountered the shear zone and the best intersection was 2.4 metres of 4.73 grams per tonne gold, 600.69 grams per tonne silver, 6.54 per cent lead, 0.66 per cent zinc and 4.55 per cent antimony (Assessment Report 23858). The weighted average of channel sampling over a 3.9 metre footwall section gave 1.7 grams per tonne gold, 617.1 grams per tonne silver, 2.1 per cent lead, 6.3 per cent zinc, and 1.5 per cent antimony. On the hangingwall section, a 1.8 metre section averaged 3.4 grams per tonne gold, 188.56 grams per tonne silver, 2.7 per cent lead, 3.3 per cent zinc, and 4.2 per cent antimony (New Taku Mines Ltd.).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$5k</t>
+          <t>$491k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>1982</v>
+        <v>2007</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Amore Res., Amore Mineral Inc.</t>
+          <t>Firesteel Resources Inc., Xplorer Minerals Inc., Stow Resources Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>50.03639</v>
+        <v>58.71361</v>
       </c>
       <c r="W14" t="n">
-        <v>-116.9125</v>
+        <v>-133.31944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE031</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++052</t>
         </is>
       </c>
     </row>
@@ -1814,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.6</v>
+        <v>25.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1853,25 +1857,35 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>$212k</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1989</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
         <v>13</v>
@@ -1880,17 +1894,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>55.99139</v>
+        <v>53.09694</v>
       </c>
       <c r="W15" t="n">
-        <v>-130.03694</v>
+        <v>-128.335</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -1900,35 +1914,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAST SHOT</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>103O  003</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1939,44 +1953,874 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>$234k</t>
+        </is>
+      </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>200</v>
+      </c>
+      <c r="U16" t="n">
+        <v>64</v>
+      </c>
+      <c r="V16" t="n">
+        <v>49.47472</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-121.51417</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DALEY WEST</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>093M  053</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New Hazelton</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$193k</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
         <v>13</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>325</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
+        <v>61</v>
+      </c>
+      <c r="V17" t="n">
+        <v>55.22278</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-127.56333</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACE                           </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>104K  025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Callison Ranch</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Asbestos</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Prospect  </t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
+        <v>60</v>
+      </c>
+      <c r="V18" t="n">
+        <v>58.88222</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-132.1175</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SCOUT ADIT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>092HSW176</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Harrison Mills</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Copper, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 1870g/t, Cu 1.11%, Zn 0.24%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>In 2013, two samples (A-1 and A-2) of mineralized vein material assayed 0.306 and 0.236 per cent zinc and 1.565 and 1.11 per cent copper with 2660 and 1870 grams per tonne silver, respectively (Assessment Report 34753).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$34k</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Reimer, Abram</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="n">
+        <v>325</v>
+      </c>
+      <c r="U19" t="n">
+        <v>57</v>
+      </c>
+      <c r="V19" t="n">
+        <v>49.24611</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-121.92</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW176</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KENALLAN                      </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>082LSW045</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Westwold</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Molybdenum</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Molybdenum, Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>67 t (assay)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Mo 3.61%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$21k</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>200</v>
+      </c>
+      <c r="U20" t="n">
+        <v>57</v>
+      </c>
+      <c r="V20" t="n">
+        <v>50.43917</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-119.81833</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SPRING</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>104K  096</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tulsequah</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Silver, Zinc, Copper, Gold, Lead</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 0.2g/t, Ag 357g/t, Cu 0.12%, Zn 5.31%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>One of these samples was a grab from a sulphide lens which assayed 0.17 gram per tonne gold, 356.6 grams per tonne silver, 10.3 per cent zinc, and 0.12 per cent copper (Assessment Report 9106). The only noteworthy mineralization intersected was from 57.61 to 59.13 metres (1.52 metres) which analysed 0.31 per cent zinc (Assessment Report 22164).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$6k</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1988</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Georgia Resources Inc.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>325</v>
+      </c>
+      <c r="U21" t="n">
+        <v>57</v>
+      </c>
+      <c r="V21" t="n">
+        <v>58.56778</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-133.48722</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++096</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FISH CREEK</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>103O  005</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
         <v>55</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V22" t="n">
+        <v>55.99139</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-130.03694</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
+        <v>55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LAST SHOT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>103O  003</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
         <v>55.9975</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W24" t="n">
         <v>-130.05694</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>BRIAN BORU (L. 607, 608)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093M  064</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Red Rose</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1089,33 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 1.1g/t, Ag 143g/t, Cu 0.13%, Pb 1.84%, Zn 16.77%, Co 0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A 15-centimetre channel sample taken from one vein assayed trace gold, 220.5 grams per tonne silver, 1.84 per cent lead, and 11.27 per cent zinc (Geological Survey of Canada Memoir 223). Samples 23201 and 23176 assayed 0.10 and 1.11 grams per tonne gold, 152.0 and 66.0 grams per tonne silver, 0.50 and 0.13 per cent copper, 14.26 and 22.27 per cent zinc with 0.013 and 0.019 per cent cobalt, respectively (Assessment Report 30431).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.5M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P7" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Duncastle Gold Corp., Hardy, Samuel Anthony Kyler; Johnson</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>50.53139</v>
+        <v>55.07806</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.2025</v>
+        <v>-127.60611</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++064</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1225,14 +1225,14 @@
         <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1338,21 +1338,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>25.2</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>1989</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>53.09694</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-128.335</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1434,35 +1434,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>ZOHINI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>104K  052</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.9</v>
+        <v>16.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 2.5g/t, Ag 403g/t, Pb 2.40%, Zn 3.30%, Sb 4.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>A 1.8 metre chip sample assayed 10.6 grams per tonne gold, 1664 grams per tonne silver, 5.12 per cent lead, 0.16 per cent zinc, and 1.89 per cent arsenic. All of the drillholes encountered the shear zone and the best intersection was 2.4 metres of 4.73 grams per tonne gold, 600.69 grams per tonne silver, 6.54 per cent lead, 0.66 per cent zinc and 4.55 per cent antimony (Assessment Report 23858). The weighted average of channel sampling over a 3.9 metre footwall section gave 1.7 grams per tonne gold, 617.1 grams per tonne silver, 2.1 per cent lead, 6.3 per cent zinc, and 1.5 per cent antimony. On the hangingwall section, a 1.8 metre section averaged 3.4 grams per tonne gold, 188.56 grams per tonne silver, 2.7 per cent lead, 3.3 per cent zinc, and 4.2 per cent antimony (New Taku Mines Ltd.).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$491k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Firesteel Resources Inc., Xplorer Minerals Inc., Stow Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>49.47472</v>
+        <v>58.71361</v>
       </c>
       <c r="W11" t="n">
-        <v>-121.51417</v>
+        <v>-133.31944</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++052</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.1</v>
+        <v>25.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1569,33 +1569,33 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2023</v>
+        <v>1989</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1606,17 +1606,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>50.37417</v>
+        <v>53.09694</v>
       </c>
       <c r="W12" t="n">
-        <v>-116.36167</v>
+        <v>-128.335</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>37.4</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,50 +1665,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>4.3 Mt</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1966</v>
+        <v>2010</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V13" t="n">
-        <v>58.88222</v>
+        <v>49.47472</v>
       </c>
       <c r="W13" t="n">
-        <v>-132.1175</v>
+        <v>-121.51417</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1718,30 +1722,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUBA                          </t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSE031</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Birchdale</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1757,54 +1761,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 423g/t</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A grab sample from the vein near the shaft assayed 423 grams per tonne silver (Assessment Report 9598).</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$5k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>1982</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Amore Res., Amore Mineral Inc.</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>50.03639</v>
+        <v>55.22278</v>
       </c>
       <c r="W14" t="n">
-        <v>-116.9125</v>
+        <v>-127.56333</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE031</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -1814,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.6</v>
+        <v>37.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1853,25 +1857,31 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
         <v>13</v>
@@ -1880,17 +1890,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V15" t="n">
-        <v>55.99139</v>
+        <v>58.88222</v>
       </c>
       <c r="W15" t="n">
-        <v>-130.03694</v>
+        <v>-132.1175</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -1900,21 +1910,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAST SHOT</t>
+          <t>SCOUT ADIT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>103O  003</t>
+          <t>092HSW176</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Harrison Mills</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1923,7 +1933,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
+          <t>Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1944,20 +1954,30 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
+          <t>Ag 1870g/t, Cu 1.11%, Zn 0.24%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>In 2013, two samples (A-1 and A-2) of mineralized vein material assayed 0.306 and 0.236 per cent zinc and 1.565 and 1.11 per cent copper with 2660 and 1870 grams per tonne silver, respectively (Assessment Report 34753).</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>$34k</t>
+        </is>
+      </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2014</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Reimer, Abram</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
         <v>13</v>
@@ -1966,17 +1986,643 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
+        <v>57</v>
+      </c>
+      <c r="V16" t="n">
+        <v>49.24611</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-121.92</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW176</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AVON</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>092F  350</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Chetarpe</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$33k</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>57</v>
+      </c>
+      <c r="V17" t="n">
+        <v>49.40417</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-125.75833</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KENALLAN                      </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>082LSW045</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Westwold</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Molybdenum</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Molybdenum, Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>67 t (assay)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Mo 3.61%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$21k</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="n">
+        <v>250</v>
+      </c>
+      <c r="U18" t="n">
+        <v>57</v>
+      </c>
+      <c r="V18" t="n">
+        <v>50.43917</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-119.81833</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="n">
+        <v>325</v>
+      </c>
+      <c r="U19" t="n">
         <v>55</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V19" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FISH CREEK</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>103O  005</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>13</v>
+      </c>
+      <c r="T20" t="n">
+        <v>325</v>
+      </c>
+      <c r="U20" t="n">
+        <v>55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>55.99139</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-130.03694</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LAST SHOT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>103O  003</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>325</v>
+      </c>
+      <c r="U21" t="n">
+        <v>55</v>
+      </c>
+      <c r="V21" t="n">
         <v>55.9975</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W21" t="n">
         <v>-130.05694</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
+        <v>55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER QUEEN (L. 1182)        </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>082LSW010</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Silver Star</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Silver, Lead, Zinc, Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ag 1197.5g/t, Pb 18.2%, Zn 1.55%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>A sample from initial surface sampling in 1896 assayed 13.4 grams per tonne gold ($8) and 83.6 grams per tonne silver ($50) (Minister of Mines Annual Report 1896 page 579). Shipments in 1948 and 1950, totalling 3.4 tonnes, assayed 870 grams per tonne silver, 13 per cent lead and 1 per cent zinc.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Conditional Registration Reserve (Ski Development) — special process</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="n">
+        <v>225</v>
+      </c>
+      <c r="U23" t="n">
+        <v>55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>50.37306</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-119.05861</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW010</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BRIAN BORU (L. 607, 608)</t>
+          <t xml:space="preserve">SILVER BELT (L.5695)          </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>093M  064</t>
+          <t>082KNW159</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Red Rose</t>
+          <t>Five Mile</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>10.6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Copper</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1092,51 +1092,43 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Au 1.1g/t, Ag 143g/t, Cu 0.13%, Pb 1.84%, Zn 16.77%, Co 0.02%</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>A 15-centimetre channel sample taken from one vein assayed trace gold, 220.5 grams per tonne silver, 1.84 per cent lead, and 11.27 per cent zinc (Geological Survey of Canada Memoir 223). Samples 23201 and 23176 assayed 0.10 and 1.11 grams per tonne gold, 152.0 and 66.0 grams per tonne silver, 0.50 and 0.13 per cent copper, 14.26 and 22.27 per cent zinc with 0.013 and 0.019 per cent cobalt, respectively (Assessment Report 30431).</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.5M</t>
+          <t>$2.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Duncastle Gold Corp., Hardy, Samuel Anthony Kyler; Johnson</t>
+          <t>Mineral Mountain Resources Ltd., Denny, Jack Norman; Mirko</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>55.07806</v>
+        <v>50.61639</v>
       </c>
       <c r="W7" t="n">
-        <v>-127.60611</v>
+        <v>-117.32333</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++064</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW159</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1138,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>16.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,54 +1177,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2023</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>49.27111</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-125.73167</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>31.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,33 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1318,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>58.90944</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-129.09278</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1338,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1361,12 +1353,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1434,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZOHINI</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>104K  052</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16.2</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1457,12 +1449,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,33 +1465,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 2.5g/t, Ag 403g/t, Pb 2.40%, Zn 3.30%, Sb 4.20%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A 1.8 metre chip sample assayed 10.6 grams per tonne gold, 1664 grams per tonne silver, 5.12 per cent lead, 0.16 per cent zinc, and 1.89 per cent arsenic. All of the drillholes encountered the shear zone and the best intersection was 2.4 metres of 4.73 grams per tonne gold, 600.69 grams per tonne silver, 6.54 per cent lead, 0.66 per cent zinc and 4.55 per cent antimony (Assessment Report 23858). The weighted average of channel sampling over a 3.9 metre footwall section gave 1.7 grams per tonne gold, 617.1 grams per tonne silver, 2.1 per cent lead, 6.3 per cent zinc, and 1.5 per cent antimony. On the hangingwall section, a 1.8 metre section averaged 3.4 grams per tonne gold, 188.56 grams per tonne silver, 2.7 per cent lead, 3.3 per cent zinc, and 4.2 per cent antimony (New Taku Mines Ltd.).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$491k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2007</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Firesteel Resources Inc., Xplorer Minerals Inc., Stow Resources Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1510,17 +1502,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>58.71361</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-133.31944</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>25.2</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,7 +1545,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1569,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1989</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>53.09694</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-128.335</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1618,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,54 +1657,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.47472</v>
+        <v>58.185</v>
       </c>
       <c r="W13" t="n">
-        <v>-121.51417</v>
+        <v>-125.30611</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.7</v>
+        <v>39.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,7 +1737,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1766,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1798,17 +1790,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>55.22278</v>
+        <v>58.15222</v>
       </c>
       <c r="W14" t="n">
-        <v>-127.56333</v>
+        <v>-125.27778</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1810,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">HILL 60                       </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>082KSW168</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Retallack</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>37.4</v>
+        <v>8.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,50 +1849,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Ag 146g/t, Pb 8.78%, Zn 6.31%</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>The weighted average of 16 channel samples taken at surface over an average width of 50.5 centimetres and a strike length of 48 metres is 6.31 per cent zinc, 8.78 per cent lead and 146.4 grams per tonne silver (Assessment Report 13246).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$361k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>1966</v>
+        <v>2024</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Cavan Ventures Ltd., Baraniuk, Lawrence Nester</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.88222</v>
+        <v>50.02583</v>
       </c>
       <c r="W15" t="n">
-        <v>-132.1175</v>
+        <v>-117.02278</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW168</t>
         </is>
       </c>
     </row>
@@ -1910,35 +1906,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SCOUT ADIT</t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092HSW176</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Harrison Mills</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.7</v>
+        <v>25.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1949,33 +1945,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 1870g/t, Cu 1.11%, Zn 0.24%</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 2013, two samples (A-1 and A-2) of mineralized vein material assayed 0.306 and 0.236 per cent zinc and 1.565 and 1.11 per cent copper with 2660 and 1870 grams per tonne silver, respectively (Assessment Report 34753).</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$34k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2014</v>
+        <v>1989</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Reimer, Abram</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1986,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>49.24611</v>
+        <v>53.09694</v>
       </c>
       <c r="W16" t="n">
-        <v>-121.92</v>
+        <v>-128.335</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW176</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -2006,35 +2002,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>24.6</v>
+        <v>6.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2045,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$33k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1985</v>
+        <v>2010</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U17" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="V17" t="n">
-        <v>49.40417</v>
+        <v>49.47472</v>
       </c>
       <c r="W17" t="n">
-        <v>-125.75833</v>
+        <v>-121.51417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -2102,30 +2098,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">KENALLAN                      </t>
+          <t xml:space="preserve">BOYA MAIN FACE                </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>082LSW045</t>
+          <t>094M  021</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Westwold</t>
+          <t>Skooks Landing</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.6</v>
+        <v>47.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Tungsten, Molybdenum, Copper, Lead, Zinc, Bismuth</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2141,54 +2137,54 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>67 t (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Mo 3.61%</t>
+          <t>Cu 0.11%, Mo 0.20%, W 0.35%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
+          <t>Several outcrops of this rock contain layers of pyrrhotite-chalcopyrite-scheelite mineralization, a select grab sample of which assayed 0.11 per cent copper and 0.15 per cent tungsten trioxide (Assessment Report 7915, page 11). Samples of drillcore yielded low assay values, no more than 0.2 per cent molybdenum disulfide and 0.55 per cent tungsten trioxide (Assessment Report 8008);</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$21k</t>
+          <t>$81k</t>
         </is>
       </c>
       <c r="O18" t="n">
         <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
+          <t>Archer, Cathro &amp; Associates (1981) Limited, Cathro &amp; Associates (1981) Limited; Precipitate Gold Corp.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>50.43917</v>
+        <v>59.23417</v>
       </c>
       <c r="W18" t="n">
-        <v>-119.81833</v>
+        <v>-127.48639</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094M++021</t>
         </is>
       </c>
     </row>
@@ -2198,21 +2194,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2221,7 +2217,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2237,44 +2233,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>55.33556</v>
+        <v>52.85806</v>
       </c>
       <c r="W19" t="n">
-        <v>-127.69194</v>
+        <v>-132.15722</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2284,35 +2290,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.6</v>
+        <v>37.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2323,25 +2329,31 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
         <v>13</v>
@@ -2350,279 +2362,17 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V20" t="n">
-        <v>55.99139</v>
+        <v>58.88222</v>
       </c>
       <c r="W20" t="n">
-        <v>-130.03694</v>
+        <v>-132.1175</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LAST SHOT</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>103O  003</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>325</v>
-      </c>
-      <c r="U21" t="n">
-        <v>55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>55.9975</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-130.05694</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER QUEEN (L. 1182)        </t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>082LSW010</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Silver Star</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Silver, Lead, Zinc, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Ag 1197.5g/t, Pb 18.2%, Zn 1.55%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>A sample from initial surface sampling in 1896 assayed 13.4 grams per tonne gold ($8) and 83.6 grams per tonne silver ($50) (Minister of Mines Annual Report 1896 page 579). Shipments in 1948 and 1950, totalling 3.4 tonnes, assayed 870 grams per tonne silver, 13 per cent lead and 1 per cent zinc.</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Conditional Registration Reserve (Ski Development) — special process</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>9</v>
-      </c>
-      <c r="T23" t="n">
-        <v>225</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>50.37306</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-119.05861</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1138,21 +1138,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t xml:space="preserve">EDYE PASS                     </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>103J  015</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Hunts Inlet</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.7</v>
+        <v>10.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1177,33 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>226 kt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Au 29.0g/t, Ag 10.0g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$1.8M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P8" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1214,17 @@
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.27111</v>
+        <v>54.0275</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.73167</v>
+        <v>-130.585</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1234,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31.5</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1273,33 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>58.90944</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-129.09278</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1409,14 +1409,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>58.73611</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-133.27</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>ZOHINI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104K  052</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>16.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,28 +1662,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 2.5g/t, Ag 403g/t, Pb 2.40%, Zn 3.30%, Sb 4.20%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A 1.8 metre chip sample assayed 10.6 grams per tonne gold, 1664 grams per tonne silver, 5.12 per cent lead, 0.16 per cent zinc, and 1.89 per cent arsenic. All of the drillholes encountered the shear zone and the best intersection was 2.4 metres of 4.73 grams per tonne gold, 600.69 grams per tonne silver, 6.54 per cent lead, 0.66 per cent zinc and 4.55 per cent antimony (Assessment Report 23858). The weighted average of channel sampling over a 3.9 metre footwall section gave 1.7 grams per tonne gold, 617.1 grams per tonne silver, 2.1 per cent lead, 6.3 per cent zinc, and 1.5 per cent antimony. On the hangingwall section, a 1.8 metre section averaged 3.4 grams per tonne gold, 188.56 grams per tonne silver, 2.7 per cent lead, 3.3 per cent zinc, and 4.2 per cent antimony (New Taku Mines Ltd.).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$491k</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Firesteel Resources Inc., Xplorer Minerals Inc., Stow Resources Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1697,14 +1697,14 @@
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.185</v>
+        <v>58.71361</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.30611</v>
+        <v>-133.31944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++052</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">HILL 60                       </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>082KSW168</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Retallack</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39.3</v>
+        <v>8.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,49 +1758,49 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Ag 146g/t, Pb 8.78%, Zn 6.31%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>The weighted average of 16 channel samples taken at surface over an average width of 50.5 centimetres and a strike length of 48 metres is 6.31 per cent zinc, 8.78 per cent lead and 146.4 grams per tonne silver (Assessment Report 13246).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$361k</t>
         </is>
       </c>
       <c r="O14" t="n">
         <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Cavan Ventures Ltd., Baraniuk, Lawrence Nester</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.15222</v>
+        <v>50.02583</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.27778</v>
+        <v>-117.02278</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW168</t>
         </is>
       </c>
     </row>
@@ -1810,35 +1810,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HILL 60                       </t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>082KSW168</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Retallack</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.4</v>
+        <v>25.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1849,54 +1849,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 146g/t, Pb 8.78%, Zn 6.31%</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The weighted average of 16 channel samples taken at surface over an average width of 50.5 centimetres and a strike length of 48 metres is 6.31 per cent zinc, 8.78 per cent lead and 146.4 grams per tonne silver (Assessment Report 13246).</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$361k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2024</v>
+        <v>1989</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Cavan Ventures Ltd., Baraniuk, Lawrence Nester</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>50.02583</v>
+        <v>53.09694</v>
       </c>
       <c r="W15" t="n">
-        <v>-117.02278</v>
+        <v>-128.335</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW168</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>25.2</v>
+        <v>6.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,54 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1989</v>
+        <v>2010</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="V16" t="n">
-        <v>53.09694</v>
+        <v>49.47472</v>
       </c>
       <c r="W16" t="n">
-        <v>-128.335</v>
+        <v>-121.51417</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -2002,35 +2002,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.9</v>
+        <v>37.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2041,54 +2041,50 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>2010</v>
+        <v>1966</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="V17" t="n">
-        <v>49.47472</v>
+        <v>58.88222</v>
       </c>
       <c r="W17" t="n">
-        <v>-121.51417</v>
+        <v>-132.1175</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2098,30 +2094,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOYA MAIN FACE                </t>
+          <t>SCOUT ADIT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>094M  021</t>
+          <t>092HSW176</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Skooks Landing</t>
+          <t>Harrison Mills</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>47.4</v>
+        <v>2.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tungsten, Molybdenum, Copper, Lead, Zinc, Bismuth</t>
+          <t>Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2142,28 +2138,28 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 0.11%, Mo 0.20%, W 0.35%</t>
+          <t>Ag 1870g/t, Cu 1.11%, Zn 0.24%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Several outcrops of this rock contain layers of pyrrhotite-chalcopyrite-scheelite mineralization, a select grab sample of which assayed 0.11 per cent copper and 0.15 per cent tungsten trioxide (Assessment Report 7915, page 11). Samples of drillcore yielded low assay values, no more than 0.2 per cent molybdenum disulfide and 0.55 per cent tungsten trioxide (Assessment Report 8008);</t>
+          <t>In 2013, two samples (A-1 and A-2) of mineralized vein material assayed 0.306 and 0.236 per cent zinc and 1.565 and 1.11 per cent copper with 2660 and 1870 grams per tonne silver, respectively (Assessment Report 34753).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$81k</t>
+          <t>$34k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Archer, Cathro &amp; Associates (1981) Limited, Cathro &amp; Associates (1981) Limited; Precipitate Gold Corp.</t>
+          <t>Reimer, Abram</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2174,17 +2170,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V18" t="n">
-        <v>59.23417</v>
+        <v>49.24611</v>
       </c>
       <c r="W18" t="n">
-        <v>-127.48639</v>
+        <v>-121.92</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094M++021</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW176</t>
         </is>
       </c>
     </row>
@@ -2194,30 +2190,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">KENALLAN                      </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>082LSW045</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Westwold</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.4</v>
+        <v>4.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2233,54 +2229,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>67 t (assay)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Mo 3.61%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$21k</t>
         </is>
       </c>
       <c r="O19" t="n">
         <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>1999</v>
+        <v>2022</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V19" t="n">
-        <v>52.85806</v>
+        <v>50.43917</v>
       </c>
       <c r="W19" t="n">
-        <v>-132.15722</v>
+        <v>-119.81833</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
         </is>
       </c>
     </row>
@@ -2290,35 +2286,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>SPRING</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104K  096</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Silver, Zinc, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2329,29 +2325,33 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Au 0.2g/t, Ag 357g/t, Cu 0.12%, Zn 5.31%</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>One of these samples was a grab from a sulphide lens which assayed 0.17 gram per tonne gold, 356.6 grams per tonne silver, 10.3 per cent zinc, and 0.12 per cent copper (Assessment Report 9106). The only noteworthy mineralization intersected was from 57.61 to 59.13 metres (1.52 metres) which analysed 0.31 per cent zinc (Assessment Report 22164).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$6k</t>
         </is>
       </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>1966</v>
+        <v>1988</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Georgia Resources Inc.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -2362,17 +2362,275 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>58.88222</v>
+        <v>58.56778</v>
       </c>
       <c r="W20" t="n">
-        <v>-132.1175</v>
+        <v>-133.48722</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++096</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FISH CREEK</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>103O  005</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>325</v>
+      </c>
+      <c r="U21" t="n">
+        <v>55</v>
+      </c>
+      <c r="V21" t="n">
+        <v>55.99139</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-130.03694</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
+        <v>55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LAST SHOT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>103O  003</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
+        <v>55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>55.9975</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-130.05694</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELT (L.5695)          </t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>082KNW159</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Five Mile</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.6</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,46 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>3 t</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Au 15.1g/t</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$2.2M</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Mineral Mountain Resources Ltd., Denny, Jack Norman; Mirko</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
         <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>50.61639</v>
+        <v>49.27111</v>
       </c>
       <c r="W7" t="n">
-        <v>-117.32333</v>
+        <v>-125.73167</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW159</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1138,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDYE PASS                     </t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>103J  015</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hunts Inlet</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1177,54 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>226 kt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 29.0g/t, Ag 10.0g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.8M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>54.0275</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-130.585</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1281,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1313,14 +1321,14 @@
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1434,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,12 +1457,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>58.185</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.30611</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1522,30 +1530,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>INTERNATIONAL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>082KNE058</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Poplar Creek</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1566,28 +1574,28 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Ag 562g/t, Pb 39.20%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>The sample assayed 445.72 grams per tonne silver, 37.7 per cent lead and 1.2 per cent zinc (Minister of Mines Annual Report 1918, page 162). The average grades of 562.3 grams per tonne silver and 39.2 per cent lead are fairly typical of historical assays from old workings going back to the early 1900’s (V STOCKWATCH, March 29, 2012). A sample taken across 0.9 metre from the face of the east drift yielded 384 grams per tonne silver and 30 per cent lead (Starr, 1926 (Property File)).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$346k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Canadian Critical Minerals Inc. (FMC #278750), Canadian Critical Minerals Inc. (FMC #278750); Johnston, David W.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1601,14 +1609,14 @@
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>58.73611</v>
+        <v>50.53278</v>
       </c>
       <c r="W12" t="n">
-        <v>-133.27</v>
+        <v>-116.94528</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNE058</t>
         </is>
       </c>
     </row>
@@ -1618,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZOHINI</t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  052</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>16.2</v>
+        <v>25.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1657,33 +1665,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 2.5g/t, Ag 403g/t, Pb 2.40%, Zn 3.30%, Sb 4.20%</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>A 1.8 metre chip sample assayed 10.6 grams per tonne gold, 1664 grams per tonne silver, 5.12 per cent lead, 0.16 per cent zinc, and 1.89 per cent arsenic. All of the drillholes encountered the shear zone and the best intersection was 2.4 metres of 4.73 grams per tonne gold, 600.69 grams per tonne silver, 6.54 per cent lead, 0.66 per cent zinc and 4.55 per cent antimony (Assessment Report 23858). The weighted average of channel sampling over a 3.9 metre footwall section gave 1.7 grams per tonne gold, 617.1 grams per tonne silver, 2.1 per cent lead, 6.3 per cent zinc, and 1.5 per cent antimony. On the hangingwall section, a 1.8 metre section averaged 3.4 grams per tonne gold, 188.56 grams per tonne silver, 2.7 per cent lead, 3.3 per cent zinc, and 4.2 per cent antimony (New Taku Mines Ltd.).</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$491k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2007</v>
+        <v>1989</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Firesteel Resources Inc., Xplorer Minerals Inc., Stow Resources Ltd.</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1697,14 +1705,14 @@
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.71361</v>
+        <v>53.09694</v>
       </c>
       <c r="W13" t="n">
-        <v>-133.31944</v>
+        <v>-128.335</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -1714,35 +1722,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HILL 60                       </t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSW168</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Retallack</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1753,54 +1761,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 146g/t, Pb 8.78%, Zn 6.31%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The weighted average of 16 channel samples taken at surface over an average width of 50.5 centimetres and a strike length of 48 metres is 6.31 per cent zinc, 8.78 per cent lead and 146.4 grams per tonne silver (Assessment Report 13246).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$361k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Cavan Ventures Ltd., Baraniuk, Lawrence Nester</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="V14" t="n">
-        <v>50.02583</v>
+        <v>49.47472</v>
       </c>
       <c r="W14" t="n">
-        <v>-117.02278</v>
+        <v>-121.51417</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSW168</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1810,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25.2</v>
+        <v>37.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1849,33 +1857,29 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>215 t</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>1989</v>
+        <v>1966</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1890,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V15" t="n">
-        <v>53.09694</v>
+        <v>58.88222</v>
       </c>
       <c r="W15" t="n">
-        <v>-128.335</v>
+        <v>-132.1175</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -1906,35 +1910,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t xml:space="preserve">KENALLAN                      </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>082LSW045</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Westwold</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.9</v>
+        <v>4.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1945,54 +1949,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>67 t (assay)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Mo 3.61%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$21k</t>
         </is>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="U16" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>49.47472</v>
+        <v>50.43917</v>
       </c>
       <c r="W16" t="n">
-        <v>-121.51417</v>
+        <v>-119.81833</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
         </is>
       </c>
     </row>
@@ -2002,35 +2006,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37.4</v>
+        <v>7.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2041,31 +2045,25 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>13</v>
@@ -2074,17 +2072,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>58.88222</v>
+        <v>55.98833</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.1175</v>
+        <v>-130.06194</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2094,21 +2092,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SCOUT ADIT</t>
+          <t>LAST SHOT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092HSW176</t>
+          <t>103O  003</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Harrison Mills</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2117,7 +2115,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc</t>
+          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2138,30 +2136,20 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 1870g/t, Cu 1.11%, Zn 0.24%</t>
+          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>In 2013, two samples (A-1 and A-2) of mineralized vein material assayed 0.306 and 0.236 per cent zinc and 1.565 and 1.11 per cent copper with 2660 and 1870 grams per tonne silver, respectively (Assessment Report 34753).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$34k</t>
-        </is>
-      </c>
+          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2014</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Reimer, Abram</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2170,17 +2158,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>49.24611</v>
+        <v>55.9975</v>
       </c>
       <c r="W18" t="n">
-        <v>-121.92</v>
+        <v>-130.05694</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW176</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
         </is>
       </c>
     </row>
@@ -2190,30 +2178,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">KENALLAN                      </t>
+          <t xml:space="preserve">SILVER QUEEN (L. 1182)        </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082LSW045</t>
+          <t>082LSW010</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Westwold</t>
+          <t>Silver Star</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Silver, Lead, Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2225,58 +2213,52 @@
         <v>1</v>
       </c>
       <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 1197.5g/t, Pb 18.2%, Zn 1.55%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>A sample from initial surface sampling in 1896 assayed 13.4 grams per tonne gold ($8) and 83.6 grams per tonne silver ($50) (Minister of Mines Annual Report 1896 page 579). Shipments in 1948 and 1950, totalling 3.4 tonnes, assayed 870 grams per tonne silver, 13 per cent lead and 1 per cent zinc.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>67 t (assay)</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Mo 3.61%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$21k</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Conditional Registration Reserve (Ski Development) — special process</t>
+        </is>
+      </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="U19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>50.43917</v>
+        <v>50.37306</v>
       </c>
       <c r="W19" t="n">
-        <v>-119.81833</v>
+        <v>-119.05861</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW010</t>
         </is>
       </c>
     </row>
@@ -2286,30 +2268,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SPRING</t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>104K  096</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Copper, Gold, Lead</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2330,30 +2312,20 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 0.2g/t, Ag 357g/t, Cu 0.12%, Zn 5.31%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>One of these samples was a grab from a sulphide lens which assayed 0.17 gram per tonne gold, 356.6 grams per tonne silver, 10.3 per cent zinc, and 0.12 per cent copper (Assessment Report 9106). The only noteworthy mineralization intersected was from 57.61 to 59.13 metres (1.52 metres) which analysed 0.31 per cent zinc (Assessment Report 22164).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$6k</t>
-        </is>
-      </c>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1988</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Georgia Resources Inc.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
         <v>13</v>
@@ -2362,17 +2334,17 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>58.56778</v>
+        <v>55.99139</v>
       </c>
       <c r="W20" t="n">
-        <v>-133.48722</v>
+        <v>-130.03694</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++096</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2382,21 +2354,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2421,17 +2393,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2451,186 +2423,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>55.99139</v>
+        <v>56.00194</v>
       </c>
       <c r="W21" t="n">
-        <v>-130.03694</v>
+        <v>-130.04972</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>LAST SHOT</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>103O  003</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>55.9975</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-130.05694</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -736,10 +736,10 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="U3" t="n">
         <v>85</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t xml:space="preserve">SILVER BELT (L.5695)          </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>082KNW159</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Five Mile</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.7</v>
+        <v>10.6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,46 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3 t</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Au 15.1g/t</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$2.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Mineral Mountain Resources Ltd., Denny, Jack Norman; Mirko</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U7" t="n">
         <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>49.27111</v>
+        <v>50.61639</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.73167</v>
+        <v>-117.32333</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW159</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1138,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>16.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,54 +1177,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2023</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>49.27111</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-125.73167</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,33 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1321,14 +1313,14 @@
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1434,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1457,12 +1449,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>58.185</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.30611</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1530,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INTERNATIONAL</t>
+          <t>WESTERN COPPER</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>082KNE058</t>
+          <t>103H  033</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Poplar Creek</t>
+          <t>Butedale</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18.6</v>
+        <v>25.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1569,33 +1561,33 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>215 t</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 562g/t, Pb 39.20%</t>
+          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The sample assayed 445.72 grams per tonne silver, 37.7 per cent lead and 1.2 per cent zinc (Minister of Mines Annual Report 1918, page 162). The average grades of 562.3 grams per tonne silver and 39.2 per cent lead are fairly typical of historical assays from old workings going back to the early 1900’s (V STOCKWATCH, March 29, 2012). A sample taken across 0.9 metre from the face of the east drift yielded 384 grams per tonne silver and 30 per cent lead (Starr, 1926 (Property File)).</t>
+          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$346k</t>
+          <t>$212k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2013</v>
+        <v>1989</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Canadian Critical Minerals Inc. (FMC #278750), Canadian Critical Minerals Inc. (FMC #278750); Johnston, David W.</t>
+          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1609,14 +1601,14 @@
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>50.53278</v>
+        <v>53.09694</v>
       </c>
       <c r="W12" t="n">
-        <v>-116.94528</v>
+        <v>-128.335</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
         </is>
       </c>
     </row>
@@ -1626,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25.2</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1665,54 +1657,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1989</v>
+        <v>2010</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="V13" t="n">
-        <v>53.09694</v>
+        <v>49.47472</v>
       </c>
       <c r="W13" t="n">
-        <v>-128.335</v>
+        <v>-121.51417</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1722,35 +1714,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1761,54 +1753,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>49.47472</v>
+        <v>50.37417</v>
       </c>
       <c r="W14" t="n">
-        <v>-121.51417</v>
+        <v>-116.36167</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1810,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>37.4</v>
+        <v>11.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,50 +1849,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>544 t</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Au 8.7g/t</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>1966</v>
+        <v>1999</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>58.88222</v>
+        <v>52.85806</v>
       </c>
       <c r="W15" t="n">
-        <v>-132.1175</v>
+        <v>-132.15722</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -1910,35 +1906,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">KENALLAN                      </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>082LSW045</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Westwold</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.6</v>
+        <v>37.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1949,488 +1945,50 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>67 t (assay)</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Mo 3.61%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Samples taken by government engineers assayed as high as 3.61 per cent molybdenite (Assessment Report 282).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$21k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2022</v>
+        <v>1966</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Snowy Creek Resources Ltd., Marlow, Jeremy M (FMC# 140671)</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="V16" t="n">
-        <v>50.43917</v>
+        <v>58.88222</v>
       </c>
       <c r="W16" t="n">
-        <v>-119.81833</v>
+        <v>-132.1175</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW045</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>325</v>
-      </c>
-      <c r="U17" t="n">
-        <v>55</v>
-      </c>
-      <c r="V17" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LAST SHOT</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>103O  003</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Silver, Lead, Zinc, Copper, Gold, Tungsten</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Au 2.7g/t, Ag 387g/t, Cu 4.85%, Pb 6.20%</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>A channel sample across 66 centimetres of sulphide assayed 387.36 grams per tonne silver, 6.2 per cent lead, 4.85 per cent copper and 2.74 grams per tonne gold (United States Geological Survey Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>325</v>
-      </c>
-      <c r="U18" t="n">
-        <v>55</v>
-      </c>
-      <c r="V18" t="n">
-        <v>55.9975</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-130.05694</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++003</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER QUEEN (L. 1182)        </t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>082LSW010</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver Star</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Lead, Zinc, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ag 1197.5g/t, Pb 18.2%, Zn 1.55%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>A sample from initial surface sampling in 1896 assayed 13.4 grams per tonne gold ($8) and 83.6 grams per tonne silver ($50) (Minister of Mines Annual Report 1896 page 579). Shipments in 1948 and 1950, totalling 3.4 tonnes, assayed 870 grams per tonne silver, 13 per cent lead and 1 per cent zinc.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Conditional Registration Reserve (Ski Development) — special process</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>9</v>
-      </c>
-      <c r="T19" t="n">
-        <v>225</v>
-      </c>
-      <c r="U19" t="n">
-        <v>55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>50.37306</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-119.05861</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSW010</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>FISH CREEK</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>103O  005</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>13</v>
-      </c>
-      <c r="T20" t="n">
-        <v>325</v>
-      </c>
-      <c r="U20" t="n">
-        <v>55</v>
-      </c>
-      <c r="V20" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROANAN                        </t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>104B  164</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>325</v>
-      </c>
-      <c r="U21" t="n">
-        <v>55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>56.00194</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-130.04972</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -666,12 +666,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DRIFTPILE CREEK</t>
+          <t>TORO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>094K  066</t>
+          <t>094K  050</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>13.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Barite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -705,54 +705,54 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>18.1 Mt</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Pb 1.18%, Zn 10.00%</t>
+          <t>Cu 2.95%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
+          <t>Chip samples (B374289 and B374339), from the Toro occurrence area yielded 7.44 and 8.23 per cent copper over 2.00 and 1.50 metres, respectively, whereas a select sample (B374338) assayed 29.8 per cent copper and 3.1 grams per tonne silver (Harrington, E. Surface samples of the vein averaged 2.95 per cent copper over 2.4 metres (Geology, Exploration and Mining in British Columbia 1971).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>$1.4M</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
+          <t>Twenty-Seven Capital Corp., Fabled Copper Corp., Pugh</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="V3" t="n">
-        <v>58.06639</v>
+        <v>58.37694</v>
       </c>
       <c r="W3" t="n">
-        <v>-125.90972</v>
+        <v>-125.19583</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++050</t>
         </is>
       </c>
     </row>
@@ -762,30 +762,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TORO</t>
+          <t>ERICKSEN-ASHBY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>094K  050</t>
+          <t>104K  009</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>13.8</v>
+        <v>5.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -801,33 +801,33 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>907 kt</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 2.95%</t>
+          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Chip samples (B374289 and B374339), from the Toro occurrence area yielded 7.44 and 8.23 per cent copper over 2.00 and 1.50 metres, respectively, whereas a select sample (B374338) assayed 29.8 per cent copper and 3.1 grams per tonne silver (Harrington, E. Surface samples of the vein averaged 2.95 per cent copper over 2.4 metres (Geology, Exploration and Mining in British Columbia 1971).</t>
+          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$286k</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Twenty-Seven Capital Corp., Fabled Copper Corp., Pugh</t>
+          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -838,17 +838,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="V4" t="n">
-        <v>58.37694</v>
+        <v>58.65806</v>
       </c>
       <c r="W4" t="n">
-        <v>-125.19583</v>
+        <v>-133.475</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
         </is>
       </c>
     </row>
@@ -858,30 +858,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ERICKSEN-ASHBY</t>
+          <t>DRIFTPILE CREEK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>104K  009</t>
+          <t>094K  066</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.3</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
+          <t>Zinc, Lead, Barite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,54 +897,54 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>907 kt</t>
+          <t>18.1 Mt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
+          <t>Pb 1.18%, Zn 10.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
+          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>$286k</t>
+          <t>$1.4M</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
+          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="V5" t="n">
-        <v>58.65806</v>
+        <v>58.06639</v>
       </c>
       <c r="W5" t="n">
-        <v>-133.475</v>
+        <v>-125.90972</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
         </is>
       </c>
     </row>
@@ -954,21 +954,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUNTER                        </t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>103H  034</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21.7</v>
+        <v>16.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -977,12 +977,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>94 kt (uncategorized)</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 12g/t</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Six samples taken across this width over a 17.4 metre length averaged 35.35 grams per tonne gold and 87.1 grams per tonne silver (Assessment Report 13398). The vein is commonly 8 to 20 centimetres thick and 6 samples along a 12.5-metre length averaged 67.0 grams per tonne gold, 32.57 grams per tonne silver and 0.67 per cent copper over an average width of 0.19 metre (Assessment Report 11937). Unclassified reserves for the Hunter property are 94,338 tonnes grading 12 grams per tonne gold, diluted to a 1.2 metre mining width (George Cross News Letter June 13, 1984).</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$281k</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>1984</v>
+        <v>2023</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Du-Well Res., Arnhem Resources Inc.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V6" t="n">
-        <v>53.19417</v>
+        <v>49.27111</v>
       </c>
       <c r="W6" t="n">
-        <v>-128.385</v>
+        <v>-125.73167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++034</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELT (L.5695)          </t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>082KNW159</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Five Mile</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,46 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>118 kt (assay)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$2.2M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>1987</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Mineral Mountain Resources Ltd., Denny, Jack Norman; Mirko</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>50.61639</v>
+        <v>50.53139</v>
       </c>
       <c r="W7" t="n">
-        <v>-117.32333</v>
+        <v>-125.2025</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KNW159</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1138,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.7</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1161,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1177,54 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>49.27111</v>
+        <v>49.73278</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.73167</v>
+        <v>-125.21139</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1242,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1257,12 +1265,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>54.94444</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-126.15722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1406,17 +1414,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>58.185</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-125.30611</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1434,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>39.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,12 +1457,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>58.15222</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.27778</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1522,30 +1530,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WESTERN COPPER</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>103H  033</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Butedale</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>25.2</v>
+        <v>6.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1561,54 +1569,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>215 t</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 5.5g/t, Ag 213g/t, Cu 15.50%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The largest lens measures 10 metres long and 1.5 metres wide of which a 60 centimetre sample assayed 15.5 per cent copper, 212.6 grams per tonne silver, and 5.5 grams per tonne gold (Bulletin 1).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$212k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1989</v>
+        <v>2010</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Freemont Gold Corporation, Noranda Mining and Exploration Inc.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="V12" t="n">
-        <v>53.09694</v>
+        <v>49.47472</v>
       </c>
       <c r="W12" t="n">
-        <v>-128.335</v>
+        <v>-121.51417</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103H++033</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1618,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>21</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1657,54 +1665,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="V13" t="n">
-        <v>49.47472</v>
+        <v>58.73639</v>
       </c>
       <c r="W13" t="n">
-        <v>-121.51417</v>
+        <v>-133.24944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1753,33 +1761,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1801,14 @@
         <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>50.37417</v>
+        <v>50.16611</v>
       </c>
       <c r="W14" t="n">
-        <v>-116.36167</v>
+        <v>-125.39944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1989,6 +1997,264 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>325</v>
+      </c>
+      <c r="U17" t="n">
+        <v>55</v>
+      </c>
+      <c r="V17" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="n">
+        <v>250</v>
+      </c>
+      <c r="U18" t="n">
+        <v>55</v>
+      </c>
+      <c r="V18" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="n">
+        <v>325</v>
+      </c>
+      <c r="U19" t="n">
+        <v>55</v>
+      </c>
+      <c r="V19" t="n">
+        <v>56.00194</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-130.04972</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t xml:space="preserve">EDYE PASS                     </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>103J  015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Hunts Inlet</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>226 kt</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 29.0g/t, Ag 10.0g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.8M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>50.53139</v>
+        <v>54.0275</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.2025</v>
+        <v>-130.585</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.73278</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.21139</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1242,21 +1242,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1414,17 +1414,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>58.185</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.30611</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1434,21 +1434,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>39.3</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>58.15222</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.27778</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1530,35 +1530,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.9</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1569,54 +1569,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2010</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="U12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>49.47472</v>
+        <v>49.29972</v>
       </c>
       <c r="W12" t="n">
-        <v>-121.51417</v>
+        <v>-126.09722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1626,30 +1626,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1670,28 +1670,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1702,17 +1702,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.73639</v>
+        <v>58.185</v>
       </c>
       <c r="W13" t="n">
-        <v>-133.24944</v>
+        <v>-125.30611</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.6</v>
+        <v>39.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1798,17 +1798,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>50.16611</v>
+        <v>58.15222</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.39944</v>
+        <v>-125.27778</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>11.4</v>
+        <v>6.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,54 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O15" t="n">
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V15" t="n">
-        <v>52.85806</v>
+        <v>49.47472</v>
       </c>
       <c r="W15" t="n">
-        <v>-132.15722</v>
+        <v>-121.51417</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1914,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37.4</v>
+        <v>2.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,29 +1953,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>1966</v>
+        <v>2019</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1986,17 +1990,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.88222</v>
+        <v>55.22278</v>
       </c>
       <c r="W16" t="n">
-        <v>-132.1175</v>
+        <v>-127.56333</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -2006,30 +2010,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2045,25 +2049,35 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$170k</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>13</v>
@@ -2072,17 +2086,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>55.98833</v>
+        <v>50.37417</v>
       </c>
       <c r="W17" t="n">
-        <v>-130.06194</v>
+        <v>-116.36167</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2092,30 +2106,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.3</v>
+        <v>7.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2136,39 +2150,49 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$64k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U18" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>50.18694</v>
+        <v>49.30889</v>
       </c>
       <c r="W18" t="n">
-        <v>-125.28056</v>
+        <v>-120.00417</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2178,35 +2202,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.7</v>
+        <v>37.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2217,25 +2241,31 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>13</v>
@@ -2244,17 +2274,467 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
+        <v>60</v>
+      </c>
+      <c r="V19" t="n">
+        <v>58.88222</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-132.1175</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AVON</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>092F  350</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Chetarpe</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$33k</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>57</v>
+      </c>
+      <c r="V20" t="n">
+        <v>49.40417</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-125.75833</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KATANGA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>092GNE009</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Williams Landing</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 62.0g/t</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>325</v>
+      </c>
+      <c r="U21" t="n">
+        <v>57</v>
+      </c>
+      <c r="V21" t="n">
+        <v>49.51111</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-122.57306</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
         <v>55</v>
       </c>
-      <c r="V19" t="n">
-        <v>56.00194</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-130.04972</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+      <c r="V22" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
+        <v>55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KING GEORGE (L.159)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>092B  011</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>East Sooke</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>175</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>48.36806</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-123.69528</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDYE PASS                     </t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>103J  015</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hunts Inlet</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>226 kt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 29.0g/t, Ag 10.0g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.8M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>54.0275</v>
+        <v>50.53139</v>
       </c>
       <c r="W7" t="n">
-        <v>-130.585</v>
+        <v>-125.2025</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>49.73278</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-125.21139</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1242,21 +1242,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>54.94444</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-126.15722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1414,17 +1414,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>58.185</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-125.30611</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1434,21 +1434,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>39.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>58.15222</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.27778</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1530,35 +1530,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.8</v>
+        <v>6.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1569,54 +1569,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29972</v>
+        <v>49.47472</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.09722</v>
+        <v>-121.51417</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1626,30 +1626,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1670,28 +1670,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1702,17 +1702,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V13" t="n">
-        <v>58.185</v>
+        <v>58.73639</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.30611</v>
+        <v>-133.24944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39.3</v>
+        <v>5.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1798,17 +1798,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>58.15222</v>
+        <v>50.16611</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.27778</v>
+        <v>-125.39944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.9</v>
+        <v>11.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,54 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O15" t="n">
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>49.47472</v>
+        <v>52.85806</v>
       </c>
       <c r="W15" t="n">
-        <v>-121.51417</v>
+        <v>-132.15722</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1914,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.7</v>
+        <v>37.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,33 +1953,29 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2019</v>
+        <v>1966</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1990,17 +1986,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V16" t="n">
-        <v>55.22278</v>
+        <v>58.88222</v>
       </c>
       <c r="W16" t="n">
-        <v>-127.56333</v>
+        <v>-132.1175</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2010,30 +2006,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2049,35 +2045,25 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$170k</t>
-        </is>
-      </c>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>13</v>
@@ -2086,17 +2072,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>50.37417</v>
+        <v>55.98833</v>
       </c>
       <c r="W17" t="n">
-        <v>-116.36167</v>
+        <v>-130.06194</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2106,30 +2092,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2150,49 +2136,39 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$64k</t>
-        </is>
-      </c>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1986</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>49.30889</v>
+        <v>50.18694</v>
       </c>
       <c r="W18" t="n">
-        <v>-120.00417</v>
+        <v>-125.28056</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>
@@ -2202,35 +2178,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37.4</v>
+        <v>5.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2241,31 +2217,25 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>13</v>
@@ -2274,467 +2244,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>58.88222</v>
+        <v>56.00194</v>
       </c>
       <c r="W19" t="n">
-        <v>-132.1175</v>
+        <v>-130.04972</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AVON</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>092F  350</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Chetarpe</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper, Lead</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$33k</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>49.40417</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-125.75833</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>KATANGA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>092GNE009</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Williams Landing</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Au 62.0g/t</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>325</v>
-      </c>
-      <c r="U21" t="n">
-        <v>57</v>
-      </c>
-      <c r="V21" t="n">
-        <v>49.51111</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-122.57306</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>093M  076</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Kispiox</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>KING GEORGE (L.159)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>092B  011</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>East Sooke</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>13 t</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>7</v>
-      </c>
-      <c r="T24" t="n">
-        <v>175</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>48.36806</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-123.69528</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,7 +742,7 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V3" t="n">
         <v>58.37694</v>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDYE PASS                     </t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>103J  015</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hunts Inlet</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>226 kt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 29.0g/t, Ag 10.0g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.8M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>54.0275</v>
+        <v>50.53139</v>
       </c>
       <c r="W7" t="n">
-        <v>-130.585</v>
+        <v>-125.2025</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>49.73278</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-125.21139</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1242,21 +1242,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>54.94444</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-126.15722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>20.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1414,17 +1414,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>57.94639</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-131.66722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1434,21 +1434,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>58.185</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.30611</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.8</v>
+        <v>39.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,49 +1574,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29972</v>
+        <v>58.15222</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.09722</v>
+        <v>-125.27778</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,54 +1665,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="V13" t="n">
-        <v>58.185</v>
+        <v>49.47472</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.30611</v>
+        <v>-121.51417</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39.3</v>
+        <v>6.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1761,33 +1761,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1798,17 +1798,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>58.15222</v>
+        <v>50.37417</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.27778</v>
+        <v>-116.36167</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.9</v>
+        <v>11.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,54 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O15" t="n">
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>49.47472</v>
+        <v>52.85806</v>
       </c>
       <c r="W15" t="n">
-        <v>-121.51417</v>
+        <v>-132.15722</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -1914,30 +1914,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1953,54 +1953,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>55.22278</v>
+        <v>49.30889</v>
       </c>
       <c r="W16" t="n">
-        <v>-127.56333</v>
+        <v>-120.00417</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2010,35 +2010,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.1</v>
+        <v>37.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2049,33 +2049,29 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>2023</v>
+        <v>1966</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2086,17 +2082,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V17" t="n">
-        <v>50.37417</v>
+        <v>58.88222</v>
       </c>
       <c r="W17" t="n">
-        <v>-116.36167</v>
+        <v>-132.1175</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2106,21 +2102,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>AVON</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092F  350</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Chetarpe</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.5</v>
+        <v>24.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2129,7 +2125,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2145,54 +2141,54 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$33k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V18" t="n">
-        <v>49.30889</v>
+        <v>49.40417</v>
       </c>
       <c r="W18" t="n">
-        <v>-120.00417</v>
+        <v>-125.75833</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
         </is>
       </c>
     </row>
@@ -2202,35 +2198,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37.4</v>
+        <v>5.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2241,31 +2237,25 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>13</v>
@@ -2274,17 +2264,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>58.88222</v>
+        <v>56.00194</v>
       </c>
       <c r="W19" t="n">
-        <v>-132.1175</v>
+        <v>-130.04972</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>
@@ -2294,21 +2284,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>24.6</v>
+        <v>7.1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2307,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2338,49 +2328,39 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$33k</t>
-        </is>
-      </c>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.40417</v>
+        <v>55.98833</v>
       </c>
       <c r="W20" t="n">
-        <v>-125.75833</v>
+        <v>-130.06194</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2390,21 +2370,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2413,7 +2393,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2434,30 +2414,20 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>13</v>
@@ -2466,17 +2436,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.51111</v>
+        <v>55.99139</v>
       </c>
       <c r="W21" t="n">
-        <v>-122.57306</v>
+        <v>-130.03694</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2486,30 +2456,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2525,17 +2495,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2546,23 +2516,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>55.98833</v>
+        <v>50.18694</v>
       </c>
       <c r="W22" t="n">
-        <v>-130.06194</v>
+        <v>-125.28056</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>
@@ -2572,30 +2542,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2611,17 +2581,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2632,23 +2602,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T23" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U23" t="n">
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>55.33556</v>
+        <v>48.36806</v>
       </c>
       <c r="W23" t="n">
-        <v>-127.69194</v>
+        <v>-123.69528</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2658,30 +2628,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2697,17 +2667,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2718,23 +2688,109 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U24" t="n">
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>48.36806</v>
+        <v>48.6075</v>
       </c>
       <c r="W24" t="n">
-        <v>-123.69528</v>
+        <v>-123.57111</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>12</v>
+      </c>
+      <c r="T25" t="n">
+        <v>300</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,7 +742,7 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V3" t="n">
         <v>58.37694</v>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,21 +954,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t xml:space="preserve">EDYE PASS                     </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>103J  015</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Hunts Inlet</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.7</v>
+        <v>10.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -977,12 +977,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,33 +993,33 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>226 kt</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Au 29.0g/t, Ag 10.0g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$1.8M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P6" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -1030,17 +1030,17 @@
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V6" t="n">
-        <v>49.27111</v>
+        <v>54.0275</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.73167</v>
+        <v>-130.585</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
         </is>
       </c>
     </row>
@@ -1434,21 +1434,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>2.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1478,28 +1478,28 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1510,17 +1510,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V11" t="n">
-        <v>58.185</v>
+        <v>55.22278</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.30611</v>
+        <v>-127.56333</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -1530,30 +1530,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>39.3</v>
+        <v>7.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1569,54 +1569,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V12" t="n">
-        <v>58.15222</v>
+        <v>49.30889</v>
       </c>
       <c r="W12" t="n">
-        <v>-125.27778</v>
+        <v>-120.00417</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>37.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,54 +1665,50 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>2010</v>
+        <v>1966</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="V13" t="n">
-        <v>49.47472</v>
+        <v>58.88222</v>
       </c>
       <c r="W13" t="n">
-        <v>-121.51417</v>
+        <v>-132.1175</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1718,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">JOHN BULL                     </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092F  146</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1766,49 +1762,49 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
         <v>2023</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V14" t="n">
-        <v>50.37417</v>
+        <v>49.94611</v>
       </c>
       <c r="W14" t="n">
-        <v>-116.36167</v>
+        <v>-124.71056</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
         </is>
       </c>
     </row>
@@ -1818,21 +1814,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1841,7 +1837,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1857,54 +1853,44 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>$74k</t>
-        </is>
-      </c>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1999</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>52.85806</v>
+        <v>55.33556</v>
       </c>
       <c r="W15" t="n">
-        <v>-132.15722</v>
+        <v>-127.69194</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>
@@ -1914,30 +1900,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.5</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1953,54 +1939,44 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>$64k</t>
-        </is>
-      </c>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1986</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>49.30889</v>
+        <v>48.36806</v>
       </c>
       <c r="W16" t="n">
-        <v>-120.00417</v>
+        <v>-123.69528</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2010,35 +1986,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37.4</v>
+        <v>1.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2049,50 +2025,44 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>58.88222</v>
+        <v>48.61472</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.1175</v>
+        <v>-123.59222</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2072,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>24.6</v>
+        <v>7.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2125,7 +2095,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2146,49 +2116,39 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$33k</t>
-        </is>
-      </c>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>49.40417</v>
+        <v>55.98833</v>
       </c>
       <c r="W18" t="n">
-        <v>-125.75833</v>
+        <v>-130.06194</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2198,21 +2158,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2237,17 +2197,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2267,530 +2227,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>56.00194</v>
+        <v>55.99139</v>
       </c>
       <c r="W19" t="n">
-        <v>-130.04972</v>
+        <v>-130.03694</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>13</v>
-      </c>
-      <c r="T20" t="n">
-        <v>325</v>
-      </c>
-      <c r="U20" t="n">
-        <v>55</v>
-      </c>
-      <c r="V20" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>FISH CREEK</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>103O  005</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>325</v>
-      </c>
-      <c r="U21" t="n">
-        <v>55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CORMORANT                     </t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>092K  098</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Granite Bay</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="n">
-        <v>250</v>
-      </c>
-      <c r="U22" t="n">
-        <v>55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>50.18694</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-125.28056</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>KING GEORGE (L.159)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>092B  011</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>East Sooke</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>13 t</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>7</v>
-      </c>
-      <c r="T23" t="n">
-        <v>175</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>48.36806</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-123.69528</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>092B  060</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>48.6075</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-123.57111</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>12</v>
-      </c>
-      <c r="T25" t="n">
-        <v>300</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -762,35 +762,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ERICKSEN-ASHBY</t>
+          <t>CHARLIE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104K  009</t>
+          <t>092O  043</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Nemaiah Valley</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.3</v>
+        <v>36.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -801,54 +801,54 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>907 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
+          <t>Au 16.0g/t, Ag 224g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
+          <t>A chip sample assayed 279.9 grams per tonne silver, 10.6 grams per tonne gold and 13.68 per cent copper (Bulletin 81). The following year, samples from the East vein area assayed up to 0.48 per cent copper, 1.0 gram per tonne gold and 14.3 grams per tonne silver (Assessment Report 12105). In 1987, chip samples from the Charlie vein, taken over a length of 20 metres and width of 20 centimetres, averaged 22.1 grams per tonne gold and 224.0 grams per tonne silver, while a sample (AB 245B) of the DK vein assayed 9.9 grams per tonne gold, 95.8 grams per tonne silver and 0.14 per cent lead (Assessment Report 17038). A 20- centimetre sample of massive sulphide from the Big vein assayed 8.2 grams per tonne gold, 8557 grams per tonne silver and 26.0 per cent copper (Assessment Report 17038). In 199</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>$286k</t>
+          <t>$6.3M</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
+          <t>Galore Resources Inc., Suncor, Galore Resources Inc.; Zelon Enterprises Ltd.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U4" t="n">
         <v>75</v>
       </c>
       <c r="V4" t="n">
-        <v>58.65806</v>
+        <v>51.18028</v>
       </c>
       <c r="W4" t="n">
-        <v>-133.475</v>
+        <v>-123.67083</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092O++043</t>
         </is>
       </c>
     </row>
@@ -858,30 +858,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DRIFTPILE CREEK</t>
+          <t>ERICKSEN-ASHBY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>094K  066</t>
+          <t>104K  009</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>5.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Barite</t>
+          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,54 +897,54 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18.1 Mt</t>
+          <t>907 kt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Pb 1.18%, Zn 10.00%</t>
+          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
+          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>$1.4M</t>
+          <t>$286k</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
+          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V5" t="n">
-        <v>58.06639</v>
+        <v>58.65806</v>
       </c>
       <c r="W5" t="n">
-        <v>-125.90972</v>
+        <v>-133.475</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
         </is>
       </c>
     </row>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDYE PASS                     </t>
+          <t>DRIFTPILE CREEK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>103J  015</t>
+          <t>094K  066</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hunts Inlet</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10.7</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Zinc, Lead, Barite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>226 kt</t>
+          <t>18.1 Mt</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 29.0g/t, Ag 10.0g/t</t>
+          <t>Pb 1.18%, Zn 10.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$1.8M</t>
+          <t>$1.4M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
+          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="V6" t="n">
-        <v>54.0275</v>
+        <v>58.06639</v>
       </c>
       <c r="W6" t="n">
-        <v>-130.585</v>
+        <v>-125.90972</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>1987</v>
+        <v>2023</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>50.53139</v>
+        <v>49.27111</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.2025</v>
+        <v>-125.73167</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.73278</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.21139</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1242,21 +1242,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20.1</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1414,17 +1414,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>57.94639</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-131.66722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1434,21 +1434,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>55.22278</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-127.56333</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1569,54 +1569,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="U12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>49.30889</v>
+        <v>49.29694</v>
       </c>
       <c r="W12" t="n">
-        <v>-120.00417</v>
+        <v>-126.08111</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>37.4</v>
+        <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,29 +1665,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>1966</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1698,17 +1702,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.88222</v>
+        <v>58.73611</v>
       </c>
       <c r="W13" t="n">
-        <v>-132.1175</v>
+        <v>-133.27</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1718,30 +1722,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHN BULL                     </t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092F  146</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>toxʷnač</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.3</v>
+        <v>20.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1757,54 +1761,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$47k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O14" t="n">
         <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>49.94611</v>
+        <v>57.94639</v>
       </c>
       <c r="W14" t="n">
-        <v>-124.71056</v>
+        <v>-131.66722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1814,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.6</v>
+        <v>6.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1853,44 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>$234k</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2010</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U15" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="V15" t="n">
-        <v>55.33556</v>
+        <v>49.47472</v>
       </c>
       <c r="W15" t="n">
-        <v>-127.69194</v>
+        <v>-121.51417</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1900,30 +1914,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>21</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1939,44 +1953,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>$208k</t>
+        </is>
+      </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2007</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>48.36806</v>
+        <v>58.73639</v>
       </c>
       <c r="W16" t="n">
-        <v>-123.69528</v>
+        <v>-133.24944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1986,30 +2010,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2025,44 +2049,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$193k</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>48.61472</v>
+        <v>55.22278</v>
       </c>
       <c r="W17" t="n">
-        <v>-123.59222</v>
+        <v>-127.56333</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -2072,30 +2106,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2111,25 +2145,35 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$170k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2138,17 +2182,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>55.98833</v>
+        <v>50.37417</v>
       </c>
       <c r="W18" t="n">
-        <v>-130.06194</v>
+        <v>-116.36167</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2158,21 +2202,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2181,7 +2225,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2197,44 +2241,328 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$64k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>225</v>
+      </c>
+      <c r="U19" t="n">
+        <v>61</v>
+      </c>
+      <c r="V19" t="n">
+        <v>49.30889</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-120.00417</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACE                           </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>104K  025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Callison Ranch</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Asbestos</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Prospect  </t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>13</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>325</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
+        <v>60</v>
+      </c>
+      <c r="V20" t="n">
+        <v>58.88222</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-132.1175</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AVON</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>092F  350</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Chetarpe</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$33k</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>25</v>
+      </c>
+      <c r="U21" t="n">
+        <v>57</v>
+      </c>
+      <c r="V21" t="n">
+        <v>49.40417</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-125.75833</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
         <v>55</v>
       </c>
-      <c r="V19" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+      <c r="V22" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -762,35 +762,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHARLIE</t>
+          <t>ERICKSEN-ASHBY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>092O  043</t>
+          <t>104K  009</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nemaiah Valley</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36.9</v>
+        <v>5.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -801,54 +801,54 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>907 kt</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 16.0g/t, Ag 224g/t</t>
+          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>A chip sample assayed 279.9 grams per tonne silver, 10.6 grams per tonne gold and 13.68 per cent copper (Bulletin 81). The following year, samples from the East vein area assayed up to 0.48 per cent copper, 1.0 gram per tonne gold and 14.3 grams per tonne silver (Assessment Report 12105). In 1987, chip samples from the Charlie vein, taken over a length of 20 metres and width of 20 centimetres, averaged 22.1 grams per tonne gold and 224.0 grams per tonne silver, while a sample (AB 245B) of the DK vein assayed 9.9 grams per tonne gold, 95.8 grams per tonne silver and 0.14 per cent lead (Assessment Report 17038). A 20- centimetre sample of massive sulphide from the Big vein assayed 8.2 grams per tonne gold, 8557 grams per tonne silver and 26.0 per cent copper (Assessment Report 17038). In 199</t>
+          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>$6.3M</t>
+          <t>$286k</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Galore Resources Inc., Suncor, Galore Resources Inc.; Zelon Enterprises Ltd.</t>
+          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>75</v>
       </c>
       <c r="V4" t="n">
-        <v>51.18028</v>
+        <v>58.65806</v>
       </c>
       <c r="W4" t="n">
-        <v>-123.67083</v>
+        <v>-133.475</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092O++043</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
         </is>
       </c>
     </row>
@@ -858,30 +858,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ERICKSEN-ASHBY</t>
+          <t>DRIFTPILE CREEK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>104K  009</t>
+          <t>094K  066</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.3</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
+          <t>Zinc, Lead, Barite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,54 +897,54 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>907 kt</t>
+          <t>18.1 Mt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
+          <t>Pb 1.18%, Zn 10.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
+          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>$286k</t>
+          <t>$1.4M</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
+          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V5" t="n">
-        <v>58.65806</v>
+        <v>58.06639</v>
       </c>
       <c r="W5" t="n">
-        <v>-133.475</v>
+        <v>-125.90972</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DRIFTPILE CREEK</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>094K  066</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>16.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Barite</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18.1 Mt</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pb 1.18%, Zn 10.00%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$1.4M</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="V6" t="n">
-        <v>58.06639</v>
+        <v>49.27111</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.90972</v>
+        <v>-125.73167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.7</v>
+        <v>31.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>49.27111</v>
+        <v>58.90944</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.73167</v>
+        <v>-129.09278</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1146,30 +1146,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1185,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,33 +1281,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1321,14 +1321,14 @@
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1434,21 +1434,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>1988</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>125</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>49.29972</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-126.09722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1530,30 +1530,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.8</v>
+        <v>20</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,49 +1574,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2007</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29694</v>
+        <v>58.73611</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.08111</v>
+        <v>-133.27</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1626,30 +1626,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1670,28 +1670,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1705,14 +1705,14 @@
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.73611</v>
+        <v>58.185</v>
       </c>
       <c r="W13" t="n">
-        <v>-133.27</v>
+        <v>-125.30611</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20.1</v>
+        <v>39.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O14" t="n">
         <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1801,14 +1801,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>57.94639</v>
+        <v>58.15222</v>
       </c>
       <c r="W14" t="n">
-        <v>-131.66722</v>
+        <v>-125.27778</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -2106,30 +2106,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.1</v>
+        <v>11.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2145,33 +2145,33 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2185,14 +2185,14 @@
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>50.37417</v>
+        <v>52.85806</v>
       </c>
       <c r="W18" t="n">
-        <v>-116.36167</v>
+        <v>-132.15722</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2202,35 +2202,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.5</v>
+        <v>37.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2241,54 +2241,50 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>1986</v>
+        <v>1966</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V19" t="n">
-        <v>49.30889</v>
+        <v>58.88222</v>
       </c>
       <c r="W19" t="n">
-        <v>-120.00417</v>
+        <v>-132.1175</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2298,35 +2294,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">JOHN BULL                     </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092F  146</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37.4</v>
+        <v>3.3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2337,50 +2333,54 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>1966</v>
+        <v>2023</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>58.88222</v>
+        <v>49.94611</v>
       </c>
       <c r="W20" t="n">
-        <v>-132.1175</v>
+        <v>-124.71056</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
         </is>
       </c>
     </row>
@@ -2486,21 +2486,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2525,25 +2525,35 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>13</v>
@@ -2552,17 +2562,533 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
+        <v>57</v>
+      </c>
+      <c r="V22" t="n">
+        <v>49.51111</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-122.57306</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FISH CREEK</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>103O  005</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
         <v>55</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V23" t="n">
+        <v>55.99139</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-130.03694</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
         <v>55.33556</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W24" t="n">
         <v>-127.69194</v>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KING GEORGE (L.159)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>092B  011</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>East Sooke</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>175</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>48.36806</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-123.69528</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>13</v>
+      </c>
+      <c r="T27" t="n">
+        <v>325</v>
+      </c>
+      <c r="U27" t="n">
+        <v>55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>092B  060</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>13</v>
+      </c>
+      <c r="T28" t="n">
+        <v>325</v>
+      </c>
+      <c r="U28" t="n">
+        <v>55</v>
+      </c>
+      <c r="V28" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X28"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31.5</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1089,33 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>58.90944</v>
+        <v>50.53139</v>
       </c>
       <c r="W7" t="n">
-        <v>-129.09278</v>
+        <v>-125.2025</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1225,14 +1225,14 @@
         <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>50.40806</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1504,10 +1504,10 @@
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
@@ -1530,30 +1530,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,28 +1574,28 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1609,14 +1609,14 @@
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>58.73611</v>
+        <v>57.94639</v>
       </c>
       <c r="W12" t="n">
-        <v>-133.27</v>
+        <v>-131.66722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,54 +1665,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="V13" t="n">
-        <v>58.185</v>
+        <v>49.47472</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.30611</v>
+        <v>-121.51417</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39.3</v>
+        <v>6.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1761,33 +1761,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1798,17 +1798,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>58.15222</v>
+        <v>50.37417</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.27778</v>
+        <v>-116.36167</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,54 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>49.47472</v>
+        <v>50.16611</v>
       </c>
       <c r="W15" t="n">
-        <v>-121.51417</v>
+        <v>-125.39944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1914,21 +1914,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1953,54 +1953,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2007</v>
+        <v>1986</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.73639</v>
+        <v>49.30889</v>
       </c>
       <c r="W16" t="n">
-        <v>-133.24944</v>
+        <v>-120.00417</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2010,35 +2010,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.7</v>
+        <v>37.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2049,33 +2049,29 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>2019</v>
+        <v>1966</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2086,17 +2082,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V17" t="n">
-        <v>55.22278</v>
+        <v>58.88222</v>
       </c>
       <c r="W17" t="n">
-        <v>-127.56333</v>
+        <v>-132.1175</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2106,30 +2102,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.4</v>
+        <v>5.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2145,54 +2141,44 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$74k</t>
-        </is>
-      </c>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1999</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>52.85806</v>
+        <v>50.18694</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.15722</v>
+        <v>-125.28056</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>
@@ -2202,35 +2188,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37.4</v>
+        <v>5.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2241,31 +2227,25 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>13</v>
@@ -2274,821 +2254,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>58.88222</v>
+        <v>56.00194</v>
       </c>
       <c r="W19" t="n">
-        <v>-132.1175</v>
+        <v>-130.04972</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JOHN BULL                     </t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>092F  146</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>toxʷnač</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$47k</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>125</v>
-      </c>
-      <c r="U20" t="n">
-        <v>57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>49.94611</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-124.71056</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AVON</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>092F  350</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Chetarpe</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper, Lead</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$33k</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>57</v>
-      </c>
-      <c r="V21" t="n">
-        <v>49.40417</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-125.75833</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>KATANGA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>092GNE009</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Williams Landing</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Au 62.0g/t</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>57</v>
-      </c>
-      <c r="V22" t="n">
-        <v>49.51111</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-122.57306</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>FISH CREEK</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>103O  005</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>093M  076</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Kispiox</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>KING GEORGE (L.159)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>092B  011</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>East Sooke</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>13 t</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>7</v>
-      </c>
-      <c r="T25" t="n">
-        <v>175</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>48.36806</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-123.69528</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>13</v>
-      </c>
-      <c r="T27" t="n">
-        <v>325</v>
-      </c>
-      <c r="U27" t="n">
-        <v>55</v>
-      </c>
-      <c r="V27" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>092B  060</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>13</v>
-      </c>
-      <c r="T28" t="n">
-        <v>325</v>
-      </c>
-      <c r="U28" t="n">
-        <v>55</v>
-      </c>
-      <c r="V28" t="n">
-        <v>48.6075</v>
-      </c>
-      <c r="W28" t="n">
-        <v>-123.57111</v>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,7 +742,7 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V3" t="n">
         <v>58.37694</v>
@@ -1338,30 +1338,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1382,49 +1382,49 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2025</v>
+        <v>1988</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U10" t="n">
         <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>50.40806</v>
+        <v>49.29694</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.96167</v>
+        <v>-126.08111</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1504,10 +1504,10 @@
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1761,33 +1761,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1801,14 +1801,14 @@
         <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>50.37417</v>
+        <v>55.22278</v>
       </c>
       <c r="W14" t="n">
-        <v>-116.36167</v>
+        <v>-127.56333</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -1818,30 +1818,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1857,54 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
         <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>50.16611</v>
+        <v>49.30889</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.39944</v>
+        <v>-120.00417</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1914,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.5</v>
+        <v>37.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,54 +1953,50 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>1986</v>
+        <v>1966</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V16" t="n">
-        <v>49.30889</v>
+        <v>58.88222</v>
       </c>
       <c r="W16" t="n">
-        <v>-120.00417</v>
+        <v>-132.1175</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2010,35 +2006,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">JOHN BULL                     </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092F  146</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37.4</v>
+        <v>3.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2049,50 +2045,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>1966</v>
+        <v>2023</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U17" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="V17" t="n">
-        <v>58.88222</v>
+        <v>49.94611</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.1175</v>
+        <v>-124.71056</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
         </is>
       </c>
     </row>
@@ -2102,30 +2102,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2162,23 +2162,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>50.18694</v>
+        <v>55.98833</v>
       </c>
       <c r="W18" t="n">
-        <v>-125.28056</v>
+        <v>-130.06194</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2188,21 +2188,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2227,17 +2227,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2257,14 +2257,358 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>56.00194</v>
+        <v>55.99139</v>
       </c>
       <c r="W19" t="n">
-        <v>-130.04972</v>
+        <v>-130.03694</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>092B  060</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>13</v>
+      </c>
+      <c r="T20" t="n">
+        <v>325</v>
+      </c>
+      <c r="U20" t="n">
+        <v>55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KING GEORGE (L.159)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>092B  011</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>East Sooke</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>150</v>
+      </c>
+      <c r="U21" t="n">
+        <v>55</v>
+      </c>
+      <c r="V21" t="n">
+        <v>48.36806</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-123.69528</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
+        <v>55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>12</v>
+      </c>
+      <c r="T23" t="n">
+        <v>300</v>
+      </c>
+      <c r="U23" t="n">
+        <v>55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,7 +742,7 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V3" t="n">
         <v>58.37694</v>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>31.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1089,33 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>50.53139</v>
+        <v>58.90944</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.2025</v>
+        <v>-129.09278</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1225,14 +1225,14 @@
         <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>49.29694</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.08111</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1434,30 +1434,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1478,49 +1478,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>1988</v>
+        <v>2025</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>49.29972</v>
+        <v>50.40806</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.09722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20.1</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,49 +1574,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2019</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U12" t="n">
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>57.94639</v>
+        <v>49.29972</v>
       </c>
       <c r="W12" t="n">
-        <v>-131.66722</v>
+        <v>-126.09722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1665,54 +1665,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.47472</v>
+        <v>58.73611</v>
       </c>
       <c r="W13" t="n">
-        <v>-121.51417</v>
+        <v>-133.27</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.7</v>
+        <v>20.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
         <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1798,17 +1798,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>55.22278</v>
+        <v>57.94639</v>
       </c>
       <c r="W14" t="n">
-        <v>-127.56333</v>
+        <v>-131.66722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,54 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>1986</v>
+        <v>2010</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V15" t="n">
-        <v>49.30889</v>
+        <v>49.47472</v>
       </c>
       <c r="W15" t="n">
-        <v>-120.00417</v>
+        <v>-121.51417</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1914,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37.4</v>
+        <v>21</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,29 +1953,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1966</v>
+        <v>2007</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1986,17 +1990,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.88222</v>
+        <v>58.73639</v>
       </c>
       <c r="W16" t="n">
-        <v>-132.1175</v>
+        <v>-133.24944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2006,30 +2010,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHN BULL                     </t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092F  146</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>toxʷnač</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2045,54 +2049,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$47k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>49.94611</v>
+        <v>55.22278</v>
       </c>
       <c r="W17" t="n">
-        <v>-124.71056</v>
+        <v>-127.56333</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -2102,30 +2106,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2141,25 +2145,35 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$170k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2168,17 +2182,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>55.98833</v>
+        <v>50.37417</v>
       </c>
       <c r="W18" t="n">
-        <v>-130.06194</v>
+        <v>-116.36167</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2188,30 +2202,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t>MAGNOLIA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092F  274</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Marshall School Junction</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Copper, Gold, Silver, Lead, Zinc, Magnetite, Iron</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2232,39 +2246,49 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Au 9.9g/t, Ag 231g/t, Cu 4.60%, Pb 16.00%, Zn 15.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>Grab samples of dump material around a shaft that was sunk on the lens assayed up to 4.6 per cent copper, 18.51 grams per tonne gold and 17.14 grams per tonne silver (Assessment Report 5749). Seven hundred metres to the northwest from the Cap Sheaf shaft, grab samples from a showing on the Milner claim (Lot 77) assayed 4 to 16 per cent lead, 5 to 15 per cent zinc, 0.68 to 1.37 grams per tonne gold and 171.4 to 445.64 grams per tonne silver (Assessment 5749).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$104k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2006</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CanQuest Resource Corporation, Greenlite Ventures Inc., Longbar Minerals Limited</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>55.99139</v>
+        <v>49.70361</v>
       </c>
       <c r="W19" t="n">
-        <v>-130.03694</v>
+        <v>-124.48639</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++274</t>
         </is>
       </c>
     </row>
@@ -2274,30 +2298,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.6</v>
+        <v>11.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2313,25 +2337,35 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
         <v>13</v>
@@ -2340,17 +2374,17 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V20" t="n">
-        <v>48.6075</v>
+        <v>52.85806</v>
       </c>
       <c r="W20" t="n">
-        <v>-123.57111</v>
+        <v>-132.15722</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2360,35 +2394,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8</v>
+        <v>37.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2399,44 +2433,50 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13 t</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V21" t="n">
-        <v>48.36806</v>
+        <v>58.88222</v>
       </c>
       <c r="W21" t="n">
-        <v>-123.69528</v>
+        <v>-132.1175</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2446,21 +2486,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2469,7 +2509,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2485,25 +2525,35 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>13</v>
@@ -2512,17 +2562,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V22" t="n">
-        <v>55.33556</v>
+        <v>49.51111</v>
       </c>
       <c r="W22" t="n">
-        <v>-127.69194</v>
+        <v>-122.57306</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2532,30 +2582,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2571,17 +2621,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2592,23 +2642,281 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>48.61472</v>
+        <v>55.99139</v>
       </c>
       <c r="W23" t="n">
-        <v>-123.59222</v>
+        <v>-130.03694</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="n">
+        <v>250</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>
